--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
   <si>
     <t xml:space="preserve">meeting_date</t>
   </si>
@@ -891,21 +891,12 @@
     <t xml:space="preserve">Kerry Hoggan</t>
   </si>
   <si>
-    <t xml:space="preserve">BENTLEY SVEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shawn Speeding</t>
-  </si>
-  <si>
     <t xml:space="preserve">BLOCKER TIGER</t>
   </si>
   <si>
     <t xml:space="preserve">Stephen Neary</t>
   </si>
   <si>
-    <t xml:space="preserve">TUTA MOMENT</t>
-  </si>
-  <si>
     <t xml:space="preserve">SPEEDY BEN</t>
   </si>
   <si>
@@ -919,6 +910,12 @@
   </si>
   <si>
     <t xml:space="preserve">HOT PINK DOUBLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAKODA SKYLAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAG THE JOKER</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10 13:10:00</t>
@@ -1759,7 +1756,7 @@
         <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.18174060739556</v>
+        <v>4.18411334857935</v>
       </c>
       <c r="L2"/>
       <c r="M2"/>
@@ -1773,13 +1770,13 @@
         <v>0.226909857942562</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1783932097324</v>
+        <v>2.17913181775719</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51599283372543</v>
+        <v>1.51659310359693</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="T2"/>
       <c r="U2"/>
@@ -1885,7 +1882,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.27359140784093</v>
+        <v>4.27290634671216</v>
       </c>
       <c r="L3"/>
       <c r="M3"/>
@@ -1899,13 +1896,13 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.19964459851502</v>
+        <v>2.1995120478238</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52280417939659</v>
+        <v>1.52272172825024</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="T3"/>
       <c r="U3"/>
@@ -2011,7 +2008,7 @@
         <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5920523717456</v>
+        <v>4.5914344243232</v>
       </c>
       <c r="L4"/>
       <c r="M4"/>
@@ -2025,13 +2022,13 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32491015614774</v>
+        <v>2.32441644408913</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58184370356901</v>
+        <v>1.58153930772236</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="T4"/>
       <c r="U4"/>
@@ -2137,7 +2134,7 @@
         <v>69</v>
       </c>
       <c r="K5" t="n">
-        <v>5.13586240178947</v>
+        <v>5.13388010424858</v>
       </c>
       <c r="L5"/>
       <c r="M5"/>
@@ -2151,10 +2148,10 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55736349470599</v>
+        <v>2.55685711928246</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6954310151713</v>
+        <v>1.69514628646778</v>
       </c>
       <c r="S5" t="n">
         <v>-0.3</v>
@@ -2263,13 +2260,13 @@
         <v>71</v>
       </c>
       <c r="K6" t="n">
-        <v>11.9064712830424</v>
+        <v>11.9053012061537</v>
       </c>
       <c r="L6" t="n">
-        <v>8.5716979514871</v>
+        <v>8.56729204146321</v>
       </c>
       <c r="M6" t="n">
-        <v>38.9044661912839</v>
+        <v>38.9622432448375</v>
       </c>
       <c r="N6" t="s">
         <v>72</v>
@@ -2281,10 +2278,10 @@
         <v>0.182134690495737</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.19091230007891</v>
+        <v>5.19166631985436</v>
       </c>
       <c r="R6" t="n">
-        <v>3.05756578560834</v>
+        <v>3.05702488062709</v>
       </c>
       <c r="S6" t="n">
         <v>-1.8</v>
@@ -2413,13 +2410,13 @@
         <v>67</v>
       </c>
       <c r="K7" t="n">
-        <v>32.889173433643</v>
+        <v>32.905028755274</v>
       </c>
       <c r="L7" t="n">
         <v>35.1514938488576</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.43591542636002</v>
+        <v>-6.3908097426608</v>
       </c>
       <c r="N7" t="s">
         <v>76</v>
@@ -2431,10 +2428,10 @@
         <v>0.177173988626008</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.7872212956177</v>
+        <v>13.7896214671567</v>
       </c>
       <c r="R7" t="n">
-        <v>7.42769664569099</v>
+        <v>7.430626604508</v>
       </c>
       <c r="S7" t="n">
         <v>-3.3</v>
@@ -2561,13 +2558,13 @@
         <v>81</v>
       </c>
       <c r="K8" t="n">
-        <v>2.15617221503697</v>
+        <v>2.15585204287127</v>
       </c>
       <c r="L8" t="n">
-        <v>2.15741559702297</v>
+        <v>2.15937209854684</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0576329376555385</v>
+        <v>-0.163012927597761</v>
       </c>
       <c r="N8" t="s">
         <v>76</v>
@@ -2579,10 +2576,10 @@
         <v>0.191927728555908</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.33671443518307</v>
+        <v>1.33661658102578</v>
       </c>
       <c r="R8" t="n">
-        <v>1.11809328531995</v>
+        <v>1.11816709142163</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -2709,13 +2706,13 @@
         <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>4.72657776102373</v>
+        <v>4.72913021235934</v>
       </c>
       <c r="L9" t="n">
-        <v>4.64306606620549</v>
+        <v>4.64005010903355</v>
       </c>
       <c r="M9" t="n">
-        <v>1.79863249041572</v>
+        <v>1.9198090803453</v>
       </c>
       <c r="N9" t="s">
         <v>72</v>
@@ -2727,10 +2724,10 @@
         <v>0.249038124979973</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15648441379775</v>
+        <v>2.15715869614544</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42236159138651</v>
+        <v>1.42260675260025</v>
       </c>
       <c r="S9" t="n">
         <v>-1.2</v>
@@ -2847,7 +2844,7 @@
         <v>55</v>
       </c>
       <c r="K10" t="n">
-        <v>5.93465720439917</v>
+        <v>5.9328302991148</v>
       </c>
       <c r="L10"/>
       <c r="M10"/>
@@ -2861,10 +2858,10 @@
         <v>0.226652746151221</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56062404864703</v>
+        <v>2.55972372553759</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55424141451365</v>
+        <v>1.55403024999925</v>
       </c>
       <c r="S10" t="n">
         <v>-1.5</v>
@@ -2973,13 +2970,13 @@
         <v>86</v>
       </c>
       <c r="K11" t="n">
-        <v>13.8780400907016</v>
+        <v>13.8774846799441</v>
       </c>
       <c r="L11" t="n">
-        <v>11.4910950247041</v>
+        <v>11.4858160101068</v>
       </c>
       <c r="M11" t="n">
-        <v>20.7721288603556</v>
+        <v>20.8228015121673</v>
       </c>
       <c r="N11" t="s">
         <v>87</v>
@@ -2991,10 +2988,10 @@
         <v>0.188541326758434</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.49487380724263</v>
+        <v>5.494658553575</v>
       </c>
       <c r="R11" t="n">
-        <v>2.95485544639376</v>
+        <v>2.95459243673048</v>
       </c>
       <c r="S11" t="n">
         <v>-3</v>
@@ -3121,13 +3118,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>27.9033561914265</v>
+        <v>27.9106233720788</v>
       </c>
       <c r="L12" t="n">
-        <v>30.186236039843</v>
+        <v>30.3143376780843</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.56265155219524</v>
+        <v>-7.92929844462091</v>
       </c>
       <c r="N12" t="s">
         <v>72</v>
@@ -3139,10 +3136,10 @@
         <v>0.211560562780329</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.0036117674004</v>
+        <v>11.0157692913192</v>
       </c>
       <c r="R12" t="n">
-        <v>5.74301391099156</v>
+        <v>5.74519295815169</v>
       </c>
       <c r="S12" t="n">
         <v>-4</v>
@@ -3271,13 +3268,13 @@
         <v>67</v>
       </c>
       <c r="K13" t="n">
-        <v>34.8978317572972</v>
+        <v>34.8953655656761</v>
       </c>
       <c r="L13" t="n">
-        <v>31.5579047017987</v>
+        <v>31.4784387787221</v>
       </c>
       <c r="M13" t="n">
-        <v>10.5834879947151</v>
+        <v>10.8548165649935</v>
       </c>
       <c r="N13" t="s">
         <v>76</v>
@@ -3289,10 +3286,10 @@
         <v>0.197536959578864</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.8465535228561</v>
+        <v>13.8410499778953</v>
       </c>
       <c r="R13" t="n">
-        <v>7.09651611139646</v>
+        <v>7.09156815371654</v>
       </c>
       <c r="S13" t="n">
         <v>-4.7</v>
@@ -3419,13 +3416,13 @@
         <v>67</v>
       </c>
       <c r="K14" t="n">
-        <v>51.0346842928316</v>
+        <v>51.0402912461405</v>
       </c>
       <c r="L14" t="n">
-        <v>41.5484004985459</v>
+        <v>41.5139061851391</v>
       </c>
       <c r="M14" t="n">
-        <v>22.8318868607653</v>
+        <v>22.9474552900821</v>
       </c>
       <c r="N14" t="s">
         <v>72</v>
@@ -3437,10 +3434,10 @@
         <v>0.200108477641868</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.0250191466135</v>
+        <v>19.0187693969427</v>
       </c>
       <c r="R14" t="n">
-        <v>9.46086307407307</v>
+        <v>9.45814595701087</v>
       </c>
       <c r="S14" t="n">
         <v>-5.2</v>
@@ -3567,13 +3564,13 @@
         <v>98</v>
       </c>
       <c r="K15" t="n">
-        <v>2.85403032676696</v>
+        <v>2.85462453328373</v>
       </c>
       <c r="L15" t="n">
-        <v>3.40426183749191</v>
+        <v>3.40634899008822</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.1630196791893</v>
+        <v>-16.196944541205</v>
       </c>
       <c r="N15" t="s">
         <v>76</v>
@@ -3585,10 +3582,10 @@
         <v>0.183347862652581</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58727337219102</v>
+        <v>1.5874164594016</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23560551336129</v>
+        <v>1.23569608097425</v>
       </c>
       <c r="S15" t="n">
         <v>0.2</v>
@@ -3715,13 +3712,13 @@
         <v>71</v>
       </c>
       <c r="K16" t="n">
-        <v>3.22447203239721</v>
+        <v>3.2241320061971</v>
       </c>
       <c r="L16" t="n">
-        <v>3.58460876733933</v>
+        <v>3.58615125327213</v>
       </c>
       <c r="M16" t="n">
-        <v>-10.0467514955457</v>
+        <v>-10.0949240984947</v>
       </c>
       <c r="N16" t="s">
         <v>72</v>
@@ -3733,10 +3730,10 @@
         <v>0.175962029344542</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68289282288243</v>
+        <v>1.68274224641172</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26441103759708</v>
+        <v>1.2643835249988</v>
       </c>
       <c r="S16" t="n">
         <v>-0.2</v>
@@ -3865,13 +3862,13 @@
         <v>102</v>
       </c>
       <c r="K17" t="n">
-        <v>8.37766951521434</v>
+        <v>8.37110056395665</v>
       </c>
       <c r="L17" t="n">
-        <v>6.62692995825326</v>
+        <v>6.61465705403797</v>
       </c>
       <c r="M17" t="n">
-        <v>26.4185613548048</v>
+        <v>26.5538106597144</v>
       </c>
       <c r="N17" t="s">
         <v>72</v>
@@ -3883,10 +3880,10 @@
         <v>0.178825600449768</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.73326340428585</v>
+        <v>3.73178234233615</v>
       </c>
       <c r="R17" t="n">
-        <v>2.13683099913203</v>
+        <v>2.13615093546677</v>
       </c>
       <c r="S17" t="n">
         <v>-1.8</v>
@@ -4013,13 +4010,13 @@
         <v>104</v>
       </c>
       <c r="K18" t="n">
-        <v>13.1604864043218</v>
+        <v>13.1580835079912</v>
       </c>
       <c r="L18" t="n">
-        <v>9.30038128894262</v>
+        <v>9.31597578015836</v>
       </c>
       <c r="M18" t="n">
-        <v>41.5048049693239</v>
+        <v>41.2421395085204</v>
       </c>
       <c r="N18" t="s">
         <v>72</v>
@@ -4031,10 +4028,10 @@
         <v>0.179244637456315</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.68678340276676</v>
+        <v>5.68676607061255</v>
       </c>
       <c r="R18" t="n">
-        <v>3.14587056566486</v>
+        <v>3.14591961302023</v>
       </c>
       <c r="S18" t="n">
         <v>-2.6</v>
@@ -4161,13 +4158,13 @@
         <v>104</v>
       </c>
       <c r="K19" t="n">
-        <v>14.0474647621089</v>
+        <v>14.0587877912744</v>
       </c>
       <c r="L19" t="n">
-        <v>13.1709469247992</v>
+        <v>13.1640121100434</v>
       </c>
       <c r="M19" t="n">
-        <v>6.65493409330606</v>
+        <v>6.79713505085771</v>
       </c>
       <c r="N19" t="s">
         <v>72</v>
@@ -4179,10 +4176,10 @@
         <v>0.184265011173798</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.00274309814709</v>
+        <v>6.00741094621541</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24367130629003</v>
+        <v>3.24504757205682</v>
       </c>
       <c r="S19" t="n">
         <v>-2.4</v>
@@ -4309,13 +4306,13 @@
         <v>107</v>
       </c>
       <c r="K20" t="n">
-        <v>18.0046973378593</v>
+        <v>18.0094832066203</v>
       </c>
       <c r="L20" t="n">
-        <v>13.8533037816872</v>
+        <v>13.8074002485158</v>
       </c>
       <c r="M20" t="n">
-        <v>29.9668124051381</v>
+        <v>30.4335565165945</v>
       </c>
       <c r="N20" t="s">
         <v>72</v>
@@ -4327,10 +4324,10 @@
         <v>0.215347021935937</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.04218562794729</v>
+        <v>8.03963496888747</v>
       </c>
       <c r="R20" t="n">
-        <v>4.42089001807478</v>
+        <v>4.42000056544863</v>
       </c>
       <c r="S20" t="n">
         <v>-2.9</v>
@@ -4459,13 +4456,13 @@
         <v>109</v>
       </c>
       <c r="K21" t="n">
-        <v>57.4324699369739</v>
+        <v>57.4167169275591</v>
       </c>
       <c r="L21" t="n">
-        <v>48.1961445783133</v>
+        <v>48.3826802128689</v>
       </c>
       <c r="M21" t="n">
-        <v>19.1640336368663</v>
+        <v>18.6720468459854</v>
       </c>
       <c r="N21" t="s">
         <v>72</v>
@@ -4477,10 +4474,10 @@
         <v>0.18965029356576</v>
       </c>
       <c r="Q21" t="n">
-        <v>24.3128033020811</v>
+        <v>24.320628923544</v>
       </c>
       <c r="R21" t="n">
-        <v>12.5870154626681</v>
+        <v>12.5896603854558</v>
       </c>
       <c r="S21" t="n">
         <v>-4.5</v>
@@ -4609,13 +4606,13 @@
         <v>104</v>
       </c>
       <c r="K22" t="n">
-        <v>2.74622085412815</v>
+        <v>2.74470165769019</v>
       </c>
       <c r="L22" t="n">
-        <v>2.93249860716066</v>
+        <v>2.92786251719999</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.35218555867855</v>
+        <v>-6.25578757314603</v>
       </c>
       <c r="N22" t="s">
         <v>72</v>
@@ -4627,10 +4624,10 @@
         <v>0.183503059384755</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.55842809079867</v>
+        <v>1.55817332314027</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22729652589916</v>
+        <v>1.22727162443303</v>
       </c>
       <c r="S22" t="n">
         <v>0.3</v>
@@ -4757,13 +4754,13 @@
         <v>115</v>
       </c>
       <c r="K23" t="n">
-        <v>3.60380899355831</v>
+        <v>3.6067236130357</v>
       </c>
       <c r="L23" t="n">
-        <v>4.78571086758865</v>
+        <v>4.78433717648184</v>
       </c>
       <c r="M23" t="n">
-        <v>-24.6964747083824</v>
+        <v>-24.6139333413808</v>
       </c>
       <c r="N23" t="s">
         <v>76</v>
@@ -4775,10 +4772,10 @@
         <v>0.197917047631314</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8716295326755</v>
+        <v>1.87230363804466</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37891823805731</v>
+        <v>1.37913042919832</v>
       </c>
       <c r="S23" t="n">
         <v>-0.3</v>
@@ -4905,13 +4902,13 @@
         <v>117</v>
       </c>
       <c r="K24" t="n">
-        <v>9.72281712136781</v>
+        <v>9.72154752710711</v>
       </c>
       <c r="L24" t="n">
-        <v>7.55282833622838</v>
+        <v>7.57341915940932</v>
       </c>
       <c r="M24" t="n">
-        <v>28.7308103473069</v>
+        <v>28.3640496119765</v>
       </c>
       <c r="N24" t="s">
         <v>72</v>
@@ -4923,10 +4920,10 @@
         <v>0.17759029255941</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2889565854827</v>
+        <v>4.28954651900046</v>
       </c>
       <c r="R24" t="n">
-        <v>2.48495027412897</v>
+        <v>2.48538624692369</v>
       </c>
       <c r="S24" t="n">
         <v>-2</v>
@@ -5053,13 +5050,13 @@
         <v>119</v>
       </c>
       <c r="K25" t="n">
-        <v>11.4823306703196</v>
+        <v>11.48873987528</v>
       </c>
       <c r="L25" t="n">
-        <v>8.48595672464998</v>
+        <v>8.5061665390831</v>
       </c>
       <c r="M25" t="n">
-        <v>35.3097952640475</v>
+        <v>35.0636602574484</v>
       </c>
       <c r="N25" t="s">
         <v>72</v>
@@ -5071,10 +5068,10 @@
         <v>0.192447139973863</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.11072531377645</v>
+        <v>5.11110094579047</v>
       </c>
       <c r="R25" t="n">
-        <v>2.94282263661639</v>
+        <v>2.94260291428902</v>
       </c>
       <c r="S25" t="n">
         <v>-2.3</v>
@@ -5201,13 +5198,13 @@
         <v>121</v>
       </c>
       <c r="K26" t="n">
-        <v>13.1898854451626</v>
+        <v>13.1881696094801</v>
       </c>
       <c r="L26" t="n">
-        <v>9.72736115163895</v>
+        <v>9.73683185668387</v>
       </c>
       <c r="M26" t="n">
-        <v>35.5957205612774</v>
+        <v>35.4462088243523</v>
       </c>
       <c r="N26" t="s">
         <v>72</v>
@@ -5219,10 +5216,10 @@
         <v>0.186278368470203</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.77873633243171</v>
+        <v>5.77616530348928</v>
       </c>
       <c r="R26" t="n">
-        <v>3.2880878909306</v>
+        <v>3.28756905374394</v>
       </c>
       <c r="S26" t="n">
         <v>-2.5</v>
@@ -5349,13 +5346,13 @@
         <v>71</v>
       </c>
       <c r="K27" t="n">
-        <v>19.5505359533023</v>
+        <v>19.547623607726</v>
       </c>
       <c r="L27" t="n">
-        <v>22.3879561226774</v>
+        <v>22.4281228975107</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.673868725788</v>
+        <v>-12.8432473058385</v>
       </c>
       <c r="N27" t="s">
         <v>72</v>
@@ -5367,10 +5364,10 @@
         <v>0.168092691861424</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.06830183951689</v>
+        <v>8.07336842025816</v>
       </c>
       <c r="R27" t="n">
-        <v>4.307232119679</v>
+        <v>4.30911700150143</v>
       </c>
       <c r="S27" t="n">
         <v>-2.6</v>
@@ -5499,13 +5496,13 @@
         <v>98</v>
       </c>
       <c r="K28" t="n">
-        <v>24.1122489112967</v>
+        <v>24.0888091678317</v>
       </c>
       <c r="L28" t="n">
-        <v>19.1108350850373</v>
+        <v>19.0308277830637</v>
       </c>
       <c r="M28" t="n">
-        <v>26.1705666131528</v>
+        <v>26.5778317287345</v>
       </c>
       <c r="N28" t="s">
         <v>72</v>
@@ -5517,10 +5514,10 @@
         <v>0.180177082435504</v>
       </c>
       <c r="Q28" t="n">
-        <v>10.1812153640853</v>
+        <v>10.167276660427</v>
       </c>
       <c r="R28" t="n">
-        <v>5.51065311668814</v>
+        <v>5.50477356092611</v>
       </c>
       <c r="S28" t="n">
         <v>-3.2</v>
@@ -5647,13 +5644,13 @@
         <v>128</v>
       </c>
       <c r="K29" t="n">
-        <v>3.03138927792839</v>
+        <v>3.03093037665722</v>
       </c>
       <c r="L29" t="n">
-        <v>2.94094986031466</v>
+        <v>2.94458675617584</v>
       </c>
       <c r="M29" t="n">
-        <v>3.07517713355547</v>
+        <v>2.93228312259062</v>
       </c>
       <c r="N29" t="s">
         <v>72</v>
@@ -5665,10 +5662,10 @@
         <v>0.168718088692851</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.71400664924829</v>
+        <v>1.71370190287466</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31122225046686</v>
+        <v>1.31121436936158</v>
       </c>
       <c r="S29" t="n">
         <v>0.6</v>
@@ -5795,13 +5792,13 @@
         <v>131</v>
       </c>
       <c r="K30" t="n">
-        <v>5.06540701992887</v>
+        <v>5.06739537566278</v>
       </c>
       <c r="L30" t="n">
-        <v>5.19813919642393</v>
+        <v>5.20463179807442</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.55345560169629</v>
+        <v>-2.63681327971012</v>
       </c>
       <c r="N30" t="s">
         <v>72</v>
@@ -5813,10 +5810,10 @@
         <v>0.188460113034842</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52115102341076</v>
+        <v>2.52203579956662</v>
       </c>
       <c r="R30" t="n">
-        <v>1.70957026537626</v>
+        <v>1.7096026649541</v>
       </c>
       <c r="S30" t="n">
         <v>-0.6</v>
@@ -5945,13 +5942,13 @@
         <v>133</v>
       </c>
       <c r="K31" t="n">
-        <v>6.12633213818702</v>
+        <v>6.12248679130928</v>
       </c>
       <c r="L31" t="n">
-        <v>6.04600689196542</v>
+        <v>6.04016428096877</v>
       </c>
       <c r="M31" t="n">
-        <v>1.32856689806866</v>
+        <v>1.3629183994198</v>
       </c>
       <c r="N31" t="s">
         <v>72</v>
@@ -5963,10 +5960,10 @@
         <v>0.177927415938612</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.94425322778658</v>
+        <v>2.94330863742401</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91405792806834</v>
+        <v>1.91349851894023</v>
       </c>
       <c r="S31" t="n">
         <v>-0.9</v>
@@ -6093,13 +6090,13 @@
         <v>135</v>
       </c>
       <c r="K32" t="n">
-        <v>8.56870898969316</v>
+        <v>8.5723934273685</v>
       </c>
       <c r="L32" t="n">
-        <v>8.62352332499784</v>
+        <v>8.61460935481092</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.635637351913787</v>
+        <v>-0.490050398151176</v>
       </c>
       <c r="N32" t="s">
         <v>72</v>
@@ -6111,10 +6108,10 @@
         <v>0.169127302860132</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.90115873319744</v>
+        <v>3.90108050160262</v>
       </c>
       <c r="R32" t="n">
-        <v>2.39778847812132</v>
+        <v>2.39845270751017</v>
       </c>
       <c r="S32" t="n">
         <v>-1.4</v>
@@ -6241,13 +6238,13 @@
         <v>109</v>
       </c>
       <c r="K33" t="n">
-        <v>10.0170457114157</v>
+        <v>10.0185523076578</v>
       </c>
       <c r="L33" t="n">
-        <v>9.56913214046503</v>
+        <v>9.59299760191846</v>
       </c>
       <c r="M33" t="n">
-        <v>4.68081707281038</v>
+        <v>4.4360972805231</v>
       </c>
       <c r="N33" t="s">
         <v>72</v>
@@ -6259,10 +6256,10 @@
         <v>0.187331546657054</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.63137766651947</v>
+        <v>4.63176743405855</v>
       </c>
       <c r="R33" t="n">
-        <v>2.83236390711128</v>
+        <v>2.83242670933458</v>
       </c>
       <c r="S33" t="n">
         <v>-1.6</v>
@@ -6389,13 +6386,13 @@
         <v>138</v>
       </c>
       <c r="K34" t="n">
-        <v>18.6203338953234</v>
+        <v>18.6212489548736</v>
       </c>
       <c r="L34" t="n">
-        <v>24.1737974377568</v>
+        <v>24.0112845138055</v>
       </c>
       <c r="M34" t="n">
-        <v>-22.9730705601079</v>
+        <v>-22.4479267480793</v>
       </c>
       <c r="N34" t="s">
         <v>72</v>
@@ -6407,10 +6404,10 @@
         <v>0.165248842825829</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.12561721591229</v>
+        <v>8.13260599361066</v>
       </c>
       <c r="R34" t="n">
-        <v>4.62113084291253</v>
+        <v>4.62199023091303</v>
       </c>
       <c r="S34" t="n">
         <v>-2.3</v>
@@ -6539,13 +6536,13 @@
         <v>140</v>
       </c>
       <c r="K35" t="n">
-        <v>25.4889510674613</v>
+        <v>25.4936241603007</v>
       </c>
       <c r="L35" t="n">
-        <v>24.77260341838</v>
+        <v>24.553645961208</v>
       </c>
       <c r="M35" t="n">
-        <v>2.89169304082828</v>
+        <v>3.82826322647882</v>
       </c>
       <c r="N35" t="s">
         <v>72</v>
@@ -6557,10 +6554,10 @@
         <v>0.206074919470449</v>
       </c>
       <c r="Q35" t="n">
-        <v>11.7698818283758</v>
+        <v>11.7636255890235</v>
       </c>
       <c r="R35" t="n">
-        <v>6.97106796794476</v>
+        <v>6.97022608168457</v>
       </c>
       <c r="S35" t="n">
         <v>-3</v>
@@ -6689,13 +6686,13 @@
         <v>144</v>
       </c>
       <c r="K36" t="n">
-        <v>3.93743558636443</v>
+        <v>3.93759165739636</v>
       </c>
       <c r="L36" t="n">
-        <v>5.00465395586248</v>
+        <v>5.02729603378073</v>
       </c>
       <c r="M36" t="n">
-        <v>-21.3245187161824</v>
+        <v>-21.6757550990064</v>
       </c>
       <c r="N36" t="s">
         <v>72</v>
@@ -6707,10 +6704,10 @@
         <v>0.182781356519611</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.08894837155504</v>
+        <v>2.0891284610889</v>
       </c>
       <c r="R36" t="n">
-        <v>1.50767705664765</v>
+        <v>1.50778356036576</v>
       </c>
       <c r="S36" t="n">
         <v>0.4</v>
@@ -6839,13 +6836,13 @@
         <v>146</v>
       </c>
       <c r="K37" t="n">
-        <v>4.75375986000215</v>
+        <v>4.75390277358584</v>
       </c>
       <c r="L37" t="n">
         <v>4.19162580158431</v>
       </c>
       <c r="M37" t="n">
-        <v>13.410883629101</v>
+        <v>13.414293131534</v>
       </c>
       <c r="N37" t="s">
         <v>72</v>
@@ -6857,10 +6854,10 @@
         <v>0.19307677731308</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.41571808871404</v>
+        <v>2.41568395671871</v>
       </c>
       <c r="R37" t="n">
-        <v>1.66748856937106</v>
+        <v>1.66738605271046</v>
       </c>
       <c r="S37" t="n">
         <v>-0.4</v>
@@ -6989,13 +6986,13 @@
         <v>144</v>
       </c>
       <c r="K38" t="n">
-        <v>5.31778056481541</v>
+        <v>5.31623070891567</v>
       </c>
       <c r="L38" t="n">
-        <v>5.14365067119272</v>
+        <v>5.14523846272573</v>
       </c>
       <c r="M38" t="n">
-        <v>3.38533669477032</v>
+        <v>3.32331042436</v>
       </c>
       <c r="N38" t="s">
         <v>72</v>
@@ -7007,10 +7004,10 @@
         <v>0.183180270605474</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.63046530446445</v>
+        <v>2.62994406033485</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76443284326518</v>
+        <v>1.76408870365916</v>
       </c>
       <c r="S38" t="n">
         <v>-0.5</v>
@@ -7139,13 +7136,13 @@
         <v>109</v>
       </c>
       <c r="K39" t="n">
-        <v>8.60906834797147</v>
+        <v>8.61045611447648</v>
       </c>
       <c r="L39" t="n">
-        <v>7.86783101250885</v>
+        <v>7.85793981299599</v>
       </c>
       <c r="M39" t="n">
-        <v>9.42111408193878</v>
+        <v>9.57650884823435</v>
       </c>
       <c r="N39" t="s">
         <v>72</v>
@@ -7157,10 +7154,10 @@
         <v>0.206903293327624</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.12037651026395</v>
+        <v>4.12150786128175</v>
       </c>
       <c r="R39" t="n">
-        <v>2.61210742867631</v>
+        <v>2.61296255538259</v>
       </c>
       <c r="S39" t="n">
         <v>-1.3</v>
@@ -7287,13 +7284,13 @@
         <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>13.1673287888971</v>
+        <v>13.1739796913269</v>
       </c>
       <c r="L40" t="n">
-        <v>12.3756960772182</v>
+        <v>12.348191134708</v>
       </c>
       <c r="M40" t="n">
-        <v>6.39667220930071</v>
+        <v>6.68752651793496</v>
       </c>
       <c r="N40" t="s">
         <v>72</v>
@@ -7305,13 +7302,13 @@
         <v>0.240549762805754</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.45862460964493</v>
+        <v>6.46244153204828</v>
       </c>
       <c r="R40" t="n">
-        <v>4.07667031430523</v>
+        <v>4.07858162428322</v>
       </c>
       <c r="S40" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="T40" t="n">
         <v>100.990788297261</v>
@@ -7425,13 +7422,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="n">
-        <v>16.3777698495351</v>
+        <v>16.380366020989</v>
       </c>
       <c r="L41" t="n">
-        <v>14.2725845582988</v>
+        <v>14.1794980859209</v>
       </c>
       <c r="M41" t="n">
-        <v>14.7498533474243</v>
+        <v>15.5214798276488</v>
       </c>
       <c r="N41" t="s">
         <v>72</v>
@@ -7443,10 +7440,10 @@
         <v>0.188680487917574</v>
       </c>
       <c r="Q41" t="n">
-        <v>7.32297562029614</v>
+        <v>7.31580227217302</v>
       </c>
       <c r="R41" t="n">
-        <v>4.33497140109559</v>
+        <v>4.33294725801116</v>
       </c>
       <c r="S41" t="n">
         <v>-2.3</v>
@@ -7573,7 +7570,7 @@
         <v>152</v>
       </c>
       <c r="K42" t="n">
-        <v>18.8825261235783</v>
+        <v>18.8927990457424</v>
       </c>
       <c r="L42"/>
       <c r="M42"/>
@@ -7587,10 +7584,10 @@
         <v>0.239913505806157</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.19698483875913</v>
+        <v>9.20409114351636</v>
       </c>
       <c r="R42" t="n">
-        <v>5.69531972945867</v>
+        <v>5.69755950561625</v>
       </c>
       <c r="S42" t="n">
         <v>-2.6</v>
@@ -7699,7 +7696,7 @@
         <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>24.096452813073</v>
+        <v>24.0633414231785</v>
       </c>
       <c r="L43"/>
       <c r="M43"/>
@@ -7713,10 +7710,10 @@
         <v>0.239913505806157</v>
       </c>
       <c r="Q43" t="n">
-        <v>11.8542445172828</v>
+        <v>11.8446697834179</v>
       </c>
       <c r="R43" t="n">
-        <v>7.35977617981411</v>
+        <v>7.35431402779782</v>
       </c>
       <c r="S43" t="n">
         <v>-3.1</v>
@@ -7825,13 +7822,13 @@
         <v>158</v>
       </c>
       <c r="K44" t="n">
-        <v>3.10748399847623</v>
+        <v>3.1068844761815</v>
       </c>
       <c r="L44" t="n">
-        <v>3.65669677136276</v>
+        <v>3.64576573949182</v>
       </c>
       <c r="M44" t="n">
-        <v>-15.0193687698597</v>
+        <v>-14.7810172626569</v>
       </c>
       <c r="N44" t="s">
         <v>72</v>
@@ -7843,10 +7840,10 @@
         <v>0.181783576653451</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.7202285248984</v>
+        <v>1.72012153023849</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28695588056681</v>
+        <v>1.28682147984152</v>
       </c>
       <c r="S44" t="n">
         <v>0.5</v>
@@ -7975,13 +7972,13 @@
         <v>160</v>
       </c>
       <c r="K45" t="n">
-        <v>4.15011994075662</v>
+        <v>4.15053125403358</v>
       </c>
       <c r="L45" t="n">
-        <v>4.02847935548842</v>
+        <v>4.02361697847516</v>
       </c>
       <c r="M45" t="n">
-        <v>3.01951616315161</v>
+        <v>3.154233522658</v>
       </c>
       <c r="N45" t="s">
         <v>72</v>
@@ -7993,10 +7990,10 @@
         <v>0.164905344850108</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.05570951216516</v>
+        <v>2.05578917430325</v>
       </c>
       <c r="R45" t="n">
-        <v>1.40941302677083</v>
+        <v>1.40961665264194</v>
       </c>
       <c r="S45" t="n">
         <v>-0.5</v>
@@ -8125,13 +8122,13 @@
         <v>128</v>
       </c>
       <c r="K46" t="n">
-        <v>4.89763589584349</v>
+        <v>4.89857596219605</v>
       </c>
       <c r="L46" t="n">
-        <v>4.88768877376472</v>
+        <v>4.89534485290518</v>
       </c>
       <c r="M46" t="n">
-        <v>0.203513818886258</v>
+        <v>0.0660037114432965</v>
       </c>
       <c r="N46" t="s">
         <v>72</v>
@@ -8143,10 +8140,10 @@
         <v>0.202416532393919</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.41671419574573</v>
+        <v>2.41706329367436</v>
       </c>
       <c r="R46" t="n">
-        <v>1.58740596495245</v>
+        <v>1.58774474635067</v>
       </c>
       <c r="S46" t="n">
         <v>-0.7</v>
@@ -8273,13 +8270,13 @@
         <v>98</v>
       </c>
       <c r="K47" t="n">
-        <v>7.34335004413799</v>
+        <v>7.34186442166893</v>
       </c>
       <c r="L47" t="n">
-        <v>6.02923976608187</v>
+        <v>6.05112845646518</v>
       </c>
       <c r="M47" t="n">
-        <v>21.7956214886127</v>
+        <v>21.3305001619111</v>
       </c>
       <c r="N47" t="s">
         <v>72</v>
@@ -8291,10 +8288,10 @@
         <v>0.16210380204963</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.30319514592006</v>
+        <v>3.30192337573257</v>
       </c>
       <c r="R47" t="n">
-        <v>2.00175704786082</v>
+        <v>2.00125746101154</v>
       </c>
       <c r="S47" t="n">
         <v>-1.4</v>
@@ -8421,7 +8418,7 @@
         <v>69</v>
       </c>
       <c r="K48" t="n">
-        <v>20.0909910295569</v>
+        <v>20.0950095452481</v>
       </c>
       <c r="L48"/>
       <c r="M48"/>
@@ -8435,10 +8432,10 @@
         <v>0.223071305103427</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.24272123980334</v>
+        <v>9.24761609535713</v>
       </c>
       <c r="R48" t="n">
-        <v>5.35740255577944</v>
+        <v>5.35687262132407</v>
       </c>
       <c r="S48" t="n">
         <v>-2.8</v>
@@ -8547,13 +8544,13 @@
         <v>165</v>
       </c>
       <c r="K49" t="n">
-        <v>27.8152340391356</v>
+        <v>27.8390279737819</v>
       </c>
       <c r="L49" t="n">
-        <v>22.2089717965801</v>
+        <v>22.2386035134534</v>
       </c>
       <c r="M49" t="n">
-        <v>25.243231851998</v>
+        <v>25.1833459638799</v>
       </c>
       <c r="N49" t="s">
         <v>72</v>
@@ -8565,10 +8562,10 @@
         <v>0.193719264950183</v>
       </c>
       <c r="Q49" t="n">
-        <v>12.1730146883885</v>
+        <v>12.1724833259546</v>
       </c>
       <c r="R49" t="n">
-        <v>6.65031761186316</v>
+        <v>6.64881022584191</v>
       </c>
       <c r="S49" t="n">
         <v>-3.4</v>
@@ -8695,13 +8692,13 @@
         <v>131</v>
       </c>
       <c r="K50" t="n">
-        <v>89.6337469994524</v>
+        <v>89.5206832247388</v>
       </c>
       <c r="L50" t="n">
         <v>69.8860936408106</v>
       </c>
       <c r="M50" t="n">
-        <v>28.2569139722384</v>
+        <v>28.0951310354287</v>
       </c>
       <c r="N50" t="s">
         <v>72</v>
@@ -8713,10 +8710,10 @@
         <v>0.194648429324228</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.4204868331315</v>
+        <v>39.4523168595317</v>
       </c>
       <c r="R50" t="n">
-        <v>21.3168317266683</v>
+        <v>21.3266113481541</v>
       </c>
       <c r="S50" t="n">
         <v>-5.1</v>
@@ -8845,13 +8842,13 @@
         <v>170</v>
       </c>
       <c r="K51" t="n">
-        <v>3.51937070051067</v>
+        <v>3.52045963856133</v>
       </c>
       <c r="L51" t="n">
-        <v>3.98327159756243</v>
+        <v>4.00368309379879</v>
       </c>
       <c r="M51" t="n">
-        <v>-11.6462281240287</v>
+        <v>-12.069473130526</v>
       </c>
       <c r="N51" t="s">
         <v>72</v>
@@ -8863,10 +8860,10 @@
         <v>0.19467085849566</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.90819803685837</v>
+        <v>1.90868026442506</v>
       </c>
       <c r="R51" t="n">
-        <v>1.40610220049365</v>
+        <v>1.40620166601702</v>
       </c>
       <c r="S51" t="n">
         <v>0.3</v>
@@ -8993,13 +8990,13 @@
         <v>65</v>
       </c>
       <c r="K52" t="n">
-        <v>4.21164004487278</v>
+        <v>4.21060653765843</v>
       </c>
       <c r="L52" t="n">
-        <v>4.48486479214314</v>
+        <v>4.4909066415196</v>
       </c>
       <c r="M52" t="n">
-        <v>-6.09215126728038</v>
+        <v>-6.24150369258899</v>
       </c>
       <c r="N52" t="s">
         <v>87</v>
@@ -9011,10 +9008,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.18414034128443</v>
+        <v>2.18387664481536</v>
       </c>
       <c r="R52" t="n">
-        <v>1.53921743374233</v>
+        <v>1.53915453381457</v>
       </c>
       <c r="S52" t="n">
         <v>-0.3</v>
@@ -9141,13 +9138,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="n">
-        <v>5.87231571122325</v>
+        <v>5.87648900629423</v>
       </c>
       <c r="L53" t="n">
-        <v>6.76232334843465</v>
+        <v>6.74863351103313</v>
       </c>
       <c r="M53" t="n">
-        <v>-13.1612700451158</v>
+        <v>-12.9232755536815</v>
       </c>
       <c r="N53" t="s">
         <v>87</v>
@@ -9159,10 +9156,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.88527392880814</v>
+        <v>2.88625003200838</v>
       </c>
       <c r="R53" t="n">
-        <v>1.88847178472961</v>
+        <v>1.88944384698781</v>
       </c>
       <c r="S53" t="n">
         <v>-0.7</v>
@@ -9289,13 +9286,13 @@
         <v>174</v>
       </c>
       <c r="K54" t="n">
-        <v>9.40462598839339</v>
+        <v>9.40031503440937</v>
       </c>
       <c r="L54" t="n">
-        <v>7.39649434213446</v>
+        <v>7.37794171892291</v>
       </c>
       <c r="M54" t="n">
-        <v>27.1497760069865</v>
+        <v>27.4110774052266</v>
       </c>
       <c r="N54" t="s">
         <v>76</v>
@@ -9307,10 +9304,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.45474819734465</v>
+        <v>4.4521216468534</v>
       </c>
       <c r="R54" t="n">
-        <v>2.78104289121642</v>
+        <v>2.78014035324704</v>
       </c>
       <c r="S54" t="n">
         <v>-1.7</v>
@@ -9437,13 +9434,13 @@
         <v>128</v>
       </c>
       <c r="K55" t="n">
-        <v>9.65301703852826</v>
+        <v>9.64037921491493</v>
       </c>
       <c r="L55" t="n">
-        <v>7.82473984821219</v>
+        <v>7.76278817045719</v>
       </c>
       <c r="M55" t="n">
-        <v>23.3653415421063</v>
+        <v>24.1870704601123</v>
       </c>
       <c r="N55" t="s">
         <v>72</v>
@@ -9455,13 +9452,13 @@
         <v>0.185304474275342</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.47799187423455</v>
+        <v>4.47553831327623</v>
       </c>
       <c r="R55" t="n">
-        <v>2.75692871679468</v>
+        <v>2.75531268159047</v>
       </c>
       <c r="S55" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="T55" t="n">
         <v>104.677932400871</v>
@@ -9585,13 +9582,13 @@
         <v>128</v>
       </c>
       <c r="K56" t="n">
-        <v>15.1199271467743</v>
+        <v>15.124229402312</v>
       </c>
       <c r="L56" t="n">
-        <v>12.7773093139134</v>
+        <v>12.7805750798722</v>
       </c>
       <c r="M56" t="n">
-        <v>18.3342030415592</v>
+        <v>18.3376280628463</v>
       </c>
       <c r="N56" t="s">
         <v>72</v>
@@ -9603,10 +9600,10 @@
         <v>0.179912199615122</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.66051599946551</v>
+        <v>6.66384229201907</v>
       </c>
       <c r="R56" t="n">
-        <v>3.90713331479999</v>
+        <v>3.90795129859599</v>
       </c>
       <c r="S56" t="n">
         <v>-2.2</v>
@@ -9735,13 +9732,13 @@
         <v>178</v>
       </c>
       <c r="K57" t="n">
-        <v>61.2207671935579</v>
+        <v>61.263096015259</v>
       </c>
       <c r="L57" t="n">
-        <v>49.730482347091</v>
+        <v>49.7799900447984</v>
       </c>
       <c r="M57" t="n">
-        <v>23.1051144170916</v>
+        <v>23.0677144774972</v>
       </c>
       <c r="N57" t="s">
         <v>72</v>
@@ -9753,10 +9750,10 @@
         <v>0.186634124244702</v>
       </c>
       <c r="Q57" t="n">
-        <v>26.5753782287919</v>
+        <v>26.56388867274</v>
       </c>
       <c r="R57" t="n">
-        <v>14.8596238910836</v>
+        <v>14.8575959824851</v>
       </c>
       <c r="S57" t="n">
         <v>-4.3</v>
@@ -9883,13 +9880,13 @@
         <v>138</v>
       </c>
       <c r="K58" t="n">
-        <v>63.5602282509503</v>
+        <v>63.5760807873629</v>
       </c>
       <c r="L58" t="n">
-        <v>59.7776449491931</v>
+        <v>59.920910724985</v>
       </c>
       <c r="M58" t="n">
-        <v>6.32775564338837</v>
+        <v>6.09999083484192</v>
       </c>
       <c r="N58" t="s">
         <v>72</v>
@@ -9901,10 +9898,10 @@
         <v>0.185363151988665</v>
       </c>
       <c r="Q58" t="n">
-        <v>27.8160232315412</v>
+        <v>27.8174615134663</v>
       </c>
       <c r="R58" t="n">
-        <v>15.6088383023623</v>
+        <v>15.606136148274</v>
       </c>
       <c r="S58" t="n">
         <v>-4.2</v>
@@ -10033,13 +10030,13 @@
         <v>184</v>
       </c>
       <c r="K59" t="n">
-        <v>2.81050220168554</v>
+        <v>2.8109521843072</v>
       </c>
       <c r="L59" t="n">
-        <v>2.97327188940092</v>
+        <v>2.97840783869911</v>
       </c>
       <c r="M59" t="n">
-        <v>-5.47442998050807</v>
+        <v>-5.62232116824708</v>
       </c>
       <c r="N59" t="s">
         <v>72</v>
@@ -10051,10 +10048,10 @@
         <v>0.165332410304714</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.61593037276543</v>
+        <v>1.61614911944404</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24947916892349</v>
+        <v>1.24965120314711</v>
       </c>
       <c r="S59" t="n">
         <v>0.6</v>
@@ -10183,13 +10180,13 @@
         <v>186</v>
       </c>
       <c r="K60" t="n">
-        <v>4.76734982690631</v>
+        <v>4.7695848361106</v>
       </c>
       <c r="L60" t="n">
-        <v>5.72476959184842</v>
+        <v>5.73067445991634</v>
       </c>
       <c r="M60" t="n">
-        <v>-16.7241624240282</v>
+        <v>-16.7709687669079</v>
       </c>
       <c r="N60" t="s">
         <v>72</v>
@@ -10201,10 +10198,10 @@
         <v>0.175285242181235</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.33877369615997</v>
+        <v>2.33959924680473</v>
       </c>
       <c r="R60" t="n">
-        <v>1.58068686610542</v>
+        <v>1.58093938733828</v>
       </c>
       <c r="S60" t="n">
         <v>-0.6</v>
@@ -10333,13 +10330,13 @@
         <v>178</v>
       </c>
       <c r="K61" t="n">
-        <v>5.53040578536637</v>
+        <v>5.52950159488132</v>
       </c>
       <c r="L61" t="n">
-        <v>5.95238378667936</v>
+        <v>5.95096697411485</v>
       </c>
       <c r="M61" t="n">
-        <v>-7.08922704643679</v>
+        <v>-7.08230075997383</v>
       </c>
       <c r="N61" t="s">
         <v>72</v>
@@ -10351,10 +10348,10 @@
         <v>0.169331339660101</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.62992637923552</v>
+        <v>2.62964402893857</v>
       </c>
       <c r="R61" t="n">
-        <v>1.70569643337942</v>
+        <v>1.70531258691017</v>
       </c>
       <c r="S61" t="n">
         <v>-0.9</v>
@@ -10483,13 +10480,13 @@
         <v>189</v>
       </c>
       <c r="K62" t="n">
-        <v>10.6355862046406</v>
+        <v>10.620779170522</v>
       </c>
       <c r="L62" t="n">
-        <v>8.46289244309046</v>
+        <v>8.41164101270082</v>
       </c>
       <c r="M62" t="n">
-        <v>25.6731817893304</v>
+        <v>26.2628677862692</v>
       </c>
       <c r="N62" t="s">
         <v>72</v>
@@ -10501,10 +10498,10 @@
         <v>0.15651704457591</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.71055205656723</v>
+        <v>4.70391152728274</v>
       </c>
       <c r="R62" t="n">
-        <v>2.77577988749165</v>
+        <v>2.77496698055925</v>
       </c>
       <c r="S62" t="n">
         <v>-2</v>
@@ -10631,13 +10628,13 @@
         <v>98</v>
       </c>
       <c r="K63" t="n">
-        <v>11.949159155491</v>
+        <v>11.9462969205645</v>
       </c>
       <c r="L63" t="n">
-        <v>9.71403593977659</v>
+        <v>9.70084392278591</v>
       </c>
       <c r="M63" t="n">
-        <v>23.0092129530027</v>
+        <v>23.1469861349316</v>
       </c>
       <c r="N63" t="s">
         <v>72</v>
@@ -10649,10 +10646,10 @@
         <v>0.152260572340975</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.21658513567557</v>
+        <v>5.21432569255141</v>
       </c>
       <c r="R63" t="n">
-        <v>3.02833529123943</v>
+        <v>3.02705383766781</v>
       </c>
       <c r="S63" t="n">
         <v>-2.2</v>
@@ -10779,13 +10776,13 @@
         <v>119</v>
       </c>
       <c r="K64" t="n">
-        <v>13.1750334851859</v>
+        <v>13.1794528755032</v>
       </c>
       <c r="L64" t="n">
-        <v>10.0116127740515</v>
+        <v>10.025664160401</v>
       </c>
       <c r="M64" t="n">
-        <v>31.5975136327042</v>
+        <v>31.457155003844</v>
       </c>
       <c r="N64" t="s">
         <v>72</v>
@@ -10797,10 +10794,10 @@
         <v>0.16915966966937</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.90449331509716</v>
+        <v>5.91108795484046</v>
       </c>
       <c r="R64" t="n">
-        <v>3.44488053743537</v>
+        <v>3.44685233820473</v>
       </c>
       <c r="S64" t="n">
         <v>-2.4</v>
@@ -10927,13 +10924,13 @@
         <v>158</v>
       </c>
       <c r="K65" t="n">
-        <v>2.61250181106024</v>
+        <v>2.61345140839034</v>
       </c>
       <c r="L65" t="n">
-        <v>2.9466984884646</v>
+        <v>2.94426943798393</v>
       </c>
       <c r="M65" t="n">
-        <v>-11.3413937229285</v>
+        <v>-11.2359971314348</v>
       </c>
       <c r="N65" t="s">
         <v>87</v>
@@ -10945,10 +10942,10 @@
         <v>0.200056801394905</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.4989227829422</v>
+        <v>1.49909340035418</v>
       </c>
       <c r="R65" t="n">
-        <v>1.20142477454455</v>
+        <v>1.20140967120381</v>
       </c>
       <c r="S65" t="n">
         <v>0.3</v>
@@ -11075,13 +11072,13 @@
         <v>65</v>
       </c>
       <c r="K66" t="n">
-        <v>3.20243159824429</v>
+        <v>3.2005043311507</v>
       </c>
       <c r="L66" t="n">
-        <v>3.28768204082974</v>
+        <v>3.28724977812839</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.59302577094541</v>
+        <v>-2.63884562575215</v>
       </c>
       <c r="N66" t="s">
         <v>72</v>
@@ -11093,10 +11090,10 @@
         <v>0.204075782482982</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.66813073735846</v>
+        <v>1.66758216171773</v>
       </c>
       <c r="R66" t="n">
-        <v>1.26847514866947</v>
+        <v>1.26821813094542</v>
       </c>
       <c r="S66" t="n">
         <v>-0.3</v>
@@ -11225,13 +11222,13 @@
         <v>197</v>
       </c>
       <c r="K67" t="n">
-        <v>12.0864189011847</v>
+        <v>12.0792604497879</v>
       </c>
       <c r="L67" t="n">
-        <v>10.7040565128974</v>
+        <v>10.6971868649053</v>
       </c>
       <c r="M67" t="n">
-        <v>12.9143786434776</v>
+        <v>12.9199723472788</v>
       </c>
       <c r="N67" t="s">
         <v>72</v>
@@ -11243,10 +11240,10 @@
         <v>0.176874647064087</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.06105324765526</v>
+        <v>5.05960490509439</v>
       </c>
       <c r="R67" t="n">
-        <v>2.7253072245759</v>
+        <v>2.72498367812946</v>
       </c>
       <c r="S67" t="n">
         <v>-2.3</v>
@@ -11375,13 +11372,13 @@
         <v>133</v>
       </c>
       <c r="K68" t="n">
-        <v>15.7914626832629</v>
+        <v>15.7874233562349</v>
       </c>
       <c r="L68" t="n">
-        <v>12.7903824018417</v>
+        <v>12.7707827863619</v>
       </c>
       <c r="M68" t="n">
-        <v>23.4635696348617</v>
+        <v>23.6214225888688</v>
       </c>
       <c r="N68" t="s">
         <v>72</v>
@@ -11393,10 +11390,10 @@
         <v>0.193308968305331</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.63165584275302</v>
+        <v>6.62639040931285</v>
       </c>
       <c r="R68" t="n">
-        <v>3.56479686565746</v>
+        <v>3.56213021213569</v>
       </c>
       <c r="S68" t="n">
         <v>-2.7</v>
@@ -11525,13 +11522,13 @@
         <v>178</v>
       </c>
       <c r="K69" t="n">
-        <v>17.1132095361183</v>
+        <v>17.1252213715053</v>
       </c>
       <c r="L69" t="n">
-        <v>14.3298466829059</v>
+        <v>14.3627746660922</v>
       </c>
       <c r="M69" t="n">
-        <v>19.423535469732</v>
+        <v>19.2333777395723</v>
       </c>
       <c r="N69" t="s">
         <v>72</v>
@@ -11543,10 +11540,10 @@
         <v>0.187308054133596</v>
       </c>
       <c r="Q69" t="n">
-        <v>7.08277921773334</v>
+        <v>7.08655084406901</v>
       </c>
       <c r="R69" t="n">
-        <v>3.78510768242019</v>
+        <v>3.78565910146882</v>
       </c>
       <c r="S69" t="n">
         <v>-2.8</v>
@@ -11675,13 +11672,13 @@
         <v>107</v>
       </c>
       <c r="K70" t="n">
-        <v>17.7349381203695</v>
+        <v>17.7366606574657</v>
       </c>
       <c r="L70" t="n">
-        <v>18.7245834113462</v>
+        <v>18.7597073719752</v>
       </c>
       <c r="M70" t="n">
-        <v>-5.28527267729247</v>
+        <v>-5.45342576098957</v>
       </c>
       <c r="N70" t="s">
         <v>72</v>
@@ -11693,10 +11690,10 @@
         <v>0.201523936890671</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.47945550184692</v>
+        <v>7.47889006262495</v>
       </c>
       <c r="R70" t="n">
-        <v>3.93353379334898</v>
+        <v>3.93397608342196</v>
       </c>
       <c r="S70" t="n">
         <v>-2.7</v>
@@ -11825,13 +11822,13 @@
         <v>135</v>
       </c>
       <c r="K71" t="n">
-        <v>26.8913219337702</v>
+        <v>26.9422294548463</v>
       </c>
       <c r="L71" t="n">
-        <v>19.854675402025</v>
+        <v>19.9497307001795</v>
       </c>
       <c r="M71" t="n">
-        <v>35.4407533201351</v>
+        <v>35.0505922097677</v>
       </c>
       <c r="N71" t="s">
         <v>72</v>
@@ -11843,10 +11840,10 @@
         <v>0.176808714571014</v>
       </c>
       <c r="Q71" t="n">
-        <v>10.6405409936831</v>
+        <v>10.6667283323929</v>
       </c>
       <c r="R71" t="n">
-        <v>5.472640563229</v>
+        <v>5.48292504330238</v>
       </c>
       <c r="S71" t="n">
         <v>-3.6</v>
@@ -11973,13 +11970,13 @@
         <v>203</v>
       </c>
       <c r="K72" t="n">
-        <v>145.083301249066</v>
+        <v>145.029922719217</v>
       </c>
       <c r="L72" t="n">
         <v>88.4244031830239</v>
       </c>
       <c r="M72" t="n">
-        <v>64.0760876256837</v>
+        <v>64.015721337727</v>
       </c>
       <c r="N72" t="s">
         <v>72</v>
@@ -11991,10 +11988,10 @@
         <v>0.204477307697909</v>
       </c>
       <c r="Q72" t="n">
-        <v>61.9796619040947</v>
+        <v>61.9869481876659</v>
       </c>
       <c r="R72" t="n">
-        <v>32.5626384006225</v>
+        <v>32.5774770478332</v>
       </c>
       <c r="S72" t="n">
         <v>-6.3</v>
@@ -12121,13 +12118,13 @@
         <v>71</v>
       </c>
       <c r="K73" t="n">
-        <v>1.42568764365249</v>
+        <v>1.42576254697926</v>
       </c>
       <c r="L73" t="n">
-        <v>1.5091674589162</v>
+        <v>1.51067204422894</v>
       </c>
       <c r="M73" t="n">
-        <v>-5.53151439692878</v>
+        <v>-5.62064397590775</v>
       </c>
       <c r="N73" t="s">
         <v>72</v>
@@ -12139,10 +12136,10 @@
         <v>0.186486154555426</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.11758563209266</v>
+        <v>1.11773363039239</v>
       </c>
       <c r="R73" t="n">
-        <v>1.05067551502925</v>
+        <v>1.05076625241576</v>
       </c>
       <c r="S73" t="n">
         <v>3.7</v>
@@ -12271,13 +12268,13 @@
         <v>207</v>
       </c>
       <c r="K74" t="n">
-        <v>14.4715562789762</v>
+        <v>14.4563064562216</v>
       </c>
       <c r="L74" t="n">
-        <v>12.5370440015043</v>
+        <v>12.4434490481523</v>
       </c>
       <c r="M74" t="n">
-        <v>15.4303700077926</v>
+        <v>16.1760409053805</v>
       </c>
       <c r="N74" t="s">
         <v>72</v>
@@ -12289,10 +12286,10 @@
         <v>0.196897477500637</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.80590079731766</v>
+        <v>3.80662754715138</v>
       </c>
       <c r="R74" t="n">
-        <v>2.13338817700755</v>
+        <v>2.13377802582125</v>
       </c>
       <c r="S74" t="n">
         <v>-3.7</v>
@@ -12421,13 +12418,13 @@
         <v>135</v>
       </c>
       <c r="K75" t="n">
-        <v>15.5179964950957</v>
+        <v>15.5279408296291</v>
       </c>
       <c r="L75" t="n">
-        <v>13.2478473970062</v>
+        <v>13.2513581555585</v>
       </c>
       <c r="M75" t="n">
-        <v>17.1359846627047</v>
+        <v>17.1799950416076</v>
       </c>
       <c r="N75" t="s">
         <v>72</v>
@@ -12439,10 +12436,10 @@
         <v>0.179917480381816</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.00714957693747</v>
+        <v>4.00621232358298</v>
       </c>
       <c r="R75" t="n">
-        <v>2.19484550679278</v>
+        <v>2.19430547321047</v>
       </c>
       <c r="S75" t="n">
         <v>-3.8</v>
@@ -12569,7 +12566,7 @@
         <v>146</v>
       </c>
       <c r="K76" t="n">
-        <v>18.1588047397249</v>
+        <v>18.1386638846393</v>
       </c>
       <c r="L76"/>
       <c r="M76"/>
@@ -12583,10 +12580,10 @@
         <v>0.242473165911646</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.24669529846235</v>
+        <v>5.2442143427743</v>
       </c>
       <c r="R76" t="n">
-        <v>2.88190473823281</v>
+        <v>2.88166811718963</v>
       </c>
       <c r="S76" t="n">
         <v>-4.1</v>
@@ -12695,13 +12692,13 @@
         <v>211</v>
       </c>
       <c r="K77" t="n">
-        <v>18.9666375166154</v>
+        <v>18.9857037836858</v>
       </c>
       <c r="L77" t="n">
-        <v>15.0818881013422</v>
+        <v>15.090991398823</v>
       </c>
       <c r="M77" t="n">
-        <v>25.757712755656</v>
+        <v>25.8081943189401</v>
       </c>
       <c r="N77" t="s">
         <v>72</v>
@@ -12713,10 +12710,10 @@
         <v>0.186040305258737</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.070159866877</v>
+        <v>5.07024672913352</v>
       </c>
       <c r="R77" t="n">
-        <v>2.69716248581431</v>
+        <v>2.69671980164843</v>
       </c>
       <c r="S77" t="n">
         <v>-4.2</v>
@@ -12845,13 +12842,13 @@
         <v>213</v>
       </c>
       <c r="K78" t="n">
-        <v>29.7292249842517</v>
+        <v>29.7338649247341</v>
       </c>
       <c r="L78" t="n">
-        <v>25.2609244758777</v>
+        <v>25.2481696541277</v>
       </c>
       <c r="M78" t="n">
-        <v>17.6885866257225</v>
+        <v>17.7664176534595</v>
       </c>
       <c r="N78" t="s">
         <v>72</v>
@@ -12863,10 +12860,10 @@
         <v>0.185498016566022</v>
       </c>
       <c r="Q78" t="n">
-        <v>7.91003281367375</v>
+        <v>7.91022394447439</v>
       </c>
       <c r="R78" t="n">
-        <v>4.00517352356035</v>
+        <v>4.00495589855957</v>
       </c>
       <c r="S78" t="n">
         <v>-4.9</v>
@@ -12993,13 +12990,13 @@
         <v>133</v>
       </c>
       <c r="K79" t="n">
-        <v>60.9579298629431</v>
+        <v>60.9389190215425</v>
       </c>
       <c r="L79" t="n">
-        <v>58.110400929692</v>
+        <v>57.9085118702953</v>
       </c>
       <c r="M79" t="n">
-        <v>4.90020527770292</v>
+        <v>5.23309450264373</v>
       </c>
       <c r="N79" t="s">
         <v>72</v>
@@ -13011,10 +13008,10 @@
         <v>0.218708528504461</v>
       </c>
       <c r="Q79" t="n">
-        <v>18.1533328687357</v>
+        <v>18.1375915823205</v>
       </c>
       <c r="R79" t="n">
-        <v>9.23881713158701</v>
+        <v>9.24159276038776</v>
       </c>
       <c r="S79" t="n">
         <v>-6.1</v>
@@ -13143,13 +13140,13 @@
         <v>104</v>
       </c>
       <c r="K80" t="n">
-        <v>138.770226641641</v>
+        <v>138.825030913702</v>
       </c>
       <c r="L80" t="n">
         <v>131.762845849802</v>
       </c>
       <c r="M80" t="n">
-        <v>5.31817656687987</v>
+        <v>5.35976968192557</v>
       </c>
       <c r="N80" t="s">
         <v>72</v>
@@ -13161,10 +13158,10 @@
         <v>0.195302281898581</v>
       </c>
       <c r="Q80" t="n">
-        <v>42.4204930523957</v>
+        <v>42.4588293048347</v>
       </c>
       <c r="R80" t="n">
-        <v>20.7418533991266</v>
+        <v>20.7481858688355</v>
       </c>
       <c r="S80" t="n">
         <v>-7.7</v>
@@ -13291,13 +13288,13 @@
         <v>146</v>
       </c>
       <c r="K81" t="n">
-        <v>3.26023336542828</v>
+        <v>3.25976824275553</v>
       </c>
       <c r="L81" t="n">
-        <v>3.66098034191163</v>
+        <v>3.66312589282444</v>
       </c>
       <c r="M81" t="n">
-        <v>-10.9464389058723</v>
+        <v>-11.0112964137823</v>
       </c>
       <c r="N81" t="s">
         <v>72</v>
@@ -13309,10 +13306,10 @@
         <v>0.191305642174389</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.82274160229602</v>
+        <v>1.82248622515463</v>
       </c>
       <c r="R81" t="n">
-        <v>1.36634884087988</v>
+        <v>1.36618621226784</v>
       </c>
       <c r="S81" t="n">
         <v>0.5</v>
@@ -13441,13 +13438,13 @@
         <v>65</v>
       </c>
       <c r="K82" t="n">
-        <v>4.60518026234466</v>
+        <v>4.60579601276758</v>
       </c>
       <c r="L82" t="n">
-        <v>4.74619144796165</v>
+        <v>4.75657550535077</v>
       </c>
       <c r="M82" t="n">
-        <v>-2.97103871942537</v>
+        <v>-3.16991693737607</v>
       </c>
       <c r="N82" t="s">
         <v>72</v>
@@ -13459,10 +13456,10 @@
         <v>0.195837315289254</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.34965851080151</v>
+        <v>2.3494075767166</v>
       </c>
       <c r="R82" t="n">
-        <v>1.62636466371309</v>
+        <v>1.62656304490083</v>
       </c>
       <c r="S82" t="n">
         <v>-0.5</v>
@@ -13589,13 +13586,13 @@
         <v>104</v>
       </c>
       <c r="K83" t="n">
-        <v>6.26860830615637</v>
+        <v>6.2733900278677</v>
       </c>
       <c r="L83" t="n">
-        <v>5.55316786051419</v>
+        <v>5.55501860800978</v>
       </c>
       <c r="M83" t="n">
-        <v>12.88346514301</v>
+        <v>12.9319354362217</v>
       </c>
       <c r="N83" t="s">
         <v>72</v>
@@ -13607,13 +13604,13 @@
         <v>0.183952932417733</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.02275169971118</v>
+        <v>3.02439782543252</v>
       </c>
       <c r="R83" t="n">
-        <v>1.96878183584156</v>
+        <v>1.96957867717729</v>
       </c>
       <c r="S83" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="T83" t="n">
         <v>105.658343200874</v>
@@ -13737,13 +13734,13 @@
         <v>121</v>
       </c>
       <c r="K84" t="n">
-        <v>7.31885745743246</v>
+        <v>7.31440774195679</v>
       </c>
       <c r="L84" t="n">
-        <v>6.51893618408187</v>
+        <v>6.48932580624229</v>
       </c>
       <c r="M84" t="n">
-        <v>12.2707333031401</v>
+        <v>12.7144476999571</v>
       </c>
       <c r="N84" t="s">
         <v>72</v>
@@ -13755,10 +13752,10 @@
         <v>0.182998837599141</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.45290730342232</v>
+        <v>3.4525064594264</v>
       </c>
       <c r="R84" t="n">
-        <v>2.19621416066072</v>
+        <v>2.19610382756051</v>
       </c>
       <c r="S84" t="n">
         <v>-1.3</v>
@@ -13885,13 +13882,13 @@
         <v>189</v>
       </c>
       <c r="K85" t="n">
-        <v>11.0432042239065</v>
+        <v>11.037133029547</v>
       </c>
       <c r="L85" t="n">
-        <v>8.67137778548513</v>
+        <v>8.65786511990304</v>
       </c>
       <c r="M85" t="n">
-        <v>27.3523596491384</v>
+        <v>27.480999954301</v>
       </c>
       <c r="N85" t="s">
         <v>72</v>
@@ -13903,10 +13900,10 @@
         <v>0.159247618432818</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.89682218560636</v>
+        <v>4.89592216369355</v>
       </c>
       <c r="R85" t="n">
-        <v>2.9310014518891</v>
+        <v>2.9296446609747</v>
       </c>
       <c r="S85" t="n">
         <v>-1.9</v>
@@ -14033,13 +14030,13 @@
         <v>223</v>
       </c>
       <c r="K86" t="n">
-        <v>16.6280023409634</v>
+        <v>16.6261599295867</v>
       </c>
       <c r="L86" t="n">
-        <v>22.7858282068808</v>
+        <v>22.8378625256908</v>
       </c>
       <c r="M86" t="n">
-        <v>-27.0248059890923</v>
+        <v>-27.1991417284188</v>
       </c>
       <c r="N86" t="s">
         <v>72</v>
@@ -14051,10 +14048,10 @@
         <v>0.181921231719556</v>
       </c>
       <c r="Q86" t="n">
-        <v>7.4200224160809</v>
+        <v>7.41816814524963</v>
       </c>
       <c r="R86" t="n">
-        <v>4.33673977240522</v>
+        <v>4.33641810140672</v>
       </c>
       <c r="S86" t="n">
         <v>-2.1</v>
@@ -14183,13 +14180,13 @@
         <v>133</v>
       </c>
       <c r="K87" t="n">
-        <v>34.158381593448</v>
+        <v>34.1966220505981</v>
       </c>
       <c r="L87" t="n">
-        <v>42.6105666808692</v>
+        <v>42.7928968763372</v>
       </c>
       <c r="M87" t="n">
-        <v>-19.8358898878854</v>
+        <v>-20.0880881015852</v>
       </c>
       <c r="N87" t="s">
         <v>72</v>
@@ -14201,10 +14198,10 @@
         <v>0.170352817282645</v>
       </c>
       <c r="Q87" t="n">
-        <v>15.068829030837</v>
+        <v>15.0795370963412</v>
       </c>
       <c r="R87" t="n">
-        <v>8.45818665383946</v>
+        <v>8.45851754155013</v>
       </c>
       <c r="S87" t="n">
         <v>-3.1</v>
@@ -18931,28 +18928,28 @@
         <v>291</v>
       </c>
       <c r="K120" t="n">
-        <v>2.41853704994452</v>
+        <v>1.81901005451654</v>
       </c>
       <c r="L120" t="n">
-        <v>3.05619900375882</v>
+        <v>2.17507992779312</v>
       </c>
       <c r="M120" t="n">
-        <v>-20.8645429512294</v>
+        <v>-16.3704270692186</v>
       </c>
       <c r="N120" t="s">
         <v>72</v>
       </c>
       <c r="O120" t="n">
-        <v>0.214643316740399</v>
+        <v>0.218725735639998</v>
       </c>
       <c r="P120" t="n">
-        <v>0.2150378301614</v>
+        <v>0.219127752528009</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.45919672373068</v>
+        <v>1.20995661257853</v>
       </c>
       <c r="R120" t="n">
-        <v>1.18288323529519</v>
+        <v>1.07610033299256</v>
       </c>
       <c r="S120" t="n">
         <v>1.3</v>
@@ -19072,7 +19069,7 @@
         <v>126</v>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I121" t="s">
         <v>292</v>
@@ -19081,85 +19078,85 @@
         <v>293</v>
       </c>
       <c r="K121" t="n">
-        <v>5.38104154804863</v>
+        <v>4.23381389247458</v>
       </c>
       <c r="L121" t="n">
-        <v>4.65261688764829</v>
+        <v>4.0609087586795</v>
       </c>
       <c r="M121" t="n">
-        <v>15.6562355764592</v>
+        <v>4.25779410644298</v>
       </c>
       <c r="N121" t="s">
         <v>72</v>
       </c>
       <c r="O121" t="n">
-        <v>0.228089782950901</v>
+        <v>0.219526813034275</v>
       </c>
       <c r="P121" t="n">
-        <v>0.228509010914454</v>
+        <v>0.219930302298823</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.48494530752078</v>
+        <v>1.70186439257116</v>
       </c>
       <c r="R121" t="n">
-        <v>1.6164025091129</v>
+        <v>1.24640369903518</v>
       </c>
       <c r="S121" t="n">
         <v>-1.3</v>
       </c>
       <c r="T121" t="n">
-        <v>103.605545947297</v>
+        <v>101.255844892457</v>
       </c>
       <c r="U121" t="n">
-        <v>103.605545947297</v>
+        <v>104.077119217106</v>
       </c>
       <c r="V121" t="n">
-        <v>103.964099392494</v>
+        <v>104.199082826953</v>
       </c>
       <c r="W121" t="n">
-        <v>103.130133501371</v>
+        <v>105.018947433678</v>
       </c>
       <c r="X121" t="n">
-        <v>95.1131881159502</v>
+        <v>100.736880385705</v>
       </c>
       <c r="Y121" t="n">
-        <v>103.642456724651</v>
+        <v>105.048142128313</v>
       </c>
       <c r="Z121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AA121" t="n">
-        <v>103.669753494035</v>
+        <v>105.048142128313</v>
       </c>
       <c r="AB121" t="n">
-        <v>103.341643187035</v>
+        <v>104.077119217106</v>
       </c>
       <c r="AC121" t="n">
-        <v>103.341643187035</v>
+        <v>104.323107043656</v>
       </c>
       <c r="AD121" t="n">
-        <v>103.341643187035</v>
+        <v>108.266260597671</v>
       </c>
       <c r="AE121" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AF121" t="n">
-        <v>217</v>
+        <v>98</v>
       </c>
       <c r="AG121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AH121" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI121" t="n">
         <v>10</v>
       </c>
-      <c r="AI121" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ121" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="AK121" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
@@ -19222,7 +19219,7 @@
         <v>126</v>
       </c>
       <c r="H122" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I122" t="s">
         <v>294</v>
@@ -19231,85 +19228,75 @@
         <v>295</v>
       </c>
       <c r="K122" t="n">
-        <v>5.7601428357267</v>
+        <v>16.5138304335828</v>
       </c>
       <c r="L122" t="n">
-        <v>6.01407180227314</v>
+        <v>12.8231824592897</v>
       </c>
       <c r="M122" t="n">
-        <v>-4.22224700494025</v>
+        <v>28.7810610666272</v>
       </c>
       <c r="N122" t="s">
         <v>72</v>
       </c>
       <c r="O122" t="n">
-        <v>0.215429442380211</v>
+        <v>0.268895322062865</v>
       </c>
       <c r="P122" t="n">
-        <v>0.215825400696493</v>
+        <v>0.250173595419795</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.59604976675609</v>
+        <v>6.32000870318953</v>
       </c>
       <c r="R122" t="n">
-        <v>1.65282397205083</v>
+        <v>3.04013960851606</v>
       </c>
       <c r="S122" t="n">
-        <v>-1.3</v>
+        <v>-3.4</v>
       </c>
       <c r="T122" t="n">
-        <v>101.255844892457</v>
+        <v>102.179892912761</v>
       </c>
       <c r="U122" t="n">
-        <v>104.077119217106</v>
+        <v>101.602636510187</v>
       </c>
       <c r="V122" t="n">
-        <v>104.199082826953</v>
+        <v>100.102187043833</v>
       </c>
       <c r="W122" t="n">
-        <v>105.018947433678</v>
+        <v>101.323096565154</v>
       </c>
       <c r="X122" t="n">
-        <v>100.736880385705</v>
+        <v>100.881699689764</v>
       </c>
       <c r="Y122" t="n">
-        <v>105.048142128313</v>
+        <v>100.67212219852</v>
       </c>
       <c r="Z122" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>105.048142128313</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>104.077119217106</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>104.323107043656</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>108.266260597671</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AA122"/>
+      <c r="AB122"/>
+      <c r="AC122"/>
+      <c r="AD122"/>
       <c r="AE122" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>98</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF122"/>
       <c r="AG122" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AH122" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AI122" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AK122" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
@@ -19324,7 +19311,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ122" t="s">
         <v>129</v>
@@ -19372,88 +19359,88 @@
         <v>126</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I123" t="s">
         <v>296</v>
       </c>
       <c r="J123" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="K123" t="n">
-        <v>9.42907747013126</v>
+        <v>24.6013240801013</v>
       </c>
       <c r="L123" t="n">
-        <v>7.30251916757941</v>
+        <v>18.6199962762986</v>
       </c>
       <c r="M123" t="n">
-        <v>29.120886282545</v>
+        <v>32.1231417828813</v>
       </c>
       <c r="N123" t="s">
         <v>72</v>
       </c>
       <c r="O123" t="n">
-        <v>0.220734265627762</v>
+        <v>0.200052394741294</v>
       </c>
       <c r="P123" t="n">
-        <v>0.208332392121718</v>
+        <v>0.20042009011531</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.13875764291549</v>
+        <v>8.53931987708725</v>
       </c>
       <c r="R123" t="n">
-        <v>2.45308652390068</v>
+        <v>3.81597218128006</v>
       </c>
       <c r="S123" t="n">
-        <v>-2.3</v>
+        <v>-3.8</v>
       </c>
       <c r="T123" t="n">
-        <v>104.558982642207</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="U123" t="n">
-        <v>102.817771556793</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="V123" t="n">
-        <v>99.2301332394831</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="W123" t="n">
-        <v>103.083419603713</v>
+        <v>103.101668230153</v>
       </c>
       <c r="X123" t="n">
-        <v>98.5428857453734</v>
+        <v>98.0982391540476</v>
       </c>
       <c r="Y123" t="n">
-        <v>99.8125817462865</v>
+        <v>97.3164565383449</v>
       </c>
       <c r="Z123" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AA123" t="n">
-        <v>99.2301332394831</v>
+        <v>98.5119400345742</v>
       </c>
       <c r="AB123" t="n">
-        <v>99.2301332394831</v>
+        <v>100.65610265142</v>
       </c>
       <c r="AC123" t="n">
-        <v>99.2301332394831</v>
+        <v>98.4265179639656</v>
       </c>
       <c r="AD123" t="n">
-        <v>99.2301332394831</v>
+        <v>100.839894696788</v>
       </c>
       <c r="AE123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AF123" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AG123" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AH123" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AI123" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AJ123" t="n">
         <v>17</v>
@@ -19522,61 +19509,61 @@
         <v>126</v>
       </c>
       <c r="H124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I124" t="s">
         <v>297</v>
       </c>
       <c r="J124" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="K124" t="n">
-        <v>22.8286113551675</v>
+        <v>26.5571979155157</v>
       </c>
       <c r="L124" t="n">
-        <v>19.0165430690245</v>
+        <v>15.3175065094195</v>
       </c>
       <c r="M124" t="n">
-        <v>20.0460634317515</v>
+        <v>73.3780749444064</v>
       </c>
       <c r="N124" t="s">
         <v>72</v>
       </c>
       <c r="O124" t="n">
-        <v>0.263876510071714</v>
+        <v>0.268376028428921</v>
       </c>
       <c r="P124" t="n">
-        <v>0.245504216157523</v>
+        <v>0.249690457392381</v>
       </c>
       <c r="Q124" t="n">
-        <v>9.93141013749459</v>
+        <v>10.6459526841878</v>
       </c>
       <c r="R124" t="n">
-        <v>5.60488802939449</v>
+        <v>5.36000863038986</v>
       </c>
       <c r="S124" t="n">
-        <v>-3.5</v>
+        <v>-4.7</v>
       </c>
       <c r="T124" t="n">
-        <v>102.179892912761</v>
+        <v>94.7166875566949</v>
       </c>
       <c r="U124" t="n">
-        <v>101.602636510187</v>
+        <v>95.8145063799703</v>
       </c>
       <c r="V124" t="n">
-        <v>100.102187043833</v>
+        <v>95.8145063799703</v>
       </c>
       <c r="W124" t="n">
-        <v>101.323096565154</v>
+        <v>102.22962505915</v>
       </c>
       <c r="X124" t="n">
-        <v>100.881699689764</v>
+        <v>98.4541869098614</v>
       </c>
       <c r="Y124" t="n">
-        <v>100.67212219852</v>
+        <v>96.8376420433072</v>
       </c>
       <c r="Z124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA124"/>
       <c r="AB124"/>
@@ -19587,19 +19574,19 @@
       </c>
       <c r="AF124"/>
       <c r="AG124" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AH124" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="AK124" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AL124" t="n">
         <v>0</v>
@@ -19614,7 +19601,7 @@
         <v>1</v>
       </c>
       <c r="AP124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AQ124" t="s">
         <v>129</v>
@@ -19662,94 +19649,94 @@
         <v>126</v>
       </c>
       <c r="H125" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I125" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J125" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="K125" t="n">
-        <v>35.7109890780377</v>
+        <v>30.6074088758334</v>
       </c>
       <c r="L125" t="n">
-        <v>30.0775939849624</v>
+        <v>24.1740391588107</v>
       </c>
       <c r="M125" t="n">
-        <v>18.7295403212497</v>
+        <v>26.6127215016027</v>
       </c>
       <c r="N125" t="s">
         <v>72</v>
       </c>
       <c r="O125" t="n">
-        <v>0.196318505472103</v>
+        <v>0.203232222144609</v>
       </c>
       <c r="P125" t="n">
-        <v>0.196679337974954</v>
+        <v>0.203605762026649</v>
       </c>
       <c r="Q125" t="n">
-        <v>14.4766002078416</v>
+        <v>10.4576893239488</v>
       </c>
       <c r="R125" t="n">
-        <v>7.58389099732437</v>
+        <v>4.62785206374769</v>
       </c>
       <c r="S125" t="n">
-        <v>-3.9</v>
+        <v>-4.1</v>
       </c>
       <c r="T125" t="n">
-        <v>97.1797219228692</v>
+        <v>97.2189361420206</v>
       </c>
       <c r="U125" t="n">
-        <v>97.1797219228692</v>
+        <v>97.2189361420206</v>
       </c>
       <c r="V125" t="n">
         <v>97.1797219228692</v>
       </c>
       <c r="W125" t="n">
-        <v>103.101668230153</v>
+        <v>102.065912808901</v>
       </c>
       <c r="X125" t="n">
-        <v>98.0982391540476</v>
+        <v>98.8598447363989</v>
       </c>
       <c r="Y125" t="n">
-        <v>97.3164565383449</v>
+        <v>96.812068204534</v>
       </c>
       <c r="Z125" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AA125" t="n">
-        <v>98.5119400345742</v>
+        <v>97.6589794795881</v>
       </c>
       <c r="AB125" t="n">
-        <v>100.65610265142</v>
+        <v>97.3822631487352</v>
       </c>
       <c r="AC125" t="n">
-        <v>98.4265179639656</v>
+        <v>97.9194864056909</v>
       </c>
       <c r="AD125" t="n">
-        <v>100.839894696788</v>
+        <v>98.7211772632021</v>
       </c>
       <c r="AE125" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AF125" t="n">
         <v>14</v>
       </c>
       <c r="AG125" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AH125" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="AI125" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AJ125" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AK125" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AL125" t="n">
         <v>0</v>
@@ -19812,87 +19799,97 @@
         <v>126</v>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I126" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J126" t="s">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="K126" t="n">
-        <v>37.4147152054147</v>
+        <v>44.9163282760142</v>
       </c>
       <c r="L126" t="n">
-        <v>22.9113402061856</v>
+        <v>36.8082443871918</v>
       </c>
       <c r="M126" t="n">
-        <v>63.3021676982194</v>
+        <v>22.0279016937952</v>
       </c>
       <c r="N126" t="s">
         <v>72</v>
       </c>
       <c r="O126" t="n">
-        <v>0.263366908823257</v>
+        <v>0.224932531623054</v>
       </c>
       <c r="P126" t="n">
-        <v>0.245030095687226</v>
+        <v>0.21229478008661</v>
       </c>
       <c r="Q126" t="n">
-        <v>16.7498370156795</v>
+        <v>16.1285302885811</v>
       </c>
       <c r="R126" t="n">
-        <v>9.53695856747676</v>
+        <v>7.16010248756576</v>
       </c>
       <c r="S126" t="n">
         <v>-4.7</v>
       </c>
       <c r="T126" t="n">
-        <v>94.7166875566949</v>
+        <v>92.4330397803157</v>
       </c>
       <c r="U126" t="n">
-        <v>95.8145063799703</v>
+        <v>92.8249003896263</v>
       </c>
       <c r="V126" t="n">
-        <v>95.8145063799703</v>
+        <v>94.4745763645127</v>
       </c>
       <c r="W126" t="n">
-        <v>102.22962505915</v>
+        <v>103.906504756181</v>
       </c>
       <c r="X126" t="n">
-        <v>98.4541869098614</v>
+        <v>96.0827738671513</v>
       </c>
       <c r="Y126" t="n">
-        <v>96.8376420433072</v>
+        <v>94.98030271759</v>
       </c>
       <c r="Z126" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA126"/>
-      <c r="AB126"/>
-      <c r="AC126"/>
-      <c r="AD126"/>
+        <v>22</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>92.8249003896263</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>92.8249003896263</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>92.8249003896263</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>92.8249003896263</v>
+      </c>
       <c r="AE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF126"/>
+        <v>1</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>28</v>
+      </c>
       <c r="AG126" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AH126" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AI126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ126" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="AK126" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AL126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM126" t="n">
         <v>0</v>
@@ -19952,97 +19949,97 @@
         <v>126</v>
       </c>
       <c r="H127" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I127" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J127" t="s">
         <v>241</v>
       </c>
       <c r="K127" t="n">
-        <v>44.4585916285473</v>
+        <v>49.350487642013</v>
       </c>
       <c r="L127" t="n">
-        <v>39.7330154946365</v>
+        <v>35.1028431028431</v>
       </c>
       <c r="M127" t="n">
-        <v>11.8933236631604</v>
+        <v>40.5882922287168</v>
       </c>
       <c r="N127" t="s">
         <v>72</v>
       </c>
       <c r="O127" t="n">
-        <v>0.19943898280648</v>
+        <v>0.201737846905621</v>
       </c>
       <c r="P127" t="n">
-        <v>0.199805550732204</v>
+        <v>0.2021086401329</v>
       </c>
       <c r="Q127" t="n">
-        <v>17.8637235273449</v>
+        <v>16.9369614651515</v>
       </c>
       <c r="R127" t="n">
-        <v>9.24675412617599</v>
+        <v>7.40142961493698</v>
       </c>
       <c r="S127" t="n">
-        <v>-4.1</v>
+        <v>-4.8</v>
       </c>
       <c r="T127" t="n">
-        <v>97.2189361420206</v>
+        <v>93.1388468453272</v>
       </c>
       <c r="U127" t="n">
-        <v>97.2189361420206</v>
+        <v>95.5308584446334</v>
       </c>
       <c r="V127" t="n">
-        <v>97.1797219228692</v>
+        <v>95.5308584446334</v>
       </c>
       <c r="W127" t="n">
-        <v>102.065912808901</v>
+        <v>103.029006411032</v>
       </c>
       <c r="X127" t="n">
-        <v>98.8598447363989</v>
+        <v>98.9894033744476</v>
       </c>
       <c r="Y127" t="n">
-        <v>96.812068204534</v>
+        <v>95.9563345237125</v>
       </c>
       <c r="Z127" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AA127" t="n">
-        <v>97.6589794795881</v>
+        <v>94.875414711859</v>
       </c>
       <c r="AB127" t="n">
-        <v>97.3822631487352</v>
+        <v>93.9437789698598</v>
       </c>
       <c r="AC127" t="n">
-        <v>97.9194864056909</v>
+        <v>95.4348205860085</v>
       </c>
       <c r="AD127" t="n">
-        <v>98.7211772632021</v>
+        <v>96.5160449854777</v>
       </c>
       <c r="AE127" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF127" t="n">
         <v>14</v>
       </c>
       <c r="AG127" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AH127" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI127" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ127" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AK127" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AL127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
@@ -20084,7 +20081,7 @@
         <v>46275</v>
       </c>
       <c r="B128" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C128" t="s">
         <v>226</v>
@@ -20096,7 +20093,7 @@
         <v>6</v>
       </c>
       <c r="F128" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G128" t="s">
         <v>126</v>
@@ -20105,10 +20102,10 @@
         <v>4</v>
       </c>
       <c r="I128" t="s">
+        <v>303</v>
+      </c>
+      <c r="J128" t="s">
         <v>304</v>
-      </c>
-      <c r="J128" t="s">
-        <v>305</v>
       </c>
       <c r="K128" t="n">
         <v>2.78451002912125</v>
@@ -20234,7 +20231,7 @@
         <v>46275</v>
       </c>
       <c r="B129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C129" t="s">
         <v>226</v>
@@ -20246,7 +20243,7 @@
         <v>6</v>
       </c>
       <c r="F129" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G129" t="s">
         <v>126</v>
@@ -20255,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J129" t="s">
         <v>245</v>
@@ -20384,7 +20381,7 @@
         <v>46275</v>
       </c>
       <c r="B130" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C130" t="s">
         <v>226</v>
@@ -20396,7 +20393,7 @@
         <v>6</v>
       </c>
       <c r="F130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G130" t="s">
         <v>126</v>
@@ -20405,7 +20402,7 @@
         <v>2</v>
       </c>
       <c r="I130" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J130" t="s">
         <v>283</v>
@@ -20534,7 +20531,7 @@
         <v>46275</v>
       </c>
       <c r="B131" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C131" t="s">
         <v>226</v>
@@ -20546,7 +20543,7 @@
         <v>6</v>
       </c>
       <c r="F131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G131" t="s">
         <v>126</v>
@@ -20555,10 +20552,10 @@
         <v>7</v>
       </c>
       <c r="I131" t="s">
+        <v>307</v>
+      </c>
+      <c r="J131" t="s">
         <v>308</v>
-      </c>
-      <c r="J131" t="s">
-        <v>309</v>
       </c>
       <c r="K131" t="n">
         <v>8.11779105211661</v>
@@ -20674,7 +20671,7 @@
         <v>46275</v>
       </c>
       <c r="B132" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C132" t="s">
         <v>226</v>
@@ -20686,7 +20683,7 @@
         <v>6</v>
       </c>
       <c r="F132" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G132" t="s">
         <v>126</v>
@@ -20695,10 +20692,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
+        <v>309</v>
+      </c>
+      <c r="J132" t="s">
         <v>310</v>
-      </c>
-      <c r="J132" t="s">
-        <v>311</v>
       </c>
       <c r="K132" t="n">
         <v>19.9010468794427</v>
@@ -20814,7 +20811,7 @@
         <v>46275</v>
       </c>
       <c r="B133" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C133" t="s">
         <v>226</v>
@@ -20826,7 +20823,7 @@
         <v>6</v>
       </c>
       <c r="F133" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G133" t="s">
         <v>126</v>
@@ -20835,10 +20832,10 @@
         <v>5</v>
       </c>
       <c r="I133" t="s">
+        <v>311</v>
+      </c>
+      <c r="J133" t="s">
         <v>312</v>
-      </c>
-      <c r="J133" t="s">
-        <v>313</v>
       </c>
       <c r="K133" t="n">
         <v>20.2372202612462</v>
@@ -20940,7 +20937,7 @@
         <v>46275</v>
       </c>
       <c r="B134" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C134" t="s">
         <v>226</v>
@@ -20952,7 +20949,7 @@
         <v>6</v>
       </c>
       <c r="F134" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G134" t="s">
         <v>126</v>
@@ -20961,7 +20958,7 @@
         <v>3</v>
       </c>
       <c r="I134" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J134" t="s">
         <v>251</v>
@@ -21090,7 +21087,7 @@
         <v>46275</v>
       </c>
       <c r="B135" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C135" t="s">
         <v>226</v>
@@ -21102,7 +21099,7 @@
         <v>6</v>
       </c>
       <c r="F135" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G135" t="s">
         <v>126</v>
@@ -21111,10 +21108,10 @@
         <v>6</v>
       </c>
       <c r="I135" t="s">
+        <v>314</v>
+      </c>
+      <c r="J135" t="s">
         <v>315</v>
-      </c>
-      <c r="J135" t="s">
-        <v>316</v>
       </c>
       <c r="K135" t="n">
         <v>149.829520045</v>
@@ -21240,7 +21237,7 @@
         <v>46275</v>
       </c>
       <c r="B136" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C136" t="s">
         <v>226</v>
@@ -21252,19 +21249,19 @@
         <v>7</v>
       </c>
       <c r="F136" t="s">
+        <v>317</v>
+      </c>
+      <c r="G136" t="s">
         <v>318</v>
-      </c>
-      <c r="G136" t="s">
-        <v>319</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
       <c r="I136" t="s">
+        <v>319</v>
+      </c>
+      <c r="J136" t="s">
         <v>320</v>
-      </c>
-      <c r="J136" t="s">
-        <v>321</v>
       </c>
       <c r="K136" t="n">
         <v>3.03544572611321</v>
@@ -21390,7 +21387,7 @@
         <v>46275</v>
       </c>
       <c r="B137" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C137" t="s">
         <v>226</v>
@@ -21402,16 +21399,16 @@
         <v>7</v>
       </c>
       <c r="F137" t="s">
+        <v>317</v>
+      </c>
+      <c r="G137" t="s">
         <v>318</v>
-      </c>
-      <c r="G137" t="s">
-        <v>319</v>
       </c>
       <c r="H137" t="n">
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J137" t="s">
         <v>251</v>
@@ -21540,7 +21537,7 @@
         <v>46275</v>
       </c>
       <c r="B138" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C138" t="s">
         <v>226</v>
@@ -21552,19 +21549,19 @@
         <v>7</v>
       </c>
       <c r="F138" t="s">
+        <v>317</v>
+      </c>
+      <c r="G138" t="s">
         <v>318</v>
       </c>
-      <c r="G138" t="s">
-        <v>319</v>
-      </c>
       <c r="H138" t="n">
         <v>1</v>
       </c>
       <c r="I138" t="s">
+        <v>322</v>
+      </c>
+      <c r="J138" t="s">
         <v>323</v>
-      </c>
-      <c r="J138" t="s">
-        <v>324</v>
       </c>
       <c r="K138" t="n">
         <v>8.22290351976709</v>
@@ -21690,7 +21687,7 @@
         <v>46275</v>
       </c>
       <c r="B139" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C139" t="s">
         <v>226</v>
@@ -21702,16 +21699,16 @@
         <v>7</v>
       </c>
       <c r="F139" t="s">
+        <v>317</v>
+      </c>
+      <c r="G139" t="s">
         <v>318</v>
-      </c>
-      <c r="G139" t="s">
-        <v>319</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
       </c>
       <c r="I139" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J139" t="s">
         <v>135</v>
@@ -21830,7 +21827,7 @@
         <v>46275</v>
       </c>
       <c r="B140" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C140" t="s">
         <v>226</v>
@@ -21842,19 +21839,19 @@
         <v>7</v>
       </c>
       <c r="F140" t="s">
+        <v>317</v>
+      </c>
+      <c r="G140" t="s">
         <v>318</v>
-      </c>
-      <c r="G140" t="s">
-        <v>319</v>
       </c>
       <c r="H140" t="n">
         <v>6</v>
       </c>
       <c r="I140" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J140" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K140" t="n">
         <v>15.7931118632922</v>
@@ -21980,7 +21977,7 @@
         <v>46275</v>
       </c>
       <c r="B141" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C141" t="s">
         <v>226</v>
@@ -21992,19 +21989,19 @@
         <v>7</v>
       </c>
       <c r="F141" t="s">
+        <v>317</v>
+      </c>
+      <c r="G141" t="s">
         <v>318</v>
-      </c>
-      <c r="G141" t="s">
-        <v>319</v>
       </c>
       <c r="H141" t="n">
         <v>2</v>
       </c>
       <c r="I141" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J141" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K141" t="n">
         <v>21.1053082219426</v>
@@ -22130,7 +22127,7 @@
         <v>46275</v>
       </c>
       <c r="B142" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C142" t="s">
         <v>226</v>
@@ -22142,19 +22139,19 @@
         <v>7</v>
       </c>
       <c r="F142" t="s">
+        <v>317</v>
+      </c>
+      <c r="G142" t="s">
         <v>318</v>
-      </c>
-      <c r="G142" t="s">
-        <v>319</v>
       </c>
       <c r="H142" t="n">
         <v>5</v>
       </c>
       <c r="I142" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J142" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K142" t="n">
         <v>34.9405470887116</v>
@@ -22280,7 +22277,7 @@
         <v>46275</v>
       </c>
       <c r="B143" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C143" t="s">
         <v>226</v>
@@ -22292,16 +22289,16 @@
         <v>7</v>
       </c>
       <c r="F143" t="s">
+        <v>317</v>
+      </c>
+      <c r="G143" t="s">
         <v>318</v>
-      </c>
-      <c r="G143" t="s">
-        <v>319</v>
       </c>
       <c r="H143" t="n">
         <v>7</v>
       </c>
       <c r="I143" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J143" t="s">
         <v>283</v>
@@ -22430,7 +22427,7 @@
         <v>46275</v>
       </c>
       <c r="B144" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C144" t="s">
         <v>226</v>
@@ -22442,19 +22439,19 @@
         <v>8</v>
       </c>
       <c r="F144" t="s">
+        <v>330</v>
+      </c>
+      <c r="G144" t="s">
         <v>331</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="s">
         <v>332</v>
       </c>
-      <c r="H144" t="n">
-        <v>1</v>
-      </c>
-      <c r="I144" t="s">
-        <v>333</v>
-      </c>
       <c r="J144" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K144" t="n">
         <v>2.77718743021649</v>
@@ -22580,7 +22577,7 @@
         <v>46275</v>
       </c>
       <c r="B145" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C145" t="s">
         <v>226</v>
@@ -22592,16 +22589,16 @@
         <v>8</v>
       </c>
       <c r="F145" t="s">
+        <v>330</v>
+      </c>
+      <c r="G145" t="s">
         <v>331</v>
-      </c>
-      <c r="G145" t="s">
-        <v>332</v>
       </c>
       <c r="H145" t="n">
         <v>3</v>
       </c>
       <c r="I145" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J145" t="s">
         <v>245</v>
@@ -22730,7 +22727,7 @@
         <v>46275</v>
       </c>
       <c r="B146" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C146" t="s">
         <v>226</v>
@@ -22742,16 +22739,16 @@
         <v>8</v>
       </c>
       <c r="F146" t="s">
+        <v>330</v>
+      </c>
+      <c r="G146" t="s">
         <v>331</v>
-      </c>
-      <c r="G146" t="s">
-        <v>332</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J146" t="s">
         <v>287</v>
@@ -22880,7 +22877,7 @@
         <v>46275</v>
       </c>
       <c r="B147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s">
         <v>226</v>
@@ -22892,19 +22889,19 @@
         <v>8</v>
       </c>
       <c r="F147" t="s">
+        <v>330</v>
+      </c>
+      <c r="G147" t="s">
         <v>331</v>
-      </c>
-      <c r="G147" t="s">
-        <v>332</v>
       </c>
       <c r="H147" t="n">
         <v>7</v>
       </c>
       <c r="I147" t="s">
+        <v>335</v>
+      </c>
+      <c r="J147" t="s">
         <v>336</v>
-      </c>
-      <c r="J147" t="s">
-        <v>337</v>
       </c>
       <c r="K147" t="n">
         <v>8.72999425186407</v>
@@ -23030,7 +23027,7 @@
         <v>46275</v>
       </c>
       <c r="B148" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C148" t="s">
         <v>226</v>
@@ -23042,19 +23039,19 @@
         <v>8</v>
       </c>
       <c r="F148" t="s">
+        <v>330</v>
+      </c>
+      <c r="G148" t="s">
         <v>331</v>
-      </c>
-      <c r="G148" t="s">
-        <v>332</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
       </c>
       <c r="I148" t="s">
+        <v>337</v>
+      </c>
+      <c r="J148" t="s">
         <v>338</v>
-      </c>
-      <c r="J148" t="s">
-        <v>339</v>
       </c>
       <c r="K148" t="n">
         <v>11.4718544654461</v>
@@ -23180,7 +23177,7 @@
         <v>46275</v>
       </c>
       <c r="B149" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C149" t="s">
         <v>226</v>
@@ -23192,19 +23189,19 @@
         <v>8</v>
       </c>
       <c r="F149" t="s">
+        <v>330</v>
+      </c>
+      <c r="G149" t="s">
         <v>331</v>
-      </c>
-      <c r="G149" t="s">
-        <v>332</v>
       </c>
       <c r="H149" t="n">
         <v>4</v>
       </c>
       <c r="I149" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K149" t="n">
         <v>13.4584252714435</v>
@@ -23330,7 +23327,7 @@
         <v>46275</v>
       </c>
       <c r="B150" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C150" t="s">
         <v>226</v>
@@ -23342,19 +23339,19 @@
         <v>8</v>
       </c>
       <c r="F150" t="s">
+        <v>330</v>
+      </c>
+      <c r="G150" t="s">
         <v>331</v>
-      </c>
-      <c r="G150" t="s">
-        <v>332</v>
       </c>
       <c r="H150" t="n">
         <v>6</v>
       </c>
       <c r="I150" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J150" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K150" t="n">
         <v>15.3631346945442</v>
@@ -23480,7 +23477,7 @@
         <v>46275</v>
       </c>
       <c r="B151" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C151" t="s">
         <v>226</v>
@@ -23492,19 +23489,19 @@
         <v>9</v>
       </c>
       <c r="F151" t="s">
+        <v>342</v>
+      </c>
+      <c r="G151" t="s">
         <v>343</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
         <v>344</v>
       </c>
-      <c r="H151" t="n">
-        <v>1</v>
-      </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>345</v>
-      </c>
-      <c r="J151" t="s">
-        <v>346</v>
       </c>
       <c r="K151" t="n">
         <v>1.32085373323319</v>
@@ -23630,7 +23627,7 @@
         <v>46275</v>
       </c>
       <c r="B152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C152" t="s">
         <v>226</v>
@@ -23642,16 +23639,16 @@
         <v>9</v>
       </c>
       <c r="F152" t="s">
+        <v>342</v>
+      </c>
+      <c r="G152" t="s">
         <v>343</v>
-      </c>
-      <c r="G152" t="s">
-        <v>344</v>
       </c>
       <c r="H152" t="n">
         <v>6</v>
       </c>
       <c r="I152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J152" t="s">
         <v>131</v>
@@ -23780,7 +23777,7 @@
         <v>46275</v>
       </c>
       <c r="B153" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C153" t="s">
         <v>226</v>
@@ -23792,16 +23789,16 @@
         <v>9</v>
       </c>
       <c r="F153" t="s">
+        <v>342</v>
+      </c>
+      <c r="G153" t="s">
         <v>343</v>
-      </c>
-      <c r="G153" t="s">
-        <v>344</v>
       </c>
       <c r="H153" t="n">
         <v>5</v>
       </c>
       <c r="I153" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J153" t="s">
         <v>277</v>
@@ -23930,7 +23927,7 @@
         <v>46275</v>
       </c>
       <c r="B154" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C154" t="s">
         <v>226</v>
@@ -23942,19 +23939,19 @@
         <v>9</v>
       </c>
       <c r="F154" t="s">
+        <v>342</v>
+      </c>
+      <c r="G154" t="s">
         <v>343</v>
-      </c>
-      <c r="G154" t="s">
-        <v>344</v>
       </c>
       <c r="H154" t="n">
         <v>8</v>
       </c>
       <c r="I154" t="s">
+        <v>348</v>
+      </c>
+      <c r="J154" t="s">
         <v>349</v>
-      </c>
-      <c r="J154" t="s">
-        <v>350</v>
       </c>
       <c r="K154" t="n">
         <v>37.5474665366462</v>
@@ -24080,7 +24077,7 @@
         <v>46275</v>
       </c>
       <c r="B155" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C155" t="s">
         <v>226</v>
@@ -24092,16 +24089,16 @@
         <v>9</v>
       </c>
       <c r="F155" t="s">
+        <v>342</v>
+      </c>
+      <c r="G155" t="s">
         <v>343</v>
-      </c>
-      <c r="G155" t="s">
-        <v>344</v>
       </c>
       <c r="H155" t="n">
         <v>7</v>
       </c>
       <c r="I155" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J155" t="s">
         <v>245</v>
@@ -24230,7 +24227,7 @@
         <v>46275</v>
       </c>
       <c r="B156" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C156" t="s">
         <v>226</v>
@@ -24242,19 +24239,19 @@
         <v>9</v>
       </c>
       <c r="F156" t="s">
+        <v>342</v>
+      </c>
+      <c r="G156" t="s">
         <v>343</v>
-      </c>
-      <c r="G156" t="s">
-        <v>344</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
       </c>
       <c r="I156" t="s">
+        <v>351</v>
+      </c>
+      <c r="J156" t="s">
         <v>352</v>
-      </c>
-      <c r="J156" t="s">
-        <v>353</v>
       </c>
       <c r="K156" t="n">
         <v>43.4808173725608</v>
@@ -24380,7 +24377,7 @@
         <v>46275</v>
       </c>
       <c r="B157" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C157" t="s">
         <v>226</v>
@@ -24392,16 +24389,16 @@
         <v>9</v>
       </c>
       <c r="F157" t="s">
+        <v>342</v>
+      </c>
+      <c r="G157" t="s">
         <v>343</v>
-      </c>
-      <c r="G157" t="s">
-        <v>344</v>
       </c>
       <c r="H157" t="n">
         <v>4</v>
       </c>
       <c r="I157" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J157" t="s">
         <v>265</v>
@@ -24530,7 +24527,7 @@
         <v>46275</v>
       </c>
       <c r="B158" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C158" t="s">
         <v>226</v>
@@ -24542,19 +24539,19 @@
         <v>9</v>
       </c>
       <c r="F158" t="s">
+        <v>342</v>
+      </c>
+      <c r="G158" t="s">
         <v>343</v>
-      </c>
-      <c r="G158" t="s">
-        <v>344</v>
       </c>
       <c r="H158" t="n">
         <v>2</v>
       </c>
       <c r="I158" t="s">
+        <v>354</v>
+      </c>
+      <c r="J158" t="s">
         <v>355</v>
-      </c>
-      <c r="J158" t="s">
-        <v>356</v>
       </c>
       <c r="K158" t="n">
         <v>159.469696825063</v>
@@ -24680,7 +24677,7 @@
         <v>46275</v>
       </c>
       <c r="B159" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C159" t="s">
         <v>226</v>
@@ -24692,19 +24689,19 @@
         <v>10</v>
       </c>
       <c r="F159" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G159" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H159" t="n">
         <v>5</v>
       </c>
       <c r="I159" t="s">
+        <v>358</v>
+      </c>
+      <c r="J159" t="s">
         <v>359</v>
-      </c>
-      <c r="J159" t="s">
-        <v>360</v>
       </c>
       <c r="K159" t="n">
         <v>3.58395657858519</v>
@@ -24830,7 +24827,7 @@
         <v>46275</v>
       </c>
       <c r="B160" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C160" t="s">
         <v>226</v>
@@ -24842,19 +24839,19 @@
         <v>10</v>
       </c>
       <c r="F160" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G160" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H160" t="n">
         <v>4</v>
       </c>
       <c r="I160" t="s">
+        <v>360</v>
+      </c>
+      <c r="J160" t="s">
         <v>361</v>
-      </c>
-      <c r="J160" t="s">
-        <v>362</v>
       </c>
       <c r="K160" t="n">
         <v>5.02206171492511</v>
@@ -24980,7 +24977,7 @@
         <v>46275</v>
       </c>
       <c r="B161" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C161" t="s">
         <v>226</v>
@@ -24992,16 +24989,16 @@
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G161" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H161" t="n">
         <v>1</v>
       </c>
       <c r="I161" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J161" t="s">
         <v>131</v>
@@ -25130,7 +25127,7 @@
         <v>46275</v>
       </c>
       <c r="B162" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C162" t="s">
         <v>226</v>
@@ -25142,16 +25139,16 @@
         <v>10</v>
       </c>
       <c r="F162" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G162" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H162" t="n">
         <v>3</v>
       </c>
       <c r="I162" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J162" t="s">
         <v>291</v>
@@ -25280,7 +25277,7 @@
         <v>46275</v>
       </c>
       <c r="B163" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C163" t="s">
         <v>226</v>
@@ -25292,19 +25289,19 @@
         <v>10</v>
       </c>
       <c r="F163" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G163" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H163" t="n">
         <v>7</v>
       </c>
       <c r="I163" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J163" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K163" t="n">
         <v>9.29188355596786</v>
@@ -25430,7 +25427,7 @@
         <v>46275</v>
       </c>
       <c r="B164" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C164" t="s">
         <v>226</v>
@@ -25442,19 +25439,19 @@
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G164" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H164" t="n">
         <v>2</v>
       </c>
       <c r="I164" t="s">
+        <v>365</v>
+      </c>
+      <c r="J164" t="s">
         <v>366</v>
-      </c>
-      <c r="J164" t="s">
-        <v>367</v>
       </c>
       <c r="K164" t="n">
         <v>17.7275879434238</v>
@@ -25580,7 +25577,7 @@
         <v>46275</v>
       </c>
       <c r="B165" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C165" t="s">
         <v>226</v>
@@ -25592,19 +25589,19 @@
         <v>10</v>
       </c>
       <c r="F165" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G165" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H165" t="n">
         <v>8</v>
       </c>
       <c r="I165" t="s">
+        <v>367</v>
+      </c>
+      <c r="J165" t="s">
         <v>368</v>
-      </c>
-      <c r="J165" t="s">
-        <v>369</v>
       </c>
       <c r="K165" t="n">
         <v>24.8554887373151</v>
@@ -25728,7 +25725,7 @@
         <v>46275</v>
       </c>
       <c r="B166" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C166" t="s">
         <v>226</v>
@@ -25740,16 +25737,16 @@
         <v>10</v>
       </c>
       <c r="F166" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G166" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H166" t="n">
         <v>6</v>
       </c>
       <c r="I166" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="J166" t="s">
         <v>283</v>
@@ -25878,7 +25875,7 @@
         <v>46275</v>
       </c>
       <c r="B167" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C167" t="s">
         <v>226</v>
@@ -25890,7 +25887,7 @@
         <v>11</v>
       </c>
       <c r="F167" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G167" t="s">
         <v>182</v>
@@ -25899,10 +25896,10 @@
         <v>6</v>
       </c>
       <c r="I167" t="s">
+        <v>372</v>
+      </c>
+      <c r="J167" t="s">
         <v>373</v>
-      </c>
-      <c r="J167" t="s">
-        <v>374</v>
       </c>
       <c r="K167" t="n">
         <v>1.81141388161351</v>
@@ -26028,7 +26025,7 @@
         <v>46275</v>
       </c>
       <c r="B168" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C168" t="s">
         <v>226</v>
@@ -26040,7 +26037,7 @@
         <v>11</v>
       </c>
       <c r="F168" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G168" t="s">
         <v>182</v>
@@ -26049,7 +26046,7 @@
         <v>4</v>
       </c>
       <c r="I168" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J168" t="s">
         <v>277</v>
@@ -26178,7 +26175,7 @@
         <v>46275</v>
       </c>
       <c r="B169" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C169" t="s">
         <v>226</v>
@@ -26190,7 +26187,7 @@
         <v>11</v>
       </c>
       <c r="F169" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G169" t="s">
         <v>182</v>
@@ -26199,7 +26196,7 @@
         <v>1</v>
       </c>
       <c r="I169" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J169" t="s">
         <v>253</v>
@@ -26328,7 +26325,7 @@
         <v>46275</v>
       </c>
       <c r="B170" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C170" t="s">
         <v>226</v>
@@ -26340,7 +26337,7 @@
         <v>11</v>
       </c>
       <c r="F170" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G170" t="s">
         <v>182</v>
@@ -26349,7 +26346,7 @@
         <v>3</v>
       </c>
       <c r="I170" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J170" t="s">
         <v>251</v>
@@ -26478,7 +26475,7 @@
         <v>46275</v>
       </c>
       <c r="B171" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C171" t="s">
         <v>226</v>
@@ -26490,7 +26487,7 @@
         <v>11</v>
       </c>
       <c r="F171" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G171" t="s">
         <v>182</v>
@@ -26499,10 +26496,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J171" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K171" t="n">
         <v>17.8661791793517</v>
@@ -26628,7 +26625,7 @@
         <v>46275</v>
       </c>
       <c r="B172" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C172" t="s">
         <v>226</v>
@@ -26640,7 +26637,7 @@
         <v>11</v>
       </c>
       <c r="F172" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G172" t="s">
         <v>182</v>
@@ -26649,10 +26646,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J172" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K172" t="n">
         <v>41.3555104531547</v>
@@ -26778,7 +26775,7 @@
         <v>46275</v>
       </c>
       <c r="B173" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C173" t="s">
         <v>226</v>
@@ -26790,7 +26787,7 @@
         <v>11</v>
       </c>
       <c r="F173" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G173" t="s">
         <v>182</v>
@@ -26799,7 +26796,7 @@
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J173" t="s">
         <v>255</v>
@@ -26928,7 +26925,7 @@
         <v>46275</v>
       </c>
       <c r="B174" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C174" t="s">
         <v>226</v>
@@ -26940,7 +26937,7 @@
         <v>12</v>
       </c>
       <c r="F174" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G174" t="s">
         <v>182</v>
@@ -26949,7 +26946,7 @@
         <v>3</v>
       </c>
       <c r="I174" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J174" t="s">
         <v>251</v>
@@ -27078,7 +27075,7 @@
         <v>46275</v>
       </c>
       <c r="B175" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C175" t="s">
         <v>226</v>
@@ -27090,7 +27087,7 @@
         <v>12</v>
       </c>
       <c r="F175" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G175" t="s">
         <v>182</v>
@@ -27099,10 +27096,10 @@
         <v>2</v>
       </c>
       <c r="I175" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J175" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K175" t="n">
         <v>6.58829272068803</v>
@@ -27204,7 +27201,7 @@
         <v>46275</v>
       </c>
       <c r="B176" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C176" t="s">
         <v>226</v>
@@ -27216,7 +27213,7 @@
         <v>12</v>
       </c>
       <c r="F176" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G176" t="s">
         <v>182</v>
@@ -27225,10 +27222,10 @@
         <v>8</v>
       </c>
       <c r="I176" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J176" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K176" t="n">
         <v>8.01855616742048</v>
@@ -27354,7 +27351,7 @@
         <v>46275</v>
       </c>
       <c r="B177" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C177" t="s">
         <v>226</v>
@@ -27366,7 +27363,7 @@
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G177" t="s">
         <v>182</v>
@@ -27375,7 +27372,7 @@
         <v>7</v>
       </c>
       <c r="I177" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J177" t="s">
         <v>255</v>
@@ -27504,7 +27501,7 @@
         <v>46275</v>
       </c>
       <c r="B178" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C178" t="s">
         <v>226</v>
@@ -27516,7 +27513,7 @@
         <v>12</v>
       </c>
       <c r="F178" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G178" t="s">
         <v>182</v>
@@ -27525,7 +27522,7 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J178" t="s">
         <v>291</v>
@@ -27654,7 +27651,7 @@
         <v>46275</v>
       </c>
       <c r="B179" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C179" t="s">
         <v>226</v>
@@ -27666,7 +27663,7 @@
         <v>12</v>
       </c>
       <c r="F179" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G179" t="s">
         <v>182</v>
@@ -27675,10 +27672,10 @@
         <v>6</v>
       </c>
       <c r="I179" t="s">
+        <v>387</v>
+      </c>
+      <c r="J179" t="s">
         <v>388</v>
-      </c>
-      <c r="J179" t="s">
-        <v>389</v>
       </c>
       <c r="K179" t="n">
         <v>34.2727179359168</v>
@@ -27804,7 +27801,7 @@
         <v>46275</v>
       </c>
       <c r="B180" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C180" t="s">
         <v>226</v>
@@ -27816,7 +27813,7 @@
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G180" t="s">
         <v>182</v>
@@ -27825,10 +27822,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="s">
+        <v>389</v>
+      </c>
+      <c r="J180" t="s">
         <v>390</v>
-      </c>
-      <c r="J180" t="s">
-        <v>391</v>
       </c>
       <c r="K180" t="n">
         <v>51.5043704790109</v>

--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="392">
   <si>
     <t xml:space="preserve">meeting_date</t>
   </si>
@@ -891,12 +891,21 @@
     <t xml:space="preserve">Kerry Hoggan</t>
   </si>
   <si>
+    <t xml:space="preserve">BENTLEY SVEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shawn Speeding</t>
+  </si>
+  <si>
     <t xml:space="preserve">BLOCKER TIGER</t>
   </si>
   <si>
     <t xml:space="preserve">Stephen Neary</t>
   </si>
   <si>
+    <t xml:space="preserve">TUTA MOMENT</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPEEDY BEN</t>
   </si>
   <si>
@@ -910,12 +919,6 @@
   </si>
   <si>
     <t xml:space="preserve">HOT PINK DOUBLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAKODA SKYLAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAG THE JOKER</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10 13:10:00</t>
@@ -1756,7 +1759,7 @@
         <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.18411334857935</v>
+        <v>4.18174060739556</v>
       </c>
       <c r="L2"/>
       <c r="M2"/>
@@ -1770,13 +1773,13 @@
         <v>0.226909857942562</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.17913181775719</v>
+        <v>2.1783932097324</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51659310359693</v>
+        <v>1.51599283372543</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="T2"/>
       <c r="U2"/>
@@ -1882,7 +1885,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.27290634671216</v>
+        <v>4.27359140784093</v>
       </c>
       <c r="L3"/>
       <c r="M3"/>
@@ -1896,13 +1899,13 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.1995120478238</v>
+        <v>2.19964459851502</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52272172825024</v>
+        <v>1.52280417939659</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="T3"/>
       <c r="U3"/>
@@ -2008,7 +2011,7 @@
         <v>67</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5914344243232</v>
+        <v>4.5920523717456</v>
       </c>
       <c r="L4"/>
       <c r="M4"/>
@@ -2022,13 +2025,13 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32441644408913</v>
+        <v>2.32491015614774</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58153930772236</v>
+        <v>1.58184370356901</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="T4"/>
       <c r="U4"/>
@@ -2134,7 +2137,7 @@
         <v>69</v>
       </c>
       <c r="K5" t="n">
-        <v>5.13388010424858</v>
+        <v>5.13586240178947</v>
       </c>
       <c r="L5"/>
       <c r="M5"/>
@@ -2148,10 +2151,10 @@
         <v>0.214774626933501</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.55685711928246</v>
+        <v>2.55736349470599</v>
       </c>
       <c r="R5" t="n">
-        <v>1.69514628646778</v>
+        <v>1.6954310151713</v>
       </c>
       <c r="S5" t="n">
         <v>-0.3</v>
@@ -2260,13 +2263,13 @@
         <v>71</v>
       </c>
       <c r="K6" t="n">
-        <v>11.9053012061537</v>
+        <v>11.9064712830424</v>
       </c>
       <c r="L6" t="n">
-        <v>8.56729204146321</v>
+        <v>8.5716979514871</v>
       </c>
       <c r="M6" t="n">
-        <v>38.9622432448375</v>
+        <v>38.9044661912839</v>
       </c>
       <c r="N6" t="s">
         <v>72</v>
@@ -2278,10 +2281,10 @@
         <v>0.182134690495737</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.19166631985436</v>
+        <v>5.19091230007891</v>
       </c>
       <c r="R6" t="n">
-        <v>3.05702488062709</v>
+        <v>3.05756578560834</v>
       </c>
       <c r="S6" t="n">
         <v>-1.8</v>
@@ -2410,13 +2413,13 @@
         <v>67</v>
       </c>
       <c r="K7" t="n">
-        <v>32.905028755274</v>
+        <v>32.889173433643</v>
       </c>
       <c r="L7" t="n">
         <v>35.1514938488576</v>
       </c>
       <c r="M7" t="n">
-        <v>-6.3908097426608</v>
+        <v>-6.43591542636002</v>
       </c>
       <c r="N7" t="s">
         <v>76</v>
@@ -2428,10 +2431,10 @@
         <v>0.177173988626008</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.7896214671567</v>
+        <v>13.7872212956177</v>
       </c>
       <c r="R7" t="n">
-        <v>7.430626604508</v>
+        <v>7.42769664569099</v>
       </c>
       <c r="S7" t="n">
         <v>-3.3</v>
@@ -2558,13 +2561,13 @@
         <v>81</v>
       </c>
       <c r="K8" t="n">
-        <v>2.15585204287127</v>
+        <v>2.15617221503697</v>
       </c>
       <c r="L8" t="n">
-        <v>2.15937209854684</v>
+        <v>2.15741559702297</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.163012927597761</v>
+        <v>-0.0576329376555385</v>
       </c>
       <c r="N8" t="s">
         <v>76</v>
@@ -2576,10 +2579,10 @@
         <v>0.191927728555908</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.33661658102578</v>
+        <v>1.33671443518307</v>
       </c>
       <c r="R8" t="n">
-        <v>1.11816709142163</v>
+        <v>1.11809328531995</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -2706,13 +2709,13 @@
         <v>83</v>
       </c>
       <c r="K9" t="n">
-        <v>4.72913021235934</v>
+        <v>4.72657776102373</v>
       </c>
       <c r="L9" t="n">
-        <v>4.64005010903355</v>
+        <v>4.64306606620549</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9198090803453</v>
+        <v>1.79863249041572</v>
       </c>
       <c r="N9" t="s">
         <v>72</v>
@@ -2724,10 +2727,10 @@
         <v>0.249038124979973</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15715869614544</v>
+        <v>2.15648441379775</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42260675260025</v>
+        <v>1.42236159138651</v>
       </c>
       <c r="S9" t="n">
         <v>-1.2</v>
@@ -2844,7 +2847,7 @@
         <v>55</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9328302991148</v>
+        <v>5.93465720439917</v>
       </c>
       <c r="L10"/>
       <c r="M10"/>
@@ -2858,10 +2861,10 @@
         <v>0.226652746151221</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.55972372553759</v>
+        <v>2.56062404864703</v>
       </c>
       <c r="R10" t="n">
-        <v>1.55403024999925</v>
+        <v>1.55424141451365</v>
       </c>
       <c r="S10" t="n">
         <v>-1.5</v>
@@ -2970,13 +2973,13 @@
         <v>86</v>
       </c>
       <c r="K11" t="n">
-        <v>13.8774846799441</v>
+        <v>13.8780400907016</v>
       </c>
       <c r="L11" t="n">
-        <v>11.4858160101068</v>
+        <v>11.4910950247041</v>
       </c>
       <c r="M11" t="n">
-        <v>20.8228015121673</v>
+        <v>20.7721288603556</v>
       </c>
       <c r="N11" t="s">
         <v>87</v>
@@ -2988,10 +2991,10 @@
         <v>0.188541326758434</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.494658553575</v>
+        <v>5.49487380724263</v>
       </c>
       <c r="R11" t="n">
-        <v>2.95459243673048</v>
+        <v>2.95485544639376</v>
       </c>
       <c r="S11" t="n">
         <v>-3</v>
@@ -3118,13 +3121,13 @@
         <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>27.9106233720788</v>
+        <v>27.9033561914265</v>
       </c>
       <c r="L12" t="n">
-        <v>30.3143376780843</v>
+        <v>30.186236039843</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.92929844462091</v>
+        <v>-7.56265155219524</v>
       </c>
       <c r="N12" t="s">
         <v>72</v>
@@ -3136,10 +3139,10 @@
         <v>0.211560562780329</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.0157692913192</v>
+        <v>11.0036117674004</v>
       </c>
       <c r="R12" t="n">
-        <v>5.74519295815169</v>
+        <v>5.74301391099156</v>
       </c>
       <c r="S12" t="n">
         <v>-4</v>
@@ -3268,13 +3271,13 @@
         <v>67</v>
       </c>
       <c r="K13" t="n">
-        <v>34.8953655656761</v>
+        <v>34.8978317572972</v>
       </c>
       <c r="L13" t="n">
-        <v>31.4784387787221</v>
+        <v>31.5579047017987</v>
       </c>
       <c r="M13" t="n">
-        <v>10.8548165649935</v>
+        <v>10.5834879947151</v>
       </c>
       <c r="N13" t="s">
         <v>76</v>
@@ -3286,10 +3289,10 @@
         <v>0.197536959578864</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.8410499778953</v>
+        <v>13.8465535228561</v>
       </c>
       <c r="R13" t="n">
-        <v>7.09156815371654</v>
+        <v>7.09651611139646</v>
       </c>
       <c r="S13" t="n">
         <v>-4.7</v>
@@ -3416,13 +3419,13 @@
         <v>67</v>
       </c>
       <c r="K14" t="n">
-        <v>51.0402912461405</v>
+        <v>51.0346842928316</v>
       </c>
       <c r="L14" t="n">
-        <v>41.5139061851391</v>
+        <v>41.5484004985459</v>
       </c>
       <c r="M14" t="n">
-        <v>22.9474552900821</v>
+        <v>22.8318868607653</v>
       </c>
       <c r="N14" t="s">
         <v>72</v>
@@ -3434,10 +3437,10 @@
         <v>0.200108477641868</v>
       </c>
       <c r="Q14" t="n">
-        <v>19.0187693969427</v>
+        <v>19.0250191466135</v>
       </c>
       <c r="R14" t="n">
-        <v>9.45814595701087</v>
+        <v>9.46086307407307</v>
       </c>
       <c r="S14" t="n">
         <v>-5.2</v>
@@ -3564,13 +3567,13 @@
         <v>98</v>
       </c>
       <c r="K15" t="n">
-        <v>2.85462453328373</v>
+        <v>2.85403032676696</v>
       </c>
       <c r="L15" t="n">
-        <v>3.40634899008822</v>
+        <v>3.40426183749191</v>
       </c>
       <c r="M15" t="n">
-        <v>-16.196944541205</v>
+        <v>-16.1630196791893</v>
       </c>
       <c r="N15" t="s">
         <v>76</v>
@@ -3582,10 +3585,10 @@
         <v>0.183347862652581</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5874164594016</v>
+        <v>1.58727337219102</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23569608097425</v>
+        <v>1.23560551336129</v>
       </c>
       <c r="S15" t="n">
         <v>0.2</v>
@@ -3712,13 +3715,13 @@
         <v>71</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2241320061971</v>
+        <v>3.22447203239721</v>
       </c>
       <c r="L16" t="n">
-        <v>3.58615125327213</v>
+        <v>3.58460876733933</v>
       </c>
       <c r="M16" t="n">
-        <v>-10.0949240984947</v>
+        <v>-10.0467514955457</v>
       </c>
       <c r="N16" t="s">
         <v>72</v>
@@ -3730,10 +3733,10 @@
         <v>0.175962029344542</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68274224641172</v>
+        <v>1.68289282288243</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2643835249988</v>
+        <v>1.26441103759708</v>
       </c>
       <c r="S16" t="n">
         <v>-0.2</v>
@@ -3862,13 +3865,13 @@
         <v>102</v>
       </c>
       <c r="K17" t="n">
-        <v>8.37110056395665</v>
+        <v>8.37766951521434</v>
       </c>
       <c r="L17" t="n">
-        <v>6.61465705403797</v>
+        <v>6.62692995825326</v>
       </c>
       <c r="M17" t="n">
-        <v>26.5538106597144</v>
+        <v>26.4185613548048</v>
       </c>
       <c r="N17" t="s">
         <v>72</v>
@@ -3880,10 +3883,10 @@
         <v>0.178825600449768</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.73178234233615</v>
+        <v>3.73326340428585</v>
       </c>
       <c r="R17" t="n">
-        <v>2.13615093546677</v>
+        <v>2.13683099913203</v>
       </c>
       <c r="S17" t="n">
         <v>-1.8</v>
@@ -4010,13 +4013,13 @@
         <v>104</v>
       </c>
       <c r="K18" t="n">
-        <v>13.1580835079912</v>
+        <v>13.1604864043218</v>
       </c>
       <c r="L18" t="n">
-        <v>9.31597578015836</v>
+        <v>9.30038128894262</v>
       </c>
       <c r="M18" t="n">
-        <v>41.2421395085204</v>
+        <v>41.5048049693239</v>
       </c>
       <c r="N18" t="s">
         <v>72</v>
@@ -4028,10 +4031,10 @@
         <v>0.179244637456315</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.68676607061255</v>
+        <v>5.68678340276676</v>
       </c>
       <c r="R18" t="n">
-        <v>3.14591961302023</v>
+        <v>3.14587056566486</v>
       </c>
       <c r="S18" t="n">
         <v>-2.6</v>
@@ -4158,13 +4161,13 @@
         <v>104</v>
       </c>
       <c r="K19" t="n">
-        <v>14.0587877912744</v>
+        <v>14.0474647621089</v>
       </c>
       <c r="L19" t="n">
-        <v>13.1640121100434</v>
+        <v>13.1709469247992</v>
       </c>
       <c r="M19" t="n">
-        <v>6.79713505085771</v>
+        <v>6.65493409330606</v>
       </c>
       <c r="N19" t="s">
         <v>72</v>
@@ -4176,10 +4179,10 @@
         <v>0.184265011173798</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.00741094621541</v>
+        <v>6.00274309814709</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24504757205682</v>
+        <v>3.24367130629003</v>
       </c>
       <c r="S19" t="n">
         <v>-2.4</v>
@@ -4306,13 +4309,13 @@
         <v>107</v>
       </c>
       <c r="K20" t="n">
-        <v>18.0094832066203</v>
+        <v>18.0046973378593</v>
       </c>
       <c r="L20" t="n">
-        <v>13.8074002485158</v>
+        <v>13.8533037816872</v>
       </c>
       <c r="M20" t="n">
-        <v>30.4335565165945</v>
+        <v>29.9668124051381</v>
       </c>
       <c r="N20" t="s">
         <v>72</v>
@@ -4324,10 +4327,10 @@
         <v>0.215347021935937</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.03963496888747</v>
+        <v>8.04218562794729</v>
       </c>
       <c r="R20" t="n">
-        <v>4.42000056544863</v>
+        <v>4.42089001807478</v>
       </c>
       <c r="S20" t="n">
         <v>-2.9</v>
@@ -4456,13 +4459,13 @@
         <v>109</v>
       </c>
       <c r="K21" t="n">
-        <v>57.4167169275591</v>
+        <v>57.4324699369739</v>
       </c>
       <c r="L21" t="n">
-        <v>48.3826802128689</v>
+        <v>48.1961445783133</v>
       </c>
       <c r="M21" t="n">
-        <v>18.6720468459854</v>
+        <v>19.1640336368663</v>
       </c>
       <c r="N21" t="s">
         <v>72</v>
@@ -4474,10 +4477,10 @@
         <v>0.18965029356576</v>
       </c>
       <c r="Q21" t="n">
-        <v>24.320628923544</v>
+        <v>24.3128033020811</v>
       </c>
       <c r="R21" t="n">
-        <v>12.5896603854558</v>
+        <v>12.5870154626681</v>
       </c>
       <c r="S21" t="n">
         <v>-4.5</v>
@@ -4606,13 +4609,13 @@
         <v>104</v>
       </c>
       <c r="K22" t="n">
-        <v>2.74470165769019</v>
+        <v>2.74622085412815</v>
       </c>
       <c r="L22" t="n">
-        <v>2.92786251719999</v>
+        <v>2.93249860716066</v>
       </c>
       <c r="M22" t="n">
-        <v>-6.25578757314603</v>
+        <v>-6.35218555867855</v>
       </c>
       <c r="N22" t="s">
         <v>72</v>
@@ -4624,10 +4627,10 @@
         <v>0.183503059384755</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.55817332314027</v>
+        <v>1.55842809079867</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22727162443303</v>
+        <v>1.22729652589916</v>
       </c>
       <c r="S22" t="n">
         <v>0.3</v>
@@ -4754,13 +4757,13 @@
         <v>115</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6067236130357</v>
+        <v>3.60380899355831</v>
       </c>
       <c r="L23" t="n">
-        <v>4.78433717648184</v>
+        <v>4.78571086758865</v>
       </c>
       <c r="M23" t="n">
-        <v>-24.6139333413808</v>
+        <v>-24.6964747083824</v>
       </c>
       <c r="N23" t="s">
         <v>76</v>
@@ -4772,10 +4775,10 @@
         <v>0.197917047631314</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87230363804466</v>
+        <v>1.8716295326755</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37913042919832</v>
+        <v>1.37891823805731</v>
       </c>
       <c r="S23" t="n">
         <v>-0.3</v>
@@ -4902,13 +4905,13 @@
         <v>117</v>
       </c>
       <c r="K24" t="n">
-        <v>9.72154752710711</v>
+        <v>9.72281712136781</v>
       </c>
       <c r="L24" t="n">
-        <v>7.57341915940932</v>
+        <v>7.55282833622838</v>
       </c>
       <c r="M24" t="n">
-        <v>28.3640496119765</v>
+        <v>28.7308103473069</v>
       </c>
       <c r="N24" t="s">
         <v>72</v>
@@ -4920,10 +4923,10 @@
         <v>0.17759029255941</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.28954651900046</v>
+        <v>4.2889565854827</v>
       </c>
       <c r="R24" t="n">
-        <v>2.48538624692369</v>
+        <v>2.48495027412897</v>
       </c>
       <c r="S24" t="n">
         <v>-2</v>
@@ -5050,13 +5053,13 @@
         <v>119</v>
       </c>
       <c r="K25" t="n">
-        <v>11.48873987528</v>
+        <v>11.4823306703196</v>
       </c>
       <c r="L25" t="n">
-        <v>8.5061665390831</v>
+        <v>8.48595672464998</v>
       </c>
       <c r="M25" t="n">
-        <v>35.0636602574484</v>
+        <v>35.3097952640475</v>
       </c>
       <c r="N25" t="s">
         <v>72</v>
@@ -5068,10 +5071,10 @@
         <v>0.192447139973863</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.11110094579047</v>
+        <v>5.11072531377645</v>
       </c>
       <c r="R25" t="n">
-        <v>2.94260291428902</v>
+        <v>2.94282263661639</v>
       </c>
       <c r="S25" t="n">
         <v>-2.3</v>
@@ -5198,13 +5201,13 @@
         <v>121</v>
       </c>
       <c r="K26" t="n">
-        <v>13.1881696094801</v>
+        <v>13.1898854451626</v>
       </c>
       <c r="L26" t="n">
-        <v>9.73683185668387</v>
+        <v>9.72736115163895</v>
       </c>
       <c r="M26" t="n">
-        <v>35.4462088243523</v>
+        <v>35.5957205612774</v>
       </c>
       <c r="N26" t="s">
         <v>72</v>
@@ -5216,10 +5219,10 @@
         <v>0.186278368470203</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.77616530348928</v>
+        <v>5.77873633243171</v>
       </c>
       <c r="R26" t="n">
-        <v>3.28756905374394</v>
+        <v>3.2880878909306</v>
       </c>
       <c r="S26" t="n">
         <v>-2.5</v>
@@ -5346,13 +5349,13 @@
         <v>71</v>
       </c>
       <c r="K27" t="n">
-        <v>19.547623607726</v>
+        <v>19.5505359533023</v>
       </c>
       <c r="L27" t="n">
-        <v>22.4281228975107</v>
+        <v>22.3879561226774</v>
       </c>
       <c r="M27" t="n">
-        <v>-12.8432473058385</v>
+        <v>-12.673868725788</v>
       </c>
       <c r="N27" t="s">
         <v>72</v>
@@ -5364,10 +5367,10 @@
         <v>0.168092691861424</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.07336842025816</v>
+        <v>8.06830183951689</v>
       </c>
       <c r="R27" t="n">
-        <v>4.30911700150143</v>
+        <v>4.307232119679</v>
       </c>
       <c r="S27" t="n">
         <v>-2.6</v>
@@ -5496,13 +5499,13 @@
         <v>98</v>
       </c>
       <c r="K28" t="n">
-        <v>24.0888091678317</v>
+        <v>24.1122489112967</v>
       </c>
       <c r="L28" t="n">
-        <v>19.0308277830637</v>
+        <v>19.1108350850373</v>
       </c>
       <c r="M28" t="n">
-        <v>26.5778317287345</v>
+        <v>26.1705666131528</v>
       </c>
       <c r="N28" t="s">
         <v>72</v>
@@ -5514,10 +5517,10 @@
         <v>0.180177082435504</v>
       </c>
       <c r="Q28" t="n">
-        <v>10.167276660427</v>
+        <v>10.1812153640853</v>
       </c>
       <c r="R28" t="n">
-        <v>5.50477356092611</v>
+        <v>5.51065311668814</v>
       </c>
       <c r="S28" t="n">
         <v>-3.2</v>
@@ -5644,13 +5647,13 @@
         <v>128</v>
       </c>
       <c r="K29" t="n">
-        <v>3.03093037665722</v>
+        <v>3.03138927792839</v>
       </c>
       <c r="L29" t="n">
-        <v>2.94458675617584</v>
+        <v>2.94094986031466</v>
       </c>
       <c r="M29" t="n">
-        <v>2.93228312259062</v>
+        <v>3.07517713355547</v>
       </c>
       <c r="N29" t="s">
         <v>72</v>
@@ -5662,10 +5665,10 @@
         <v>0.168718088692851</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.71370190287466</v>
+        <v>1.71400664924829</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31121436936158</v>
+        <v>1.31122225046686</v>
       </c>
       <c r="S29" t="n">
         <v>0.6</v>
@@ -5792,13 +5795,13 @@
         <v>131</v>
       </c>
       <c r="K30" t="n">
-        <v>5.06739537566278</v>
+        <v>5.06540701992887</v>
       </c>
       <c r="L30" t="n">
-        <v>5.20463179807442</v>
+        <v>5.19813919642393</v>
       </c>
       <c r="M30" t="n">
-        <v>-2.63681327971012</v>
+        <v>-2.55345560169629</v>
       </c>
       <c r="N30" t="s">
         <v>72</v>
@@ -5810,10 +5813,10 @@
         <v>0.188460113034842</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52203579956662</v>
+        <v>2.52115102341076</v>
       </c>
       <c r="R30" t="n">
-        <v>1.7096026649541</v>
+        <v>1.70957026537626</v>
       </c>
       <c r="S30" t="n">
         <v>-0.6</v>
@@ -5942,13 +5945,13 @@
         <v>133</v>
       </c>
       <c r="K31" t="n">
-        <v>6.12248679130928</v>
+        <v>6.12633213818702</v>
       </c>
       <c r="L31" t="n">
-        <v>6.04016428096877</v>
+        <v>6.04600689196542</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3629183994198</v>
+        <v>1.32856689806866</v>
       </c>
       <c r="N31" t="s">
         <v>72</v>
@@ -5960,10 +5963,10 @@
         <v>0.177927415938612</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.94330863742401</v>
+        <v>2.94425322778658</v>
       </c>
       <c r="R31" t="n">
-        <v>1.91349851894023</v>
+        <v>1.91405792806834</v>
       </c>
       <c r="S31" t="n">
         <v>-0.9</v>
@@ -6090,13 +6093,13 @@
         <v>135</v>
       </c>
       <c r="K32" t="n">
-        <v>8.5723934273685</v>
+        <v>8.56870898969316</v>
       </c>
       <c r="L32" t="n">
-        <v>8.61460935481092</v>
+        <v>8.62352332499784</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.490050398151176</v>
+        <v>-0.635637351913787</v>
       </c>
       <c r="N32" t="s">
         <v>72</v>
@@ -6108,10 +6111,10 @@
         <v>0.169127302860132</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.90108050160262</v>
+        <v>3.90115873319744</v>
       </c>
       <c r="R32" t="n">
-        <v>2.39845270751017</v>
+        <v>2.39778847812132</v>
       </c>
       <c r="S32" t="n">
         <v>-1.4</v>
@@ -6238,13 +6241,13 @@
         <v>109</v>
       </c>
       <c r="K33" t="n">
-        <v>10.0185523076578</v>
+        <v>10.0170457114157</v>
       </c>
       <c r="L33" t="n">
-        <v>9.59299760191846</v>
+        <v>9.56913214046503</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4360972805231</v>
+        <v>4.68081707281038</v>
       </c>
       <c r="N33" t="s">
         <v>72</v>
@@ -6256,10 +6259,10 @@
         <v>0.187331546657054</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.63176743405855</v>
+        <v>4.63137766651947</v>
       </c>
       <c r="R33" t="n">
-        <v>2.83242670933458</v>
+        <v>2.83236390711128</v>
       </c>
       <c r="S33" t="n">
         <v>-1.6</v>
@@ -6386,13 +6389,13 @@
         <v>138</v>
       </c>
       <c r="K34" t="n">
-        <v>18.6212489548736</v>
+        <v>18.6203338953234</v>
       </c>
       <c r="L34" t="n">
-        <v>24.0112845138055</v>
+        <v>24.1737974377568</v>
       </c>
       <c r="M34" t="n">
-        <v>-22.4479267480793</v>
+        <v>-22.9730705601079</v>
       </c>
       <c r="N34" t="s">
         <v>72</v>
@@ -6404,10 +6407,10 @@
         <v>0.165248842825829</v>
       </c>
       <c r="Q34" t="n">
-        <v>8.13260599361066</v>
+        <v>8.12561721591229</v>
       </c>
       <c r="R34" t="n">
-        <v>4.62199023091303</v>
+        <v>4.62113084291253</v>
       </c>
       <c r="S34" t="n">
         <v>-2.3</v>
@@ -6536,13 +6539,13 @@
         <v>140</v>
       </c>
       <c r="K35" t="n">
-        <v>25.4936241603007</v>
+        <v>25.4889510674613</v>
       </c>
       <c r="L35" t="n">
-        <v>24.553645961208</v>
+        <v>24.77260341838</v>
       </c>
       <c r="M35" t="n">
-        <v>3.82826322647882</v>
+        <v>2.89169304082828</v>
       </c>
       <c r="N35" t="s">
         <v>72</v>
@@ -6554,10 +6557,10 @@
         <v>0.206074919470449</v>
       </c>
       <c r="Q35" t="n">
-        <v>11.7636255890235</v>
+        <v>11.7698818283758</v>
       </c>
       <c r="R35" t="n">
-        <v>6.97022608168457</v>
+        <v>6.97106796794476</v>
       </c>
       <c r="S35" t="n">
         <v>-3</v>
@@ -6686,13 +6689,13 @@
         <v>144</v>
       </c>
       <c r="K36" t="n">
-        <v>3.93759165739636</v>
+        <v>3.93743558636443</v>
       </c>
       <c r="L36" t="n">
-        <v>5.02729603378073</v>
+        <v>5.00465395586248</v>
       </c>
       <c r="M36" t="n">
-        <v>-21.6757550990064</v>
+        <v>-21.3245187161824</v>
       </c>
       <c r="N36" t="s">
         <v>72</v>
@@ -6704,10 +6707,10 @@
         <v>0.182781356519611</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.0891284610889</v>
+        <v>2.08894837155504</v>
       </c>
       <c r="R36" t="n">
-        <v>1.50778356036576</v>
+        <v>1.50767705664765</v>
       </c>
       <c r="S36" t="n">
         <v>0.4</v>
@@ -6836,13 +6839,13 @@
         <v>146</v>
       </c>
       <c r="K37" t="n">
-        <v>4.75390277358584</v>
+        <v>4.75375986000215</v>
       </c>
       <c r="L37" t="n">
         <v>4.19162580158431</v>
       </c>
       <c r="M37" t="n">
-        <v>13.414293131534</v>
+        <v>13.410883629101</v>
       </c>
       <c r="N37" t="s">
         <v>72</v>
@@ -6854,10 +6857,10 @@
         <v>0.19307677731308</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.41568395671871</v>
+        <v>2.41571808871404</v>
       </c>
       <c r="R37" t="n">
-        <v>1.66738605271046</v>
+        <v>1.66748856937106</v>
       </c>
       <c r="S37" t="n">
         <v>-0.4</v>
@@ -6986,13 +6989,13 @@
         <v>144</v>
       </c>
       <c r="K38" t="n">
-        <v>5.31623070891567</v>
+        <v>5.31778056481541</v>
       </c>
       <c r="L38" t="n">
-        <v>5.14523846272573</v>
+        <v>5.14365067119272</v>
       </c>
       <c r="M38" t="n">
-        <v>3.32331042436</v>
+        <v>3.38533669477032</v>
       </c>
       <c r="N38" t="s">
         <v>72</v>
@@ -7004,10 +7007,10 @@
         <v>0.183180270605474</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.62994406033485</v>
+        <v>2.63046530446445</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76408870365916</v>
+        <v>1.76443284326518</v>
       </c>
       <c r="S38" t="n">
         <v>-0.5</v>
@@ -7136,13 +7139,13 @@
         <v>109</v>
       </c>
       <c r="K39" t="n">
-        <v>8.61045611447648</v>
+        <v>8.60906834797147</v>
       </c>
       <c r="L39" t="n">
-        <v>7.85793981299599</v>
+        <v>7.86783101250885</v>
       </c>
       <c r="M39" t="n">
-        <v>9.57650884823435</v>
+        <v>9.42111408193878</v>
       </c>
       <c r="N39" t="s">
         <v>72</v>
@@ -7154,10 +7157,10 @@
         <v>0.206903293327624</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.12150786128175</v>
+        <v>4.12037651026395</v>
       </c>
       <c r="R39" t="n">
-        <v>2.61296255538259</v>
+        <v>2.61210742867631</v>
       </c>
       <c r="S39" t="n">
         <v>-1.3</v>
@@ -7284,13 +7287,13 @@
         <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>13.1739796913269</v>
+        <v>13.1673287888971</v>
       </c>
       <c r="L40" t="n">
-        <v>12.348191134708</v>
+        <v>12.3756960772182</v>
       </c>
       <c r="M40" t="n">
-        <v>6.68752651793496</v>
+        <v>6.39667220930071</v>
       </c>
       <c r="N40" t="s">
         <v>72</v>
@@ -7302,13 +7305,13 @@
         <v>0.240549762805754</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.46244153204828</v>
+        <v>6.45862460964493</v>
       </c>
       <c r="R40" t="n">
-        <v>4.07858162428322</v>
+        <v>4.07667031430523</v>
       </c>
       <c r="S40" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="T40" t="n">
         <v>100.990788297261</v>
@@ -7422,13 +7425,13 @@
         <v>81</v>
       </c>
       <c r="K41" t="n">
-        <v>16.380366020989</v>
+        <v>16.3777698495351</v>
       </c>
       <c r="L41" t="n">
-        <v>14.1794980859209</v>
+        <v>14.2725845582988</v>
       </c>
       <c r="M41" t="n">
-        <v>15.5214798276488</v>
+        <v>14.7498533474243</v>
       </c>
       <c r="N41" t="s">
         <v>72</v>
@@ -7440,10 +7443,10 @@
         <v>0.188680487917574</v>
       </c>
       <c r="Q41" t="n">
-        <v>7.31580227217302</v>
+        <v>7.32297562029614</v>
       </c>
       <c r="R41" t="n">
-        <v>4.33294725801116</v>
+        <v>4.33497140109559</v>
       </c>
       <c r="S41" t="n">
         <v>-2.3</v>
@@ -7570,7 +7573,7 @@
         <v>152</v>
       </c>
       <c r="K42" t="n">
-        <v>18.8927990457424</v>
+        <v>18.8825261235783</v>
       </c>
       <c r="L42"/>
       <c r="M42"/>
@@ -7584,10 +7587,10 @@
         <v>0.239913505806157</v>
       </c>
       <c r="Q42" t="n">
-        <v>9.20409114351636</v>
+        <v>9.19698483875913</v>
       </c>
       <c r="R42" t="n">
-        <v>5.69755950561625</v>
+        <v>5.69531972945867</v>
       </c>
       <c r="S42" t="n">
         <v>-2.6</v>
@@ -7696,7 +7699,7 @@
         <v>69</v>
       </c>
       <c r="K43" t="n">
-        <v>24.0633414231785</v>
+        <v>24.096452813073</v>
       </c>
       <c r="L43"/>
       <c r="M43"/>
@@ -7710,10 +7713,10 @@
         <v>0.239913505806157</v>
       </c>
       <c r="Q43" t="n">
-        <v>11.8446697834179</v>
+        <v>11.8542445172828</v>
       </c>
       <c r="R43" t="n">
-        <v>7.35431402779782</v>
+        <v>7.35977617981411</v>
       </c>
       <c r="S43" t="n">
         <v>-3.1</v>
@@ -7822,13 +7825,13 @@
         <v>158</v>
       </c>
       <c r="K44" t="n">
-        <v>3.1068844761815</v>
+        <v>3.10748399847623</v>
       </c>
       <c r="L44" t="n">
-        <v>3.64576573949182</v>
+        <v>3.65669677136276</v>
       </c>
       <c r="M44" t="n">
-        <v>-14.7810172626569</v>
+        <v>-15.0193687698597</v>
       </c>
       <c r="N44" t="s">
         <v>72</v>
@@ -7840,10 +7843,10 @@
         <v>0.181783576653451</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.72012153023849</v>
+        <v>1.7202285248984</v>
       </c>
       <c r="R44" t="n">
-        <v>1.28682147984152</v>
+        <v>1.28695588056681</v>
       </c>
       <c r="S44" t="n">
         <v>0.5</v>
@@ -7972,13 +7975,13 @@
         <v>160</v>
       </c>
       <c r="K45" t="n">
-        <v>4.15053125403358</v>
+        <v>4.15011994075662</v>
       </c>
       <c r="L45" t="n">
-        <v>4.02361697847516</v>
+        <v>4.02847935548842</v>
       </c>
       <c r="M45" t="n">
-        <v>3.154233522658</v>
+        <v>3.01951616315161</v>
       </c>
       <c r="N45" t="s">
         <v>72</v>
@@ -7990,10 +7993,10 @@
         <v>0.164905344850108</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.05578917430325</v>
+        <v>2.05570951216516</v>
       </c>
       <c r="R45" t="n">
-        <v>1.40961665264194</v>
+        <v>1.40941302677083</v>
       </c>
       <c r="S45" t="n">
         <v>-0.5</v>
@@ -8122,13 +8125,13 @@
         <v>128</v>
       </c>
       <c r="K46" t="n">
-        <v>4.89857596219605</v>
+        <v>4.89763589584349</v>
       </c>
       <c r="L46" t="n">
-        <v>4.89534485290518</v>
+        <v>4.88768877376472</v>
       </c>
       <c r="M46" t="n">
-        <v>0.0660037114432965</v>
+        <v>0.203513818886258</v>
       </c>
       <c r="N46" t="s">
         <v>72</v>
@@ -8140,10 +8143,10 @@
         <v>0.202416532393919</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.41706329367436</v>
+        <v>2.41671419574573</v>
       </c>
       <c r="R46" t="n">
-        <v>1.58774474635067</v>
+        <v>1.58740596495245</v>
       </c>
       <c r="S46" t="n">
         <v>-0.7</v>
@@ -8270,13 +8273,13 @@
         <v>98</v>
       </c>
       <c r="K47" t="n">
-        <v>7.34186442166893</v>
+        <v>7.34335004413799</v>
       </c>
       <c r="L47" t="n">
-        <v>6.05112845646518</v>
+        <v>6.02923976608187</v>
       </c>
       <c r="M47" t="n">
-        <v>21.3305001619111</v>
+        <v>21.7956214886127</v>
       </c>
       <c r="N47" t="s">
         <v>72</v>
@@ -8288,10 +8291,10 @@
         <v>0.16210380204963</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.30192337573257</v>
+        <v>3.30319514592006</v>
       </c>
       <c r="R47" t="n">
-        <v>2.00125746101154</v>
+        <v>2.00175704786082</v>
       </c>
       <c r="S47" t="n">
         <v>-1.4</v>
@@ -8418,7 +8421,7 @@
         <v>69</v>
       </c>
       <c r="K48" t="n">
-        <v>20.0950095452481</v>
+        <v>20.0909910295569</v>
       </c>
       <c r="L48"/>
       <c r="M48"/>
@@ -8432,10 +8435,10 @@
         <v>0.223071305103427</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.24761609535713</v>
+        <v>9.24272123980334</v>
       </c>
       <c r="R48" t="n">
-        <v>5.35687262132407</v>
+        <v>5.35740255577944</v>
       </c>
       <c r="S48" t="n">
         <v>-2.8</v>
@@ -8544,13 +8547,13 @@
         <v>165</v>
       </c>
       <c r="K49" t="n">
-        <v>27.8390279737819</v>
+        <v>27.8152340391356</v>
       </c>
       <c r="L49" t="n">
-        <v>22.2386035134534</v>
+        <v>22.2089717965801</v>
       </c>
       <c r="M49" t="n">
-        <v>25.1833459638799</v>
+        <v>25.243231851998</v>
       </c>
       <c r="N49" t="s">
         <v>72</v>
@@ -8562,10 +8565,10 @@
         <v>0.193719264950183</v>
       </c>
       <c r="Q49" t="n">
-        <v>12.1724833259546</v>
+        <v>12.1730146883885</v>
       </c>
       <c r="R49" t="n">
-        <v>6.64881022584191</v>
+        <v>6.65031761186316</v>
       </c>
       <c r="S49" t="n">
         <v>-3.4</v>
@@ -8692,13 +8695,13 @@
         <v>131</v>
       </c>
       <c r="K50" t="n">
-        <v>89.5206832247388</v>
+        <v>89.6337469994524</v>
       </c>
       <c r="L50" t="n">
         <v>69.8860936408106</v>
       </c>
       <c r="M50" t="n">
-        <v>28.0951310354287</v>
+        <v>28.2569139722384</v>
       </c>
       <c r="N50" t="s">
         <v>72</v>
@@ -8710,10 +8713,10 @@
         <v>0.194648429324228</v>
       </c>
       <c r="Q50" t="n">
-        <v>39.4523168595317</v>
+        <v>39.4204868331315</v>
       </c>
       <c r="R50" t="n">
-        <v>21.3266113481541</v>
+        <v>21.3168317266683</v>
       </c>
       <c r="S50" t="n">
         <v>-5.1</v>
@@ -8842,13 +8845,13 @@
         <v>170</v>
       </c>
       <c r="K51" t="n">
-        <v>3.52045963856133</v>
+        <v>3.51937070051067</v>
       </c>
       <c r="L51" t="n">
-        <v>4.00368309379879</v>
+        <v>3.98327159756243</v>
       </c>
       <c r="M51" t="n">
-        <v>-12.069473130526</v>
+        <v>-11.6462281240287</v>
       </c>
       <c r="N51" t="s">
         <v>72</v>
@@ -8860,10 +8863,10 @@
         <v>0.19467085849566</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.90868026442506</v>
+        <v>1.90819803685837</v>
       </c>
       <c r="R51" t="n">
-        <v>1.40620166601702</v>
+        <v>1.40610220049365</v>
       </c>
       <c r="S51" t="n">
         <v>0.3</v>
@@ -8990,13 +8993,13 @@
         <v>65</v>
       </c>
       <c r="K52" t="n">
-        <v>4.21060653765843</v>
+        <v>4.21164004487278</v>
       </c>
       <c r="L52" t="n">
-        <v>4.4909066415196</v>
+        <v>4.48486479214314</v>
       </c>
       <c r="M52" t="n">
-        <v>-6.24150369258899</v>
+        <v>-6.09215126728038</v>
       </c>
       <c r="N52" t="s">
         <v>87</v>
@@ -9008,10 +9011,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.18387664481536</v>
+        <v>2.18414034128443</v>
       </c>
       <c r="R52" t="n">
-        <v>1.53915453381457</v>
+        <v>1.53921743374233</v>
       </c>
       <c r="S52" t="n">
         <v>-0.3</v>
@@ -9138,13 +9141,13 @@
         <v>81</v>
       </c>
       <c r="K53" t="n">
-        <v>5.87648900629423</v>
+        <v>5.87231571122325</v>
       </c>
       <c r="L53" t="n">
-        <v>6.74863351103313</v>
+        <v>6.76232334843465</v>
       </c>
       <c r="M53" t="n">
-        <v>-12.9232755536815</v>
+        <v>-13.1612700451158</v>
       </c>
       <c r="N53" t="s">
         <v>87</v>
@@ -9156,10 +9159,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.88625003200838</v>
+        <v>2.88527392880814</v>
       </c>
       <c r="R53" t="n">
-        <v>1.88944384698781</v>
+        <v>1.88847178472961</v>
       </c>
       <c r="S53" t="n">
         <v>-0.7</v>
@@ -9286,13 +9289,13 @@
         <v>174</v>
       </c>
       <c r="K54" t="n">
-        <v>9.40031503440937</v>
+        <v>9.40462598839339</v>
       </c>
       <c r="L54" t="n">
-        <v>7.37794171892291</v>
+        <v>7.39649434213446</v>
       </c>
       <c r="M54" t="n">
-        <v>27.4110774052266</v>
+        <v>27.1497760069865</v>
       </c>
       <c r="N54" t="s">
         <v>76</v>
@@ -9304,10 +9307,10 @@
         <v>0.193512877021705</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.4521216468534</v>
+        <v>4.45474819734465</v>
       </c>
       <c r="R54" t="n">
-        <v>2.78014035324704</v>
+        <v>2.78104289121642</v>
       </c>
       <c r="S54" t="n">
         <v>-1.7</v>
@@ -9434,13 +9437,13 @@
         <v>128</v>
       </c>
       <c r="K55" t="n">
-        <v>9.64037921491493</v>
+        <v>9.65301703852826</v>
       </c>
       <c r="L55" t="n">
-        <v>7.76278817045719</v>
+        <v>7.82473984821219</v>
       </c>
       <c r="M55" t="n">
-        <v>24.1870704601123</v>
+        <v>23.3653415421063</v>
       </c>
       <c r="N55" t="s">
         <v>72</v>
@@ -9452,13 +9455,13 @@
         <v>0.185304474275342</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.47553831327623</v>
+        <v>4.47799187423455</v>
       </c>
       <c r="R55" t="n">
-        <v>2.75531268159047</v>
+        <v>2.75692871679468</v>
       </c>
       <c r="S55" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="T55" t="n">
         <v>104.677932400871</v>
@@ -9582,13 +9585,13 @@
         <v>128</v>
       </c>
       <c r="K56" t="n">
-        <v>15.124229402312</v>
+        <v>15.1199271467743</v>
       </c>
       <c r="L56" t="n">
-        <v>12.7805750798722</v>
+        <v>12.7773093139134</v>
       </c>
       <c r="M56" t="n">
-        <v>18.3376280628463</v>
+        <v>18.3342030415592</v>
       </c>
       <c r="N56" t="s">
         <v>72</v>
@@ -9600,10 +9603,10 @@
         <v>0.179912199615122</v>
       </c>
       <c r="Q56" t="n">
-        <v>6.66384229201907</v>
+        <v>6.66051599946551</v>
       </c>
       <c r="R56" t="n">
-        <v>3.90795129859599</v>
+        <v>3.90713331479999</v>
       </c>
       <c r="S56" t="n">
         <v>-2.2</v>
@@ -9732,13 +9735,13 @@
         <v>178</v>
       </c>
       <c r="K57" t="n">
-        <v>61.263096015259</v>
+        <v>61.2207671935579</v>
       </c>
       <c r="L57" t="n">
-        <v>49.7799900447984</v>
+        <v>49.730482347091</v>
       </c>
       <c r="M57" t="n">
-        <v>23.0677144774972</v>
+        <v>23.1051144170916</v>
       </c>
       <c r="N57" t="s">
         <v>72</v>
@@ -9750,10 +9753,10 @@
         <v>0.186634124244702</v>
       </c>
       <c r="Q57" t="n">
-        <v>26.56388867274</v>
+        <v>26.5753782287919</v>
       </c>
       <c r="R57" t="n">
-        <v>14.8575959824851</v>
+        <v>14.8596238910836</v>
       </c>
       <c r="S57" t="n">
         <v>-4.3</v>
@@ -9880,13 +9883,13 @@
         <v>138</v>
       </c>
       <c r="K58" t="n">
-        <v>63.5760807873629</v>
+        <v>63.5602282509503</v>
       </c>
       <c r="L58" t="n">
-        <v>59.920910724985</v>
+        <v>59.7776449491931</v>
       </c>
       <c r="M58" t="n">
-        <v>6.09999083484192</v>
+        <v>6.32775564338837</v>
       </c>
       <c r="N58" t="s">
         <v>72</v>
@@ -9898,10 +9901,10 @@
         <v>0.185363151988665</v>
       </c>
       <c r="Q58" t="n">
-        <v>27.8174615134663</v>
+        <v>27.8160232315412</v>
       </c>
       <c r="R58" t="n">
-        <v>15.606136148274</v>
+        <v>15.6088383023623</v>
       </c>
       <c r="S58" t="n">
         <v>-4.2</v>
@@ -10030,13 +10033,13 @@
         <v>184</v>
       </c>
       <c r="K59" t="n">
-        <v>2.8109521843072</v>
+        <v>2.81050220168554</v>
       </c>
       <c r="L59" t="n">
-        <v>2.97840783869911</v>
+        <v>2.97327188940092</v>
       </c>
       <c r="M59" t="n">
-        <v>-5.62232116824708</v>
+        <v>-5.47442998050807</v>
       </c>
       <c r="N59" t="s">
         <v>72</v>
@@ -10048,10 +10051,10 @@
         <v>0.165332410304714</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.61614911944404</v>
+        <v>1.61593037276543</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24965120314711</v>
+        <v>1.24947916892349</v>
       </c>
       <c r="S59" t="n">
         <v>0.6</v>
@@ -10180,13 +10183,13 @@
         <v>186</v>
       </c>
       <c r="K60" t="n">
-        <v>4.7695848361106</v>
+        <v>4.76734982690631</v>
       </c>
       <c r="L60" t="n">
-        <v>5.73067445991634</v>
+        <v>5.72476959184842</v>
       </c>
       <c r="M60" t="n">
-        <v>-16.7709687669079</v>
+        <v>-16.7241624240282</v>
       </c>
       <c r="N60" t="s">
         <v>72</v>
@@ -10198,10 +10201,10 @@
         <v>0.175285242181235</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.33959924680473</v>
+        <v>2.33877369615997</v>
       </c>
       <c r="R60" t="n">
-        <v>1.58093938733828</v>
+        <v>1.58068686610542</v>
       </c>
       <c r="S60" t="n">
         <v>-0.6</v>
@@ -10330,13 +10333,13 @@
         <v>178</v>
       </c>
       <c r="K61" t="n">
-        <v>5.52950159488132</v>
+        <v>5.53040578536637</v>
       </c>
       <c r="L61" t="n">
-        <v>5.95096697411485</v>
+        <v>5.95238378667936</v>
       </c>
       <c r="M61" t="n">
-        <v>-7.08230075997383</v>
+        <v>-7.08922704643679</v>
       </c>
       <c r="N61" t="s">
         <v>72</v>
@@ -10348,10 +10351,10 @@
         <v>0.169331339660101</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.62964402893857</v>
+        <v>2.62992637923552</v>
       </c>
       <c r="R61" t="n">
-        <v>1.70531258691017</v>
+        <v>1.70569643337942</v>
       </c>
       <c r="S61" t="n">
         <v>-0.9</v>
@@ -10480,13 +10483,13 @@
         <v>189</v>
       </c>
       <c r="K62" t="n">
-        <v>10.620779170522</v>
+        <v>10.6355862046406</v>
       </c>
       <c r="L62" t="n">
-        <v>8.41164101270082</v>
+        <v>8.46289244309046</v>
       </c>
       <c r="M62" t="n">
-        <v>26.2628677862692</v>
+        <v>25.6731817893304</v>
       </c>
       <c r="N62" t="s">
         <v>72</v>
@@ -10498,10 +10501,10 @@
         <v>0.15651704457591</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.70391152728274</v>
+        <v>4.71055205656723</v>
       </c>
       <c r="R62" t="n">
-        <v>2.77496698055925</v>
+        <v>2.77577988749165</v>
       </c>
       <c r="S62" t="n">
         <v>-2</v>
@@ -10628,13 +10631,13 @@
         <v>98</v>
       </c>
       <c r="K63" t="n">
-        <v>11.9462969205645</v>
+        <v>11.949159155491</v>
       </c>
       <c r="L63" t="n">
-        <v>9.70084392278591</v>
+        <v>9.71403593977659</v>
       </c>
       <c r="M63" t="n">
-        <v>23.1469861349316</v>
+        <v>23.0092129530027</v>
       </c>
       <c r="N63" t="s">
         <v>72</v>
@@ -10646,10 +10649,10 @@
         <v>0.152260572340975</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.21432569255141</v>
+        <v>5.21658513567557</v>
       </c>
       <c r="R63" t="n">
-        <v>3.02705383766781</v>
+        <v>3.02833529123943</v>
       </c>
       <c r="S63" t="n">
         <v>-2.2</v>
@@ -10776,13 +10779,13 @@
         <v>119</v>
       </c>
       <c r="K64" t="n">
-        <v>13.1794528755032</v>
+        <v>13.1750334851859</v>
       </c>
       <c r="L64" t="n">
-        <v>10.025664160401</v>
+        <v>10.0116127740515</v>
       </c>
       <c r="M64" t="n">
-        <v>31.457155003844</v>
+        <v>31.5975136327042</v>
       </c>
       <c r="N64" t="s">
         <v>72</v>
@@ -10794,10 +10797,10 @@
         <v>0.16915966966937</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.91108795484046</v>
+        <v>5.90449331509716</v>
       </c>
       <c r="R64" t="n">
-        <v>3.44685233820473</v>
+        <v>3.44488053743537</v>
       </c>
       <c r="S64" t="n">
         <v>-2.4</v>
@@ -10924,13 +10927,13 @@
         <v>158</v>
       </c>
       <c r="K65" t="n">
-        <v>2.61345140839034</v>
+        <v>2.61250181106024</v>
       </c>
       <c r="L65" t="n">
-        <v>2.94426943798393</v>
+        <v>2.9466984884646</v>
       </c>
       <c r="M65" t="n">
-        <v>-11.2359971314348</v>
+        <v>-11.3413937229285</v>
       </c>
       <c r="N65" t="s">
         <v>87</v>
@@ -10942,10 +10945,10 @@
         <v>0.200056801394905</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.49909340035418</v>
+        <v>1.4989227829422</v>
       </c>
       <c r="R65" t="n">
-        <v>1.20140967120381</v>
+        <v>1.20142477454455</v>
       </c>
       <c r="S65" t="n">
         <v>0.3</v>
@@ -11072,13 +11075,13 @@
         <v>65</v>
       </c>
       <c r="K66" t="n">
-        <v>3.2005043311507</v>
+        <v>3.20243159824429</v>
       </c>
       <c r="L66" t="n">
-        <v>3.28724977812839</v>
+        <v>3.28768204082974</v>
       </c>
       <c r="M66" t="n">
-        <v>-2.63884562575215</v>
+        <v>-2.59302577094541</v>
       </c>
       <c r="N66" t="s">
         <v>72</v>
@@ -11090,10 +11093,10 @@
         <v>0.204075782482982</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.66758216171773</v>
+        <v>1.66813073735846</v>
       </c>
       <c r="R66" t="n">
-        <v>1.26821813094542</v>
+        <v>1.26847514866947</v>
       </c>
       <c r="S66" t="n">
         <v>-0.3</v>
@@ -11222,13 +11225,13 @@
         <v>197</v>
       </c>
       <c r="K67" t="n">
-        <v>12.0792604497879</v>
+        <v>12.0864189011847</v>
       </c>
       <c r="L67" t="n">
-        <v>10.6971868649053</v>
+        <v>10.7040565128974</v>
       </c>
       <c r="M67" t="n">
-        <v>12.9199723472788</v>
+        <v>12.9143786434776</v>
       </c>
       <c r="N67" t="s">
         <v>72</v>
@@ -11240,10 +11243,10 @@
         <v>0.176874647064087</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.05960490509439</v>
+        <v>5.06105324765526</v>
       </c>
       <c r="R67" t="n">
-        <v>2.72498367812946</v>
+        <v>2.7253072245759</v>
       </c>
       <c r="S67" t="n">
         <v>-2.3</v>
@@ -11372,13 +11375,13 @@
         <v>133</v>
       </c>
       <c r="K68" t="n">
-        <v>15.7874233562349</v>
+        <v>15.7914626832629</v>
       </c>
       <c r="L68" t="n">
-        <v>12.7707827863619</v>
+        <v>12.7903824018417</v>
       </c>
       <c r="M68" t="n">
-        <v>23.6214225888688</v>
+        <v>23.4635696348617</v>
       </c>
       <c r="N68" t="s">
         <v>72</v>
@@ -11390,10 +11393,10 @@
         <v>0.193308968305331</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.62639040931285</v>
+        <v>6.63165584275302</v>
       </c>
       <c r="R68" t="n">
-        <v>3.56213021213569</v>
+        <v>3.56479686565746</v>
       </c>
       <c r="S68" t="n">
         <v>-2.7</v>
@@ -11522,13 +11525,13 @@
         <v>178</v>
       </c>
       <c r="K69" t="n">
-        <v>17.1252213715053</v>
+        <v>17.1132095361183</v>
       </c>
       <c r="L69" t="n">
-        <v>14.3627746660922</v>
+        <v>14.3298466829059</v>
       </c>
       <c r="M69" t="n">
-        <v>19.2333777395723</v>
+        <v>19.423535469732</v>
       </c>
       <c r="N69" t="s">
         <v>72</v>
@@ -11540,10 +11543,10 @@
         <v>0.187308054133596</v>
       </c>
       <c r="Q69" t="n">
-        <v>7.08655084406901</v>
+        <v>7.08277921773334</v>
       </c>
       <c r="R69" t="n">
-        <v>3.78565910146882</v>
+        <v>3.78510768242019</v>
       </c>
       <c r="S69" t="n">
         <v>-2.8</v>
@@ -11672,13 +11675,13 @@
         <v>107</v>
       </c>
       <c r="K70" t="n">
-        <v>17.7366606574657</v>
+        <v>17.7349381203695</v>
       </c>
       <c r="L70" t="n">
-        <v>18.7597073719752</v>
+        <v>18.7245834113462</v>
       </c>
       <c r="M70" t="n">
-        <v>-5.45342576098957</v>
+        <v>-5.28527267729247</v>
       </c>
       <c r="N70" t="s">
         <v>72</v>
@@ -11690,10 +11693,10 @@
         <v>0.201523936890671</v>
       </c>
       <c r="Q70" t="n">
-        <v>7.47889006262495</v>
+        <v>7.47945550184692</v>
       </c>
       <c r="R70" t="n">
-        <v>3.93397608342196</v>
+        <v>3.93353379334898</v>
       </c>
       <c r="S70" t="n">
         <v>-2.7</v>
@@ -11822,13 +11825,13 @@
         <v>135</v>
       </c>
       <c r="K71" t="n">
-        <v>26.9422294548463</v>
+        <v>26.8913219337702</v>
       </c>
       <c r="L71" t="n">
-        <v>19.9497307001795</v>
+        <v>19.854675402025</v>
       </c>
       <c r="M71" t="n">
-        <v>35.0505922097677</v>
+        <v>35.4407533201351</v>
       </c>
       <c r="N71" t="s">
         <v>72</v>
@@ -11840,10 +11843,10 @@
         <v>0.176808714571014</v>
       </c>
       <c r="Q71" t="n">
-        <v>10.6667283323929</v>
+        <v>10.6405409936831</v>
       </c>
       <c r="R71" t="n">
-        <v>5.48292504330238</v>
+        <v>5.472640563229</v>
       </c>
       <c r="S71" t="n">
         <v>-3.6</v>
@@ -11970,13 +11973,13 @@
         <v>203</v>
       </c>
       <c r="K72" t="n">
-        <v>145.029922719217</v>
+        <v>145.083301249066</v>
       </c>
       <c r="L72" t="n">
         <v>88.4244031830239</v>
       </c>
       <c r="M72" t="n">
-        <v>64.015721337727</v>
+        <v>64.0760876256837</v>
       </c>
       <c r="N72" t="s">
         <v>72</v>
@@ -11988,10 +11991,10 @@
         <v>0.204477307697909</v>
       </c>
       <c r="Q72" t="n">
-        <v>61.9869481876659</v>
+        <v>61.9796619040947</v>
       </c>
       <c r="R72" t="n">
-        <v>32.5774770478332</v>
+        <v>32.5626384006225</v>
       </c>
       <c r="S72" t="n">
         <v>-6.3</v>
@@ -12118,13 +12121,13 @@
         <v>71</v>
       </c>
       <c r="K73" t="n">
-        <v>1.42576254697926</v>
+        <v>1.42568764365249</v>
       </c>
       <c r="L73" t="n">
-        <v>1.51067204422894</v>
+        <v>1.5091674589162</v>
       </c>
       <c r="M73" t="n">
-        <v>-5.62064397590775</v>
+        <v>-5.53151439692878</v>
       </c>
       <c r="N73" t="s">
         <v>72</v>
@@ -12136,10 +12139,10 @@
         <v>0.186486154555426</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.11773363039239</v>
+        <v>1.11758563209266</v>
       </c>
       <c r="R73" t="n">
-        <v>1.05076625241576</v>
+        <v>1.05067551502925</v>
       </c>
       <c r="S73" t="n">
         <v>3.7</v>
@@ -12268,13 +12271,13 @@
         <v>207</v>
       </c>
       <c r="K74" t="n">
-        <v>14.4563064562216</v>
+        <v>14.4715562789762</v>
       </c>
       <c r="L74" t="n">
-        <v>12.4434490481523</v>
+        <v>12.5370440015043</v>
       </c>
       <c r="M74" t="n">
-        <v>16.1760409053805</v>
+        <v>15.4303700077926</v>
       </c>
       <c r="N74" t="s">
         <v>72</v>
@@ -12286,10 +12289,10 @@
         <v>0.196897477500637</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.80662754715138</v>
+        <v>3.80590079731766</v>
       </c>
       <c r="R74" t="n">
-        <v>2.13377802582125</v>
+        <v>2.13338817700755</v>
       </c>
       <c r="S74" t="n">
         <v>-3.7</v>
@@ -12418,13 +12421,13 @@
         <v>135</v>
       </c>
       <c r="K75" t="n">
-        <v>15.5279408296291</v>
+        <v>15.5179964950957</v>
       </c>
       <c r="L75" t="n">
-        <v>13.2513581555585</v>
+        <v>13.2478473970062</v>
       </c>
       <c r="M75" t="n">
-        <v>17.1799950416076</v>
+        <v>17.1359846627047</v>
       </c>
       <c r="N75" t="s">
         <v>72</v>
@@ -12436,10 +12439,10 @@
         <v>0.179917480381816</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.00621232358298</v>
+        <v>4.00714957693747</v>
       </c>
       <c r="R75" t="n">
-        <v>2.19430547321047</v>
+        <v>2.19484550679278</v>
       </c>
       <c r="S75" t="n">
         <v>-3.8</v>
@@ -12566,7 +12569,7 @@
         <v>146</v>
       </c>
       <c r="K76" t="n">
-        <v>18.1386638846393</v>
+        <v>18.1588047397249</v>
       </c>
       <c r="L76"/>
       <c r="M76"/>
@@ -12580,10 +12583,10 @@
         <v>0.242473165911646</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.2442143427743</v>
+        <v>5.24669529846235</v>
       </c>
       <c r="R76" t="n">
-        <v>2.88166811718963</v>
+        <v>2.88190473823281</v>
       </c>
       <c r="S76" t="n">
         <v>-4.1</v>
@@ -12692,13 +12695,13 @@
         <v>211</v>
       </c>
       <c r="K77" t="n">
-        <v>18.9857037836858</v>
+        <v>18.9666375166154</v>
       </c>
       <c r="L77" t="n">
-        <v>15.090991398823</v>
+        <v>15.0818881013422</v>
       </c>
       <c r="M77" t="n">
-        <v>25.8081943189401</v>
+        <v>25.757712755656</v>
       </c>
       <c r="N77" t="s">
         <v>72</v>
@@ -12710,10 +12713,10 @@
         <v>0.186040305258737</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.07024672913352</v>
+        <v>5.070159866877</v>
       </c>
       <c r="R77" t="n">
-        <v>2.69671980164843</v>
+        <v>2.69716248581431</v>
       </c>
       <c r="S77" t="n">
         <v>-4.2</v>
@@ -12842,13 +12845,13 @@
         <v>213</v>
       </c>
       <c r="K78" t="n">
-        <v>29.7338649247341</v>
+        <v>29.7292249842517</v>
       </c>
       <c r="L78" t="n">
-        <v>25.2481696541277</v>
+        <v>25.2609244758777</v>
       </c>
       <c r="M78" t="n">
-        <v>17.7664176534595</v>
+        <v>17.6885866257225</v>
       </c>
       <c r="N78" t="s">
         <v>72</v>
@@ -12860,10 +12863,10 @@
         <v>0.185498016566022</v>
       </c>
       <c r="Q78" t="n">
-        <v>7.91022394447439</v>
+        <v>7.91003281367375</v>
       </c>
       <c r="R78" t="n">
-        <v>4.00495589855957</v>
+        <v>4.00517352356035</v>
       </c>
       <c r="S78" t="n">
         <v>-4.9</v>
@@ -12990,13 +12993,13 @@
         <v>133</v>
       </c>
       <c r="K79" t="n">
-        <v>60.9389190215425</v>
+        <v>60.9579298629431</v>
       </c>
       <c r="L79" t="n">
-        <v>57.9085118702953</v>
+        <v>58.110400929692</v>
       </c>
       <c r="M79" t="n">
-        <v>5.23309450264373</v>
+        <v>4.90020527770292</v>
       </c>
       <c r="N79" t="s">
         <v>72</v>
@@ -13008,10 +13011,10 @@
         <v>0.218708528504461</v>
       </c>
       <c r="Q79" t="n">
-        <v>18.1375915823205</v>
+        <v>18.1533328687357</v>
       </c>
       <c r="R79" t="n">
-        <v>9.24159276038776</v>
+        <v>9.23881713158701</v>
       </c>
       <c r="S79" t="n">
         <v>-6.1</v>
@@ -13140,13 +13143,13 @@
         <v>104</v>
       </c>
       <c r="K80" t="n">
-        <v>138.825030913702</v>
+        <v>138.770226641641</v>
       </c>
       <c r="L80" t="n">
         <v>131.762845849802</v>
       </c>
       <c r="M80" t="n">
-        <v>5.35976968192557</v>
+        <v>5.31817656687987</v>
       </c>
       <c r="N80" t="s">
         <v>72</v>
@@ -13158,10 +13161,10 @@
         <v>0.195302281898581</v>
       </c>
       <c r="Q80" t="n">
-        <v>42.4588293048347</v>
+        <v>42.4204930523957</v>
       </c>
       <c r="R80" t="n">
-        <v>20.7481858688355</v>
+        <v>20.7418533991266</v>
       </c>
       <c r="S80" t="n">
         <v>-7.7</v>
@@ -13288,13 +13291,13 @@
         <v>146</v>
       </c>
       <c r="K81" t="n">
-        <v>3.25976824275553</v>
+        <v>3.26023336542828</v>
       </c>
       <c r="L81" t="n">
-        <v>3.66312589282444</v>
+        <v>3.66098034191163</v>
       </c>
       <c r="M81" t="n">
-        <v>-11.0112964137823</v>
+        <v>-10.9464389058723</v>
       </c>
       <c r="N81" t="s">
         <v>72</v>
@@ -13306,10 +13309,10 @@
         <v>0.191305642174389</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.82248622515463</v>
+        <v>1.82274160229602</v>
       </c>
       <c r="R81" t="n">
-        <v>1.36618621226784</v>
+        <v>1.36634884087988</v>
       </c>
       <c r="S81" t="n">
         <v>0.5</v>
@@ -13438,13 +13441,13 @@
         <v>65</v>
       </c>
       <c r="K82" t="n">
-        <v>4.60579601276758</v>
+        <v>4.60518026234466</v>
       </c>
       <c r="L82" t="n">
-        <v>4.75657550535077</v>
+        <v>4.74619144796165</v>
       </c>
       <c r="M82" t="n">
-        <v>-3.16991693737607</v>
+        <v>-2.97103871942537</v>
       </c>
       <c r="N82" t="s">
         <v>72</v>
@@ -13456,10 +13459,10 @@
         <v>0.195837315289254</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.3494075767166</v>
+        <v>2.34965851080151</v>
       </c>
       <c r="R82" t="n">
-        <v>1.62656304490083</v>
+        <v>1.62636466371309</v>
       </c>
       <c r="S82" t="n">
         <v>-0.5</v>
@@ -13586,13 +13589,13 @@
         <v>104</v>
       </c>
       <c r="K83" t="n">
-        <v>6.2733900278677</v>
+        <v>6.26860830615637</v>
       </c>
       <c r="L83" t="n">
-        <v>5.55501860800978</v>
+        <v>5.55316786051419</v>
       </c>
       <c r="M83" t="n">
-        <v>12.9319354362217</v>
+        <v>12.88346514301</v>
       </c>
       <c r="N83" t="s">
         <v>72</v>
@@ -13604,13 +13607,13 @@
         <v>0.183952932417733</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.02439782543252</v>
+        <v>3.02275169971118</v>
       </c>
       <c r="R83" t="n">
-        <v>1.96957867717729</v>
+        <v>1.96878183584156</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="T83" t="n">
         <v>105.658343200874</v>
@@ -13734,13 +13737,13 @@
         <v>121</v>
       </c>
       <c r="K84" t="n">
-        <v>7.31440774195679</v>
+        <v>7.31885745743246</v>
       </c>
       <c r="L84" t="n">
-        <v>6.48932580624229</v>
+        <v>6.51893618408187</v>
       </c>
       <c r="M84" t="n">
-        <v>12.7144476999571</v>
+        <v>12.2707333031401</v>
       </c>
       <c r="N84" t="s">
         <v>72</v>
@@ -13752,10 +13755,10 @@
         <v>0.182998837599141</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.4525064594264</v>
+        <v>3.45290730342232</v>
       </c>
       <c r="R84" t="n">
-        <v>2.19610382756051</v>
+        <v>2.19621416066072</v>
       </c>
       <c r="S84" t="n">
         <v>-1.3</v>
@@ -13882,13 +13885,13 @@
         <v>189</v>
       </c>
       <c r="K85" t="n">
-        <v>11.037133029547</v>
+        <v>11.0432042239065</v>
       </c>
       <c r="L85" t="n">
-        <v>8.65786511990304</v>
+        <v>8.67137778548513</v>
       </c>
       <c r="M85" t="n">
-        <v>27.480999954301</v>
+        <v>27.3523596491384</v>
       </c>
       <c r="N85" t="s">
         <v>72</v>
@@ -13900,10 +13903,10 @@
         <v>0.159247618432818</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.89592216369355</v>
+        <v>4.89682218560636</v>
       </c>
       <c r="R85" t="n">
-        <v>2.9296446609747</v>
+        <v>2.9310014518891</v>
       </c>
       <c r="S85" t="n">
         <v>-1.9</v>
@@ -14030,13 +14033,13 @@
         <v>223</v>
       </c>
       <c r="K86" t="n">
-        <v>16.6261599295867</v>
+        <v>16.6280023409634</v>
       </c>
       <c r="L86" t="n">
-        <v>22.8378625256908</v>
+        <v>22.7858282068808</v>
       </c>
       <c r="M86" t="n">
-        <v>-27.1991417284188</v>
+        <v>-27.0248059890923</v>
       </c>
       <c r="N86" t="s">
         <v>72</v>
@@ -14048,10 +14051,10 @@
         <v>0.181921231719556</v>
       </c>
       <c r="Q86" t="n">
-        <v>7.41816814524963</v>
+        <v>7.4200224160809</v>
       </c>
       <c r="R86" t="n">
-        <v>4.33641810140672</v>
+        <v>4.33673977240522</v>
       </c>
       <c r="S86" t="n">
         <v>-2.1</v>
@@ -14180,13 +14183,13 @@
         <v>133</v>
       </c>
       <c r="K87" t="n">
-        <v>34.1966220505981</v>
+        <v>34.158381593448</v>
       </c>
       <c r="L87" t="n">
-        <v>42.7928968763372</v>
+        <v>42.6105666808692</v>
       </c>
       <c r="M87" t="n">
-        <v>-20.0880881015852</v>
+        <v>-19.8358898878854</v>
       </c>
       <c r="N87" t="s">
         <v>72</v>
@@ -14198,10 +14201,10 @@
         <v>0.170352817282645</v>
       </c>
       <c r="Q87" t="n">
-        <v>15.0795370963412</v>
+        <v>15.068829030837</v>
       </c>
       <c r="R87" t="n">
-        <v>8.45851754155013</v>
+        <v>8.45818665383946</v>
       </c>
       <c r="S87" t="n">
         <v>-3.1</v>
@@ -18928,28 +18931,28 @@
         <v>291</v>
       </c>
       <c r="K120" t="n">
-        <v>1.81901005451654</v>
+        <v>2.41853704994452</v>
       </c>
       <c r="L120" t="n">
-        <v>2.17507992779312</v>
+        <v>3.05619900375882</v>
       </c>
       <c r="M120" t="n">
-        <v>-16.3704270692186</v>
+        <v>-20.8645429512294</v>
       </c>
       <c r="N120" t="s">
         <v>72</v>
       </c>
       <c r="O120" t="n">
-        <v>0.218725735639998</v>
+        <v>0.214643316740399</v>
       </c>
       <c r="P120" t="n">
-        <v>0.219127752528009</v>
+        <v>0.2150378301614</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.20995661257853</v>
+        <v>1.45919672373068</v>
       </c>
       <c r="R120" t="n">
-        <v>1.07610033299256</v>
+        <v>1.18288323529519</v>
       </c>
       <c r="S120" t="n">
         <v>1.3</v>
@@ -19069,7 +19072,7 @@
         <v>126</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I121" t="s">
         <v>292</v>
@@ -19078,85 +19081,85 @@
         <v>293</v>
       </c>
       <c r="K121" t="n">
-        <v>4.23381389247458</v>
+        <v>5.38104154804863</v>
       </c>
       <c r="L121" t="n">
-        <v>4.0609087586795</v>
+        <v>4.65261688764829</v>
       </c>
       <c r="M121" t="n">
-        <v>4.25779410644298</v>
+        <v>15.6562355764592</v>
       </c>
       <c r="N121" t="s">
         <v>72</v>
       </c>
       <c r="O121" t="n">
-        <v>0.219526813034275</v>
+        <v>0.228089782950901</v>
       </c>
       <c r="P121" t="n">
-        <v>0.219930302298823</v>
+        <v>0.228509010914454</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.70186439257116</v>
+        <v>2.48494530752078</v>
       </c>
       <c r="R121" t="n">
-        <v>1.24640369903518</v>
+        <v>1.6164025091129</v>
       </c>
       <c r="S121" t="n">
         <v>-1.3</v>
       </c>
       <c r="T121" t="n">
-        <v>101.255844892457</v>
+        <v>103.605545947297</v>
       </c>
       <c r="U121" t="n">
-        <v>104.077119217106</v>
+        <v>103.605545947297</v>
       </c>
       <c r="V121" t="n">
-        <v>104.199082826953</v>
+        <v>103.964099392494</v>
       </c>
       <c r="W121" t="n">
-        <v>105.018947433678</v>
+        <v>103.130133501371</v>
       </c>
       <c r="X121" t="n">
-        <v>100.736880385705</v>
+        <v>95.1131881159502</v>
       </c>
       <c r="Y121" t="n">
-        <v>105.048142128313</v>
+        <v>103.642456724651</v>
       </c>
       <c r="Z121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>103.669753494035</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>103.341643187035</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>103.341643187035</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>103.341643187035</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>217</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH121" t="n">
         <v>10</v>
       </c>
-      <c r="AA121" t="n">
-        <v>105.048142128313</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>104.077119217106</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>104.323107043656</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>108.266260597671</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>98</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>15</v>
-      </c>
       <c r="AI121" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AJ121" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="AK121" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
@@ -19219,7 +19222,7 @@
         <v>126</v>
       </c>
       <c r="H122" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I122" t="s">
         <v>294</v>
@@ -19228,75 +19231,85 @@
         <v>295</v>
       </c>
       <c r="K122" t="n">
-        <v>16.5138304335828</v>
+        <v>5.7601428357267</v>
       </c>
       <c r="L122" t="n">
-        <v>12.8231824592897</v>
+        <v>6.01407180227314</v>
       </c>
       <c r="M122" t="n">
-        <v>28.7810610666272</v>
+        <v>-4.22224700494025</v>
       </c>
       <c r="N122" t="s">
         <v>72</v>
       </c>
       <c r="O122" t="n">
-        <v>0.268895322062865</v>
+        <v>0.215429442380211</v>
       </c>
       <c r="P122" t="n">
-        <v>0.250173595419795</v>
+        <v>0.215825400696493</v>
       </c>
       <c r="Q122" t="n">
-        <v>6.32000870318953</v>
+        <v>2.59604976675609</v>
       </c>
       <c r="R122" t="n">
-        <v>3.04013960851606</v>
+        <v>1.65282397205083</v>
       </c>
       <c r="S122" t="n">
-        <v>-3.4</v>
+        <v>-1.3</v>
       </c>
       <c r="T122" t="n">
-        <v>102.179892912761</v>
+        <v>101.255844892457</v>
       </c>
       <c r="U122" t="n">
-        <v>101.602636510187</v>
+        <v>104.077119217106</v>
       </c>
       <c r="V122" t="n">
-        <v>100.102187043833</v>
+        <v>104.199082826953</v>
       </c>
       <c r="W122" t="n">
-        <v>101.323096565154</v>
+        <v>105.018947433678</v>
       </c>
       <c r="X122" t="n">
-        <v>100.881699689764</v>
+        <v>100.736880385705</v>
       </c>
       <c r="Y122" t="n">
-        <v>100.67212219852</v>
+        <v>105.048142128313</v>
       </c>
       <c r="Z122" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA122"/>
-      <c r="AB122"/>
-      <c r="AC122"/>
-      <c r="AD122"/>
+        <v>10</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>105.048142128313</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>104.077119217106</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>104.323107043656</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>108.266260597671</v>
+      </c>
       <c r="AE122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF122"/>
+        <v>10</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>98</v>
+      </c>
       <c r="AG122" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AH122" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ122" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AK122" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
@@ -19311,7 +19324,7 @@
         <v>1</v>
       </c>
       <c r="AP122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AQ122" t="s">
         <v>129</v>
@@ -19359,88 +19372,88 @@
         <v>126</v>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123" t="s">
         <v>296</v>
       </c>
       <c r="J123" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="K123" t="n">
-        <v>24.6013240801013</v>
+        <v>9.42907747013126</v>
       </c>
       <c r="L123" t="n">
-        <v>18.6199962762986</v>
+        <v>7.30251916757941</v>
       </c>
       <c r="M123" t="n">
-        <v>32.1231417828813</v>
+        <v>29.120886282545</v>
       </c>
       <c r="N123" t="s">
         <v>72</v>
       </c>
       <c r="O123" t="n">
-        <v>0.200052394741294</v>
+        <v>0.220734265627762</v>
       </c>
       <c r="P123" t="n">
-        <v>0.20042009011531</v>
+        <v>0.208332392121718</v>
       </c>
       <c r="Q123" t="n">
-        <v>8.53931987708725</v>
+        <v>4.13875764291549</v>
       </c>
       <c r="R123" t="n">
-        <v>3.81597218128006</v>
+        <v>2.45308652390068</v>
       </c>
       <c r="S123" t="n">
-        <v>-3.8</v>
+        <v>-2.3</v>
       </c>
       <c r="T123" t="n">
-        <v>97.1797219228692</v>
+        <v>104.558982642207</v>
       </c>
       <c r="U123" t="n">
-        <v>97.1797219228692</v>
+        <v>102.817771556793</v>
       </c>
       <c r="V123" t="n">
-        <v>97.1797219228692</v>
+        <v>99.2301332394831</v>
       </c>
       <c r="W123" t="n">
-        <v>103.101668230153</v>
+        <v>103.083419603713</v>
       </c>
       <c r="X123" t="n">
-        <v>98.0982391540476</v>
+        <v>98.5428857453734</v>
       </c>
       <c r="Y123" t="n">
-        <v>97.3164565383449</v>
+        <v>99.8125817462865</v>
       </c>
       <c r="Z123" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA123" t="n">
-        <v>98.5119400345742</v>
+        <v>99.2301332394831</v>
       </c>
       <c r="AB123" t="n">
-        <v>100.65610265142</v>
+        <v>99.2301332394831</v>
       </c>
       <c r="AC123" t="n">
-        <v>98.4265179639656</v>
+        <v>99.2301332394831</v>
       </c>
       <c r="AD123" t="n">
-        <v>100.839894696788</v>
+        <v>99.2301332394831</v>
       </c>
       <c r="AE123" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AF123" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AG123" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AH123" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AI123" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AJ123" t="n">
         <v>17</v>
@@ -19509,61 +19522,61 @@
         <v>126</v>
       </c>
       <c r="H124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I124" t="s">
         <v>297</v>
       </c>
       <c r="J124" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="K124" t="n">
-        <v>26.5571979155157</v>
+        <v>22.8286113551675</v>
       </c>
       <c r="L124" t="n">
-        <v>15.3175065094195</v>
+        <v>19.0165430690245</v>
       </c>
       <c r="M124" t="n">
-        <v>73.3780749444064</v>
+        <v>20.0460634317515</v>
       </c>
       <c r="N124" t="s">
         <v>72</v>
       </c>
       <c r="O124" t="n">
-        <v>0.268376028428921</v>
+        <v>0.263876510071714</v>
       </c>
       <c r="P124" t="n">
-        <v>0.249690457392381</v>
+        <v>0.245504216157523</v>
       </c>
       <c r="Q124" t="n">
-        <v>10.6459526841878</v>
+        <v>9.93141013749459</v>
       </c>
       <c r="R124" t="n">
-        <v>5.36000863038986</v>
+        <v>5.60488802939449</v>
       </c>
       <c r="S124" t="n">
-        <v>-4.7</v>
+        <v>-3.5</v>
       </c>
       <c r="T124" t="n">
-        <v>94.7166875566949</v>
+        <v>102.179892912761</v>
       </c>
       <c r="U124" t="n">
-        <v>95.8145063799703</v>
+        <v>101.602636510187</v>
       </c>
       <c r="V124" t="n">
-        <v>95.8145063799703</v>
+        <v>100.102187043833</v>
       </c>
       <c r="W124" t="n">
-        <v>102.22962505915</v>
+        <v>101.323096565154</v>
       </c>
       <c r="X124" t="n">
-        <v>98.4541869098614</v>
+        <v>100.881699689764</v>
       </c>
       <c r="Y124" t="n">
-        <v>96.8376420433072</v>
+        <v>100.67212219852</v>
       </c>
       <c r="Z124" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AA124"/>
       <c r="AB124"/>
@@ -19574,19 +19587,19 @@
       </c>
       <c r="AF124"/>
       <c r="AG124" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AH124" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
       </c>
       <c r="AJ124" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="AK124" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AL124" t="n">
         <v>0</v>
@@ -19601,7 +19614,7 @@
         <v>1</v>
       </c>
       <c r="AP124" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AQ124" t="s">
         <v>129</v>
@@ -19649,94 +19662,94 @@
         <v>126</v>
       </c>
       <c r="H125" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I125" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J125" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="K125" t="n">
-        <v>30.6074088758334</v>
+        <v>35.7109890780377</v>
       </c>
       <c r="L125" t="n">
-        <v>24.1740391588107</v>
+        <v>30.0775939849624</v>
       </c>
       <c r="M125" t="n">
-        <v>26.6127215016027</v>
+        <v>18.7295403212497</v>
       </c>
       <c r="N125" t="s">
         <v>72</v>
       </c>
       <c r="O125" t="n">
-        <v>0.203232222144609</v>
+        <v>0.196318505472103</v>
       </c>
       <c r="P125" t="n">
-        <v>0.203605762026649</v>
+        <v>0.196679337974954</v>
       </c>
       <c r="Q125" t="n">
-        <v>10.4576893239488</v>
+        <v>14.4766002078416</v>
       </c>
       <c r="R125" t="n">
-        <v>4.62785206374769</v>
+        <v>7.58389099732437</v>
       </c>
       <c r="S125" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="T125" t="n">
-        <v>97.2189361420206</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="U125" t="n">
-        <v>97.2189361420206</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="V125" t="n">
         <v>97.1797219228692</v>
       </c>
       <c r="W125" t="n">
-        <v>102.065912808901</v>
+        <v>103.101668230153</v>
       </c>
       <c r="X125" t="n">
-        <v>98.8598447363989</v>
+        <v>98.0982391540476</v>
       </c>
       <c r="Y125" t="n">
-        <v>96.812068204534</v>
+        <v>97.3164565383449</v>
       </c>
       <c r="Z125" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AA125" t="n">
-        <v>97.6589794795881</v>
+        <v>98.5119400345742</v>
       </c>
       <c r="AB125" t="n">
-        <v>97.3822631487352</v>
+        <v>100.65610265142</v>
       </c>
       <c r="AC125" t="n">
-        <v>97.9194864056909</v>
+        <v>98.4265179639656</v>
       </c>
       <c r="AD125" t="n">
-        <v>98.7211772632021</v>
+        <v>100.839894696788</v>
       </c>
       <c r="AE125" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="AF125" t="n">
         <v>14</v>
       </c>
       <c r="AG125" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="AH125" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="AI125" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK125" t="n">
         <v>6</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>12</v>
       </c>
       <c r="AL125" t="n">
         <v>0</v>
@@ -19799,97 +19812,87 @@
         <v>126</v>
       </c>
       <c r="H126" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I126" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J126" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="K126" t="n">
-        <v>44.9163282760142</v>
+        <v>37.4147152054147</v>
       </c>
       <c r="L126" t="n">
-        <v>36.8082443871918</v>
+        <v>22.9113402061856</v>
       </c>
       <c r="M126" t="n">
-        <v>22.0279016937952</v>
+        <v>63.3021676982194</v>
       </c>
       <c r="N126" t="s">
         <v>72</v>
       </c>
       <c r="O126" t="n">
-        <v>0.224932531623054</v>
+        <v>0.263366908823257</v>
       </c>
       <c r="P126" t="n">
-        <v>0.21229478008661</v>
+        <v>0.245030095687226</v>
       </c>
       <c r="Q126" t="n">
-        <v>16.1285302885811</v>
+        <v>16.7498370156795</v>
       </c>
       <c r="R126" t="n">
-        <v>7.16010248756576</v>
+        <v>9.53695856747676</v>
       </c>
       <c r="S126" t="n">
         <v>-4.7</v>
       </c>
       <c r="T126" t="n">
-        <v>92.4330397803157</v>
+        <v>94.7166875566949</v>
       </c>
       <c r="U126" t="n">
-        <v>92.8249003896263</v>
+        <v>95.8145063799703</v>
       </c>
       <c r="V126" t="n">
-        <v>94.4745763645127</v>
+        <v>95.8145063799703</v>
       </c>
       <c r="W126" t="n">
-        <v>103.906504756181</v>
+        <v>102.22962505915</v>
       </c>
       <c r="X126" t="n">
-        <v>96.0827738671513</v>
+        <v>98.4541869098614</v>
       </c>
       <c r="Y126" t="n">
-        <v>94.98030271759</v>
+        <v>96.8376420433072</v>
       </c>
       <c r="Z126" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>92.8249003896263</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>92.8249003896263</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>92.8249003896263</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>92.8249003896263</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AA126"/>
+      <c r="AB126"/>
+      <c r="AC126"/>
+      <c r="AD126"/>
       <c r="AE126" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF126" t="n">
-        <v>28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF126"/>
       <c r="AG126" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AH126" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AI126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AK126" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AL126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM126" t="n">
         <v>0</v>
@@ -19949,97 +19952,97 @@
         <v>126</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I127" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J127" t="s">
         <v>241</v>
       </c>
       <c r="K127" t="n">
-        <v>49.350487642013</v>
+        <v>44.4585916285473</v>
       </c>
       <c r="L127" t="n">
-        <v>35.1028431028431</v>
+        <v>39.7330154946365</v>
       </c>
       <c r="M127" t="n">
-        <v>40.5882922287168</v>
+        <v>11.8933236631604</v>
       </c>
       <c r="N127" t="s">
         <v>72</v>
       </c>
       <c r="O127" t="n">
-        <v>0.201737846905621</v>
+        <v>0.19943898280648</v>
       </c>
       <c r="P127" t="n">
-        <v>0.2021086401329</v>
+        <v>0.199805550732204</v>
       </c>
       <c r="Q127" t="n">
-        <v>16.9369614651515</v>
+        <v>17.8637235273449</v>
       </c>
       <c r="R127" t="n">
-        <v>7.40142961493698</v>
+        <v>9.24675412617599</v>
       </c>
       <c r="S127" t="n">
-        <v>-4.8</v>
+        <v>-4.1</v>
       </c>
       <c r="T127" t="n">
-        <v>93.1388468453272</v>
+        <v>97.2189361420206</v>
       </c>
       <c r="U127" t="n">
-        <v>95.5308584446334</v>
+        <v>97.2189361420206</v>
       </c>
       <c r="V127" t="n">
-        <v>95.5308584446334</v>
+        <v>97.1797219228692</v>
       </c>
       <c r="W127" t="n">
-        <v>103.029006411032</v>
+        <v>102.065912808901</v>
       </c>
       <c r="X127" t="n">
-        <v>98.9894033744476</v>
+        <v>98.8598447363989</v>
       </c>
       <c r="Y127" t="n">
-        <v>95.9563345237125</v>
+        <v>96.812068204534</v>
       </c>
       <c r="Z127" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AA127" t="n">
-        <v>94.875414711859</v>
+        <v>97.6589794795881</v>
       </c>
       <c r="AB127" t="n">
-        <v>93.9437789698598</v>
+        <v>97.3822631487352</v>
       </c>
       <c r="AC127" t="n">
-        <v>95.4348205860085</v>
+        <v>97.9194864056909</v>
       </c>
       <c r="AD127" t="n">
-        <v>96.5160449854777</v>
+        <v>98.7211772632021</v>
       </c>
       <c r="AE127" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AF127" t="n">
         <v>14</v>
       </c>
       <c r="AG127" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AH127" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AI127" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AJ127" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AK127" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AL127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM127" t="n">
         <v>0</v>
@@ -20081,7 +20084,7 @@
         <v>46275</v>
       </c>
       <c r="B128" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C128" t="s">
         <v>226</v>
@@ -20093,7 +20096,7 @@
         <v>6</v>
       </c>
       <c r="F128" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G128" t="s">
         <v>126</v>
@@ -20102,10 +20105,10 @@
         <v>4</v>
       </c>
       <c r="I128" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J128" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K128" t="n">
         <v>2.78451002912125</v>
@@ -20231,7 +20234,7 @@
         <v>46275</v>
       </c>
       <c r="B129" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C129" t="s">
         <v>226</v>
@@ -20243,7 +20246,7 @@
         <v>6</v>
       </c>
       <c r="F129" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G129" t="s">
         <v>126</v>
@@ -20252,7 +20255,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J129" t="s">
         <v>245</v>
@@ -20381,7 +20384,7 @@
         <v>46275</v>
       </c>
       <c r="B130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C130" t="s">
         <v>226</v>
@@ -20393,7 +20396,7 @@
         <v>6</v>
       </c>
       <c r="F130" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G130" t="s">
         <v>126</v>
@@ -20402,7 +20405,7 @@
         <v>2</v>
       </c>
       <c r="I130" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J130" t="s">
         <v>283</v>
@@ -20531,7 +20534,7 @@
         <v>46275</v>
       </c>
       <c r="B131" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C131" t="s">
         <v>226</v>
@@ -20543,7 +20546,7 @@
         <v>6</v>
       </c>
       <c r="F131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G131" t="s">
         <v>126</v>
@@ -20552,10 +20555,10 @@
         <v>7</v>
       </c>
       <c r="I131" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J131" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K131" t="n">
         <v>8.11779105211661</v>
@@ -20671,7 +20674,7 @@
         <v>46275</v>
       </c>
       <c r="B132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C132" t="s">
         <v>226</v>
@@ -20683,7 +20686,7 @@
         <v>6</v>
       </c>
       <c r="F132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G132" t="s">
         <v>126</v>
@@ -20692,10 +20695,10 @@
         <v>8</v>
       </c>
       <c r="I132" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K132" t="n">
         <v>19.9010468794427</v>
@@ -20811,7 +20814,7 @@
         <v>46275</v>
       </c>
       <c r="B133" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C133" t="s">
         <v>226</v>
@@ -20823,7 +20826,7 @@
         <v>6</v>
       </c>
       <c r="F133" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G133" t="s">
         <v>126</v>
@@ -20832,10 +20835,10 @@
         <v>5</v>
       </c>
       <c r="I133" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J133" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K133" t="n">
         <v>20.2372202612462</v>
@@ -20937,7 +20940,7 @@
         <v>46275</v>
       </c>
       <c r="B134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C134" t="s">
         <v>226</v>
@@ -20949,7 +20952,7 @@
         <v>6</v>
       </c>
       <c r="F134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G134" t="s">
         <v>126</v>
@@ -20958,7 +20961,7 @@
         <v>3</v>
       </c>
       <c r="I134" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J134" t="s">
         <v>251</v>
@@ -21087,7 +21090,7 @@
         <v>46275</v>
       </c>
       <c r="B135" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C135" t="s">
         <v>226</v>
@@ -21099,7 +21102,7 @@
         <v>6</v>
       </c>
       <c r="F135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G135" t="s">
         <v>126</v>
@@ -21108,10 +21111,10 @@
         <v>6</v>
       </c>
       <c r="I135" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J135" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K135" t="n">
         <v>149.829520045</v>
@@ -21237,7 +21240,7 @@
         <v>46275</v>
       </c>
       <c r="B136" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C136" t="s">
         <v>226</v>
@@ -21249,19 +21252,19 @@
         <v>7</v>
       </c>
       <c r="F136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G136" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H136" t="n">
         <v>3</v>
       </c>
       <c r="I136" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J136" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K136" t="n">
         <v>3.03544572611321</v>
@@ -21387,7 +21390,7 @@
         <v>46275</v>
       </c>
       <c r="B137" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C137" t="s">
         <v>226</v>
@@ -21399,16 +21402,16 @@
         <v>7</v>
       </c>
       <c r="F137" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G137" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H137" t="n">
         <v>8</v>
       </c>
       <c r="I137" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J137" t="s">
         <v>251</v>
@@ -21537,7 +21540,7 @@
         <v>46275</v>
       </c>
       <c r="B138" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C138" t="s">
         <v>226</v>
@@ -21549,19 +21552,19 @@
         <v>7</v>
       </c>
       <c r="F138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G138" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H138" t="n">
         <v>1</v>
       </c>
       <c r="I138" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J138" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K138" t="n">
         <v>8.22290351976709</v>
@@ -21687,7 +21690,7 @@
         <v>46275</v>
       </c>
       <c r="B139" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C139" t="s">
         <v>226</v>
@@ -21699,16 +21702,16 @@
         <v>7</v>
       </c>
       <c r="F139" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G139" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H139" t="n">
         <v>4</v>
       </c>
       <c r="I139" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J139" t="s">
         <v>135</v>
@@ -21827,7 +21830,7 @@
         <v>46275</v>
       </c>
       <c r="B140" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C140" t="s">
         <v>226</v>
@@ -21839,19 +21842,19 @@
         <v>7</v>
       </c>
       <c r="F140" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G140" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H140" t="n">
         <v>6</v>
       </c>
       <c r="I140" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J140" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K140" t="n">
         <v>15.7931118632922</v>
@@ -21977,7 +21980,7 @@
         <v>46275</v>
       </c>
       <c r="B141" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C141" t="s">
         <v>226</v>
@@ -21989,19 +21992,19 @@
         <v>7</v>
       </c>
       <c r="F141" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G141" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H141" t="n">
         <v>2</v>
       </c>
       <c r="I141" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J141" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K141" t="n">
         <v>21.1053082219426</v>
@@ -22127,7 +22130,7 @@
         <v>46275</v>
       </c>
       <c r="B142" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C142" t="s">
         <v>226</v>
@@ -22139,19 +22142,19 @@
         <v>7</v>
       </c>
       <c r="F142" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G142" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H142" t="n">
         <v>5</v>
       </c>
       <c r="I142" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J142" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K142" t="n">
         <v>34.9405470887116</v>
@@ -22277,7 +22280,7 @@
         <v>46275</v>
       </c>
       <c r="B143" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C143" t="s">
         <v>226</v>
@@ -22289,16 +22292,16 @@
         <v>7</v>
       </c>
       <c r="F143" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G143" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H143" t="n">
         <v>7</v>
       </c>
       <c r="I143" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J143" t="s">
         <v>283</v>
@@ -22427,7 +22430,7 @@
         <v>46275</v>
       </c>
       <c r="B144" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C144" t="s">
         <v>226</v>
@@ -22439,19 +22442,19 @@
         <v>8</v>
       </c>
       <c r="F144" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G144" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H144" t="n">
         <v>1</v>
       </c>
       <c r="I144" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J144" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K144" t="n">
         <v>2.77718743021649</v>
@@ -22577,7 +22580,7 @@
         <v>46275</v>
       </c>
       <c r="B145" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C145" t="s">
         <v>226</v>
@@ -22589,16 +22592,16 @@
         <v>8</v>
       </c>
       <c r="F145" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H145" t="n">
         <v>3</v>
       </c>
       <c r="I145" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J145" t="s">
         <v>245</v>
@@ -22727,7 +22730,7 @@
         <v>46275</v>
       </c>
       <c r="B146" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C146" t="s">
         <v>226</v>
@@ -22739,16 +22742,16 @@
         <v>8</v>
       </c>
       <c r="F146" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G146" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H146" t="n">
         <v>8</v>
       </c>
       <c r="I146" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J146" t="s">
         <v>287</v>
@@ -22877,7 +22880,7 @@
         <v>46275</v>
       </c>
       <c r="B147" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C147" t="s">
         <v>226</v>
@@ -22889,19 +22892,19 @@
         <v>8</v>
       </c>
       <c r="F147" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G147" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H147" t="n">
         <v>7</v>
       </c>
       <c r="I147" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J147" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K147" t="n">
         <v>8.72999425186407</v>
@@ -23027,7 +23030,7 @@
         <v>46275</v>
       </c>
       <c r="B148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C148" t="s">
         <v>226</v>
@@ -23039,19 +23042,19 @@
         <v>8</v>
       </c>
       <c r="F148" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G148" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H148" t="n">
         <v>2</v>
       </c>
       <c r="I148" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J148" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K148" t="n">
         <v>11.4718544654461</v>
@@ -23177,7 +23180,7 @@
         <v>46275</v>
       </c>
       <c r="B149" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C149" t="s">
         <v>226</v>
@@ -23189,19 +23192,19 @@
         <v>8</v>
       </c>
       <c r="F149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G149" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H149" t="n">
         <v>4</v>
       </c>
       <c r="I149" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J149" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K149" t="n">
         <v>13.4584252714435</v>
@@ -23327,7 +23330,7 @@
         <v>46275</v>
       </c>
       <c r="B150" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C150" t="s">
         <v>226</v>
@@ -23339,19 +23342,19 @@
         <v>8</v>
       </c>
       <c r="F150" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H150" t="n">
         <v>6</v>
       </c>
       <c r="I150" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J150" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K150" t="n">
         <v>15.3631346945442</v>
@@ -23477,7 +23480,7 @@
         <v>46275</v>
       </c>
       <c r="B151" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C151" t="s">
         <v>226</v>
@@ -23489,19 +23492,19 @@
         <v>9</v>
       </c>
       <c r="F151" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G151" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H151" t="n">
         <v>1</v>
       </c>
       <c r="I151" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J151" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K151" t="n">
         <v>1.32085373323319</v>
@@ -23627,7 +23630,7 @@
         <v>46275</v>
       </c>
       <c r="B152" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C152" t="s">
         <v>226</v>
@@ -23639,16 +23642,16 @@
         <v>9</v>
       </c>
       <c r="F152" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G152" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H152" t="n">
         <v>6</v>
       </c>
       <c r="I152" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J152" t="s">
         <v>131</v>
@@ -23777,7 +23780,7 @@
         <v>46275</v>
       </c>
       <c r="B153" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C153" t="s">
         <v>226</v>
@@ -23789,16 +23792,16 @@
         <v>9</v>
       </c>
       <c r="F153" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G153" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H153" t="n">
         <v>5</v>
       </c>
       <c r="I153" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J153" t="s">
         <v>277</v>
@@ -23927,7 +23930,7 @@
         <v>46275</v>
       </c>
       <c r="B154" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" t="s">
         <v>226</v>
@@ -23939,19 +23942,19 @@
         <v>9</v>
       </c>
       <c r="F154" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G154" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H154" t="n">
         <v>8</v>
       </c>
       <c r="I154" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J154" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K154" t="n">
         <v>37.5474665366462</v>
@@ -24077,7 +24080,7 @@
         <v>46275</v>
       </c>
       <c r="B155" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C155" t="s">
         <v>226</v>
@@ -24089,16 +24092,16 @@
         <v>9</v>
       </c>
       <c r="F155" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G155" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H155" t="n">
         <v>7</v>
       </c>
       <c r="I155" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J155" t="s">
         <v>245</v>
@@ -24227,7 +24230,7 @@
         <v>46275</v>
       </c>
       <c r="B156" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C156" t="s">
         <v>226</v>
@@ -24239,19 +24242,19 @@
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G156" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H156" t="n">
         <v>3</v>
       </c>
       <c r="I156" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J156" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K156" t="n">
         <v>43.4808173725608</v>
@@ -24377,7 +24380,7 @@
         <v>46275</v>
       </c>
       <c r="B157" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C157" t="s">
         <v>226</v>
@@ -24389,16 +24392,16 @@
         <v>9</v>
       </c>
       <c r="F157" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G157" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H157" t="n">
         <v>4</v>
       </c>
       <c r="I157" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J157" t="s">
         <v>265</v>
@@ -24527,7 +24530,7 @@
         <v>46275</v>
       </c>
       <c r="B158" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C158" t="s">
         <v>226</v>
@@ -24539,19 +24542,19 @@
         <v>9</v>
       </c>
       <c r="F158" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G158" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H158" t="n">
         <v>2</v>
       </c>
       <c r="I158" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J158" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K158" t="n">
         <v>159.469696825063</v>
@@ -24677,7 +24680,7 @@
         <v>46275</v>
       </c>
       <c r="B159" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C159" t="s">
         <v>226</v>
@@ -24689,19 +24692,19 @@
         <v>10</v>
       </c>
       <c r="F159" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G159" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H159" t="n">
         <v>5</v>
       </c>
       <c r="I159" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J159" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K159" t="n">
         <v>3.58395657858519</v>
@@ -24827,7 +24830,7 @@
         <v>46275</v>
       </c>
       <c r="B160" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C160" t="s">
         <v>226</v>
@@ -24839,19 +24842,19 @@
         <v>10</v>
       </c>
       <c r="F160" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G160" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H160" t="n">
         <v>4</v>
       </c>
       <c r="I160" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J160" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K160" t="n">
         <v>5.02206171492511</v>
@@ -24977,7 +24980,7 @@
         <v>46275</v>
       </c>
       <c r="B161" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C161" t="s">
         <v>226</v>
@@ -24989,16 +24992,16 @@
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G161" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H161" t="n">
         <v>1</v>
       </c>
       <c r="I161" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J161" t="s">
         <v>131</v>
@@ -25127,7 +25130,7 @@
         <v>46275</v>
       </c>
       <c r="B162" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C162" t="s">
         <v>226</v>
@@ -25139,16 +25142,16 @@
         <v>10</v>
       </c>
       <c r="F162" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G162" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H162" t="n">
         <v>3</v>
       </c>
       <c r="I162" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J162" t="s">
         <v>291</v>
@@ -25277,7 +25280,7 @@
         <v>46275</v>
       </c>
       <c r="B163" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C163" t="s">
         <v>226</v>
@@ -25289,19 +25292,19 @@
         <v>10</v>
       </c>
       <c r="F163" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G163" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H163" t="n">
         <v>7</v>
       </c>
       <c r="I163" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J163" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K163" t="n">
         <v>9.29188355596786</v>
@@ -25427,7 +25430,7 @@
         <v>46275</v>
       </c>
       <c r="B164" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C164" t="s">
         <v>226</v>
@@ -25439,19 +25442,19 @@
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H164" t="n">
         <v>2</v>
       </c>
       <c r="I164" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J164" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K164" t="n">
         <v>17.7275879434238</v>
@@ -25577,7 +25580,7 @@
         <v>46275</v>
       </c>
       <c r="B165" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C165" t="s">
         <v>226</v>
@@ -25589,19 +25592,19 @@
         <v>10</v>
       </c>
       <c r="F165" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G165" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H165" t="n">
         <v>8</v>
       </c>
       <c r="I165" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J165" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K165" t="n">
         <v>24.8554887373151</v>
@@ -25725,7 +25728,7 @@
         <v>46275</v>
       </c>
       <c r="B166" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C166" t="s">
         <v>226</v>
@@ -25737,16 +25740,16 @@
         <v>10</v>
       </c>
       <c r="F166" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G166" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H166" t="n">
         <v>6</v>
       </c>
       <c r="I166" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J166" t="s">
         <v>283</v>
@@ -25875,7 +25878,7 @@
         <v>46275</v>
       </c>
       <c r="B167" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C167" t="s">
         <v>226</v>
@@ -25887,7 +25890,7 @@
         <v>11</v>
       </c>
       <c r="F167" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G167" t="s">
         <v>182</v>
@@ -25896,10 +25899,10 @@
         <v>6</v>
       </c>
       <c r="I167" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J167" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K167" t="n">
         <v>1.81141388161351</v>
@@ -26025,7 +26028,7 @@
         <v>46275</v>
       </c>
       <c r="B168" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C168" t="s">
         <v>226</v>
@@ -26037,7 +26040,7 @@
         <v>11</v>
       </c>
       <c r="F168" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G168" t="s">
         <v>182</v>
@@ -26046,7 +26049,7 @@
         <v>4</v>
       </c>
       <c r="I168" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J168" t="s">
         <v>277</v>
@@ -26175,7 +26178,7 @@
         <v>46275</v>
       </c>
       <c r="B169" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C169" t="s">
         <v>226</v>
@@ -26187,7 +26190,7 @@
         <v>11</v>
       </c>
       <c r="F169" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G169" t="s">
         <v>182</v>
@@ -26196,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="I169" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J169" t="s">
         <v>253</v>
@@ -26325,7 +26328,7 @@
         <v>46275</v>
       </c>
       <c r="B170" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C170" t="s">
         <v>226</v>
@@ -26337,7 +26340,7 @@
         <v>11</v>
       </c>
       <c r="F170" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G170" t="s">
         <v>182</v>
@@ -26346,7 +26349,7 @@
         <v>3</v>
       </c>
       <c r="I170" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J170" t="s">
         <v>251</v>
@@ -26475,7 +26478,7 @@
         <v>46275</v>
       </c>
       <c r="B171" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C171" t="s">
         <v>226</v>
@@ -26487,7 +26490,7 @@
         <v>11</v>
       </c>
       <c r="F171" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G171" t="s">
         <v>182</v>
@@ -26496,10 +26499,10 @@
         <v>8</v>
       </c>
       <c r="I171" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J171" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K171" t="n">
         <v>17.8661791793517</v>
@@ -26625,7 +26628,7 @@
         <v>46275</v>
       </c>
       <c r="B172" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C172" t="s">
         <v>226</v>
@@ -26637,7 +26640,7 @@
         <v>11</v>
       </c>
       <c r="F172" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G172" t="s">
         <v>182</v>
@@ -26646,10 +26649,10 @@
         <v>2</v>
       </c>
       <c r="I172" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J172" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K172" t="n">
         <v>41.3555104531547</v>
@@ -26775,7 +26778,7 @@
         <v>46275</v>
       </c>
       <c r="B173" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C173" t="s">
         <v>226</v>
@@ -26787,7 +26790,7 @@
         <v>11</v>
       </c>
       <c r="F173" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G173" t="s">
         <v>182</v>
@@ -26796,7 +26799,7 @@
         <v>7</v>
       </c>
       <c r="I173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J173" t="s">
         <v>255</v>
@@ -26925,7 +26928,7 @@
         <v>46275</v>
       </c>
       <c r="B174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C174" t="s">
         <v>226</v>
@@ -26937,7 +26940,7 @@
         <v>12</v>
       </c>
       <c r="F174" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G174" t="s">
         <v>182</v>
@@ -26946,7 +26949,7 @@
         <v>3</v>
       </c>
       <c r="I174" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J174" t="s">
         <v>251</v>
@@ -27075,7 +27078,7 @@
         <v>46275</v>
       </c>
       <c r="B175" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C175" t="s">
         <v>226</v>
@@ -27087,7 +27090,7 @@
         <v>12</v>
       </c>
       <c r="F175" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G175" t="s">
         <v>182</v>
@@ -27096,10 +27099,10 @@
         <v>2</v>
       </c>
       <c r="I175" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J175" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K175" t="n">
         <v>6.58829272068803</v>
@@ -27201,7 +27204,7 @@
         <v>46275</v>
       </c>
       <c r="B176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C176" t="s">
         <v>226</v>
@@ -27213,7 +27216,7 @@
         <v>12</v>
       </c>
       <c r="F176" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G176" t="s">
         <v>182</v>
@@ -27222,10 +27225,10 @@
         <v>8</v>
       </c>
       <c r="I176" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J176" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K176" t="n">
         <v>8.01855616742048</v>
@@ -27351,7 +27354,7 @@
         <v>46275</v>
       </c>
       <c r="B177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C177" t="s">
         <v>226</v>
@@ -27363,7 +27366,7 @@
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G177" t="s">
         <v>182</v>
@@ -27372,7 +27375,7 @@
         <v>7</v>
       </c>
       <c r="I177" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J177" t="s">
         <v>255</v>
@@ -27501,7 +27504,7 @@
         <v>46275</v>
       </c>
       <c r="B178" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C178" t="s">
         <v>226</v>
@@ -27513,7 +27516,7 @@
         <v>12</v>
       </c>
       <c r="F178" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G178" t="s">
         <v>182</v>
@@ -27522,7 +27525,7 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J178" t="s">
         <v>291</v>
@@ -27651,7 +27654,7 @@
         <v>46275</v>
       </c>
       <c r="B179" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C179" t="s">
         <v>226</v>
@@ -27663,7 +27666,7 @@
         <v>12</v>
       </c>
       <c r="F179" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G179" t="s">
         <v>182</v>
@@ -27672,10 +27675,10 @@
         <v>6</v>
       </c>
       <c r="I179" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J179" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K179" t="n">
         <v>34.2727179359168</v>
@@ -27801,7 +27804,7 @@
         <v>46275</v>
       </c>
       <c r="B180" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C180" t="s">
         <v>226</v>
@@ -27813,7 +27816,7 @@
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G180" t="s">
         <v>182</v>
@@ -27822,10 +27825,10 @@
         <v>1</v>
       </c>
       <c r="I180" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J180" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K180" t="n">
         <v>51.5043704790109</v>
